--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -8,28 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adpackmx-my.sharepoint.com/personal/mantenimiento_ad-pack_com_mx/Documents/Documentos/Propuesta de Manto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{DF2F9A4D-8A01-491B-A508-460B09F565DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7E3B881-3813-46AE-8C04-6E2CEE96F51A}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{DF2F9A4D-8A01-491B-A508-460B09F565DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B50A46A-F82E-454B-B75F-FCEEF1AAD8E2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Laminator" sheetId="2" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="11" r:id="rId2"/>
-    <sheet name="Slitter Rewinder" sheetId="3" r:id="rId3"/>
-    <sheet name="Komatsu OBS45" sheetId="4" r:id="rId4"/>
-    <sheet name="Rotary Press" sheetId="5" r:id="rId5"/>
-    <sheet name="Prensa PL" sheetId="6" r:id="rId6"/>
-    <sheet name="IMESA" sheetId="7" r:id="rId7"/>
-    <sheet name="Single Knife" sheetId="8" r:id="rId8"/>
-    <sheet name="Hojeadora Robust" sheetId="9" r:id="rId9"/>
-    <sheet name="Gapcutter" sheetId="10" r:id="rId10"/>
+    <sheet name="Slitter Rewinder" sheetId="3" r:id="rId2"/>
+    <sheet name="Komatsu OBS45" sheetId="4" r:id="rId3"/>
+    <sheet name="Rotary Press" sheetId="5" r:id="rId4"/>
+    <sheet name="Prensa PL" sheetId="6" r:id="rId5"/>
+    <sheet name="IMESA" sheetId="7" r:id="rId6"/>
+    <sheet name="Single Knife" sheetId="8" r:id="rId7"/>
+    <sheet name="Hojeadora Robust" sheetId="9" r:id="rId8"/>
+    <sheet name="Gapcutter" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="176">
   <si>
     <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
   </si>
@@ -266,17 +265,6 @@
   </si>
   <si>
     <t>VAC</t>
-  </si>
-  <si>
-    <t>Realizó: ________________________
-Firma: ___________________________</t>
-  </si>
-  <si>
-    <t>Fecha: __________________</t>
-  </si>
-  <si>
-    <t>Supervisor de Producción: ________________________
-Firma: ___________________________</t>
   </si>
   <si>
     <t>MANTENIMIENTO PREVENTIVO   —   SLITTER REWINDER 3M EXX4011A+</t>
@@ -557,6 +545,19 @@
   </si>
   <si>
     <t>Nombre de máquina:  Imesa 558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizo: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha: </t>
+  </si>
+  <si>
+    <t>Supervisor de Producción: 
+Firma: _____________________________</t>
+  </si>
+  <si>
+    <t>Firma:</t>
   </si>
 </sst>
 </file>
@@ -660,7 +661,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -715,8 +716,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -877,26 +883,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -921,11 +907,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -983,30 +978,19 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1017,11 +1001,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1029,25 +1021,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -1088,7 +1071,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1109,6 +1092,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3056,43 +3051,43 @@
       <c r="L2" s="13"/>
       <c r="M2" s="13"/>
       <c r="N2" s="13"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
     </row>
     <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="49" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="54"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="46"/>
     </row>
     <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="35" t="s">
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="K4" s="22"/>
@@ -3105,7 +3100,7 @@
     </row>
     <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="22"/>
@@ -3115,7 +3110,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="22"/>
@@ -3128,8 +3123,8 @@
     </row>
     <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="45" t="s">
-        <v>158</v>
+      <c r="B6" s="39" t="s">
+        <v>155</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -3138,8 +3133,8 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="35" t="s">
-        <v>169</v>
+      <c r="J6" s="32" t="s">
+        <v>166</v>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
@@ -3151,24 +3146,24 @@
     </row>
     <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="22"/>
@@ -3181,7 +3176,7 @@
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="22"/>
@@ -3197,7 +3192,7 @@
       <c r="L8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="39"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
@@ -3208,7 +3203,7 @@
       <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="26" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="22"/>
@@ -3224,7 +3219,7 @@
       <c r="L9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="39"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
@@ -3235,7 +3230,7 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="25" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="22"/>
@@ -3251,7 +3246,7 @@
       <c r="L10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
@@ -3262,7 +3257,7 @@
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="26" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="22"/>
@@ -3278,7 +3273,7 @@
       <c r="L11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="39"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
@@ -3289,7 +3284,7 @@
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="25" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="22"/>
@@ -3305,7 +3300,7 @@
       <c r="L12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="39"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
@@ -3316,7 +3311,7 @@
       <c r="B13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="26" t="s">
         <v>22</v>
       </c>
       <c r="D13" s="22"/>
@@ -3332,7 +3327,7 @@
       <c r="L13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
@@ -3343,7 +3338,7 @@
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="25" t="s">
         <v>24</v>
       </c>
       <c r="D14" s="22"/>
@@ -3359,7 +3354,7 @@
       <c r="L14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="39"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
@@ -3370,7 +3365,7 @@
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="26" t="s">
         <v>26</v>
       </c>
       <c r="D15" s="22"/>
@@ -3386,7 +3381,7 @@
       <c r="L15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="39"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
@@ -3397,7 +3392,7 @@
       <c r="B16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="25" t="s">
         <v>64</v>
       </c>
       <c r="D16" s="22"/>
@@ -3413,7 +3408,7 @@
       <c r="L16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="39"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
@@ -3421,24 +3416,24 @@
     </row>
     <row r="17" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="38"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="29"/>
       <c r="K17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="41" t="s">
+      <c r="M17" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N17" s="22"/>
@@ -3451,7 +3446,7 @@
       <c r="B18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="25" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="22"/>
@@ -3467,7 +3462,7 @@
       <c r="L18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="39"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
@@ -3478,7 +3473,7 @@
       <c r="B19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="26" t="s">
         <v>33</v>
       </c>
       <c r="D19" s="22"/>
@@ -3494,7 +3489,7 @@
       <c r="L19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
@@ -3505,7 +3500,7 @@
       <c r="B20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="25" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="22"/>
@@ -3521,7 +3516,7 @@
       <c r="L20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M20" s="39"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
@@ -3532,7 +3527,7 @@
       <c r="B21" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="26" t="s">
         <v>37</v>
       </c>
       <c r="D21" s="22"/>
@@ -3548,7 +3543,7 @@
       <c r="L21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="39"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
@@ -3559,7 +3554,7 @@
       <c r="B22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="22"/>
@@ -3575,7 +3570,7 @@
       <c r="L22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M22" s="39"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
@@ -3586,7 +3581,7 @@
       <c r="B23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="26" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="22"/>
@@ -3602,7 +3597,7 @@
       <c r="L23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M23" s="39"/>
+      <c r="M23" s="24"/>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
@@ -3613,7 +3608,7 @@
       <c r="B24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D24" s="22"/>
@@ -3629,7 +3624,7 @@
       <c r="L24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -3640,7 +3635,7 @@
       <c r="B25" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="26" t="s">
         <v>45</v>
       </c>
       <c r="D25" s="22"/>
@@ -3656,7 +3651,7 @@
       <c r="L25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M25" s="39"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
@@ -3667,7 +3662,7 @@
       <c r="B26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D26" s="22"/>
@@ -3683,7 +3678,7 @@
       <c r="L26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="39"/>
+      <c r="M26" s="24"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
@@ -3694,7 +3689,7 @@
       <c r="B27" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D27" s="22"/>
@@ -3710,7 +3705,7 @@
       <c r="L27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="39"/>
+      <c r="M27" s="24"/>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
@@ -3718,24 +3713,24 @@
     </row>
     <row r="28" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="38"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="29"/>
       <c r="K28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M28" s="41" t="s">
+      <c r="M28" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N28" s="22"/>
@@ -3748,7 +3743,7 @@
       <c r="B29" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="25" t="s">
         <v>52</v>
       </c>
       <c r="D29" s="22"/>
@@ -3764,7 +3759,7 @@
       <c r="L29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M29" s="39"/>
+      <c r="M29" s="24"/>
       <c r="N29" s="22"/>
       <c r="O29" s="22"/>
       <c r="P29" s="22"/>
@@ -3775,7 +3770,7 @@
       <c r="B30" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="26" t="s">
         <v>54</v>
       </c>
       <c r="D30" s="22"/>
@@ -3791,7 +3786,7 @@
       <c r="L30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M30" s="39"/>
+      <c r="M30" s="24"/>
       <c r="N30" s="22"/>
       <c r="O30" s="22"/>
       <c r="P30" s="22"/>
@@ -3802,7 +3797,7 @@
       <c r="B31" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" s="25" t="s">
         <v>56</v>
       </c>
       <c r="D31" s="22"/>
@@ -3818,7 +3813,7 @@
       <c r="L31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M31" s="39"/>
+      <c r="M31" s="24"/>
       <c r="N31" s="22"/>
       <c r="O31" s="22"/>
       <c r="P31" s="22"/>
@@ -3829,7 +3824,7 @@
       <c r="B32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="26" t="s">
         <v>58</v>
       </c>
       <c r="D32" s="22"/>
@@ -3845,7 +3840,7 @@
       <c r="L32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="39"/>
+      <c r="M32" s="24"/>
       <c r="N32" s="22"/>
       <c r="O32" s="22"/>
       <c r="P32" s="22"/>
@@ -3856,7 +3851,7 @@
       <c r="B33" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="25" t="s">
         <v>60</v>
       </c>
       <c r="D33" s="22"/>
@@ -3872,7 +3867,7 @@
       <c r="L33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M33" s="39"/>
+      <c r="M33" s="24"/>
       <c r="N33" s="22"/>
       <c r="O33" s="22"/>
       <c r="P33" s="22"/>
@@ -3880,7 +3875,7 @@
     </row>
     <row r="34" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11"/>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C34" s="22"/>
@@ -3894,7 +3889,7 @@
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
       <c r="M34" s="23"/>
-      <c r="N34" s="21" t="s">
+      <c r="N34" s="33" t="s">
         <v>62</v>
       </c>
       <c r="O34" s="22"/>
@@ -3997,67 +3992,75 @@
     </row>
     <row r="37" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
-      <c r="B37" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="I37" s="25"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="26"/>
+      <c r="B37" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L37" s="72"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="72"/>
+      <c r="O37" s="72"/>
+      <c r="P37" s="72"/>
+      <c r="Q37" s="72"/>
     </row>
     <row r="38" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="29"/>
+      <c r="B38" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="73"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="73"/>
+      <c r="K38" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
     </row>
     <row r="39" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="32"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="71">
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="K37:Q37"/>
+    <mergeCell ref="B38:G39"/>
+    <mergeCell ref="K38:Q39"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="C8:J8"/>
@@ -4090,8 +4093,6 @@
     <mergeCell ref="M15:Q15"/>
     <mergeCell ref="M21:Q21"/>
     <mergeCell ref="C11:J11"/>
-    <mergeCell ref="B37:G39"/>
-    <mergeCell ref="K37:Q39"/>
     <mergeCell ref="C20:J20"/>
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="M11:Q11"/>
@@ -4133,9 +4134,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:Q32"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -4145,7 +4146,7 @@
     <row r="1" spans="1:17" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:17" ht="56.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="22"/>
@@ -4160,17 +4161,17 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
-      <c r="O2" s="43"/>
+      <c r="O2" s="35"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="44"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="22"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="46" t="s">
-        <v>149</v>
+      <c r="E3" s="34" t="s">
+        <v>79</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
@@ -4181,13 +4182,13 @@
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="23"/>
-      <c r="O3" s="43"/>
+      <c r="O3" s="35"/>
       <c r="P3" s="22"/>
       <c r="Q3" s="23"/>
     </row>
     <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="22"/>
@@ -4197,7 +4198,7 @@
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="K4" s="22"/>
@@ -4210,7 +4211,7 @@
     </row>
     <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="22"/>
@@ -4220,7 +4221,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="22"/>
@@ -4233,7 +4234,7 @@
     </row>
     <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="39" t="s">
         <v>157</v>
       </c>
       <c r="C6" s="22"/>
@@ -4243,8 +4244,8 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="35" t="s">
-        <v>168</v>
+      <c r="J6" s="32" t="s">
+        <v>167</v>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
@@ -4256,24 +4257,24 @@
     </row>
     <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="22"/>
@@ -4286,7 +4287,7 @@
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="22"/>
@@ -4302,7 +4303,7 @@
       <c r="L8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="39"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
@@ -4313,8 +4314,8 @@
       <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>150</v>
+      <c r="C9" s="26" t="s">
+        <v>80</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
@@ -4329,7 +4330,7 @@
       <c r="L9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="39"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
@@ -4340,8 +4341,8 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>151</v>
+      <c r="C10" s="25" t="s">
+        <v>81</v>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
@@ -4356,7 +4357,7 @@
       <c r="L10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
@@ -4367,8 +4368,8 @@
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>152</v>
+      <c r="C11" s="26" t="s">
+        <v>82</v>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
@@ -4383,7 +4384,7 @@
       <c r="L11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="39"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
@@ -4394,8 +4395,8 @@
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>153</v>
+      <c r="C12" s="25" t="s">
+        <v>83</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
@@ -4410,7 +4411,7 @@
       <c r="L12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="39"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
@@ -4421,8 +4422,8 @@
       <c r="B13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>26</v>
+      <c r="C13" s="26" t="s">
+        <v>84</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
@@ -4437,7 +4438,7 @@
       <c r="L13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
@@ -4448,8 +4449,8 @@
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="34" t="s">
-        <v>147</v>
+      <c r="C14" s="25" t="s">
+        <v>85</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
@@ -4464,7 +4465,7 @@
       <c r="L14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="39"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
@@ -4472,26 +4473,26 @@
     </row>
     <row r="15" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
-      <c r="B15" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="41" t="s">
-        <v>9</v>
-      </c>
+      <c r="B15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="24"/>
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
@@ -4500,10 +4501,10 @@
     <row r="16" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
       <c r="B16" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>28</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
@@ -4518,7 +4519,7 @@
       <c r="L16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="39"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
@@ -4526,26 +4527,26 @@
     </row>
     <row r="17" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
-      <c r="B17" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="39"/>
+      <c r="B17" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="36" t="s">
+        <v>9</v>
+      </c>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
       <c r="P17" s="22"/>
@@ -4556,8 +4557,8 @@
       <c r="B18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="34" t="s">
-        <v>39</v>
+      <c r="C18" s="25" t="s">
+        <v>31</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -4572,7 +4573,7 @@
       <c r="L18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="39"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
@@ -4583,8 +4584,8 @@
       <c r="B19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="33" t="s">
-        <v>154</v>
+      <c r="C19" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -4599,7 +4600,7 @@
       <c r="L19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
@@ -4610,8 +4611,8 @@
       <c r="B20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="34" t="s">
-        <v>45</v>
+      <c r="C20" s="25" t="s">
+        <v>35</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -4626,7 +4627,7 @@
       <c r="L20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M20" s="39"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
@@ -4637,8 +4638,8 @@
       <c r="B21" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="33" t="s">
-        <v>47</v>
+      <c r="C21" s="26" t="s">
+        <v>37</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -4653,7 +4654,7 @@
       <c r="L21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="39"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
@@ -4661,26 +4662,26 @@
     </row>
     <row r="22" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
-      <c r="B22" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="41" t="s">
-        <v>9</v>
-      </c>
+      <c r="B22" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M22" s="24"/>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
@@ -4688,11 +4689,11 @@
     </row>
     <row r="23" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
-      <c r="B23" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>52</v>
+      <c r="B23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>86</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
@@ -4707,7 +4708,7 @@
       <c r="L23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M23" s="39"/>
+      <c r="M23" s="24"/>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
@@ -4715,11 +4716,11 @@
     </row>
     <row r="24" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
-      <c r="B24" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>135</v>
+      <c r="B24" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>87</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -4734,7 +4735,7 @@
       <c r="L24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -4742,11 +4743,11 @@
     </row>
     <row r="25" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
-      <c r="B25" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>92</v>
+      <c r="B25" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>45</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -4761,7 +4762,7 @@
       <c r="L25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M25" s="39"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
@@ -4769,11 +4770,11 @@
     </row>
     <row r="26" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
-      <c r="B26" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>60</v>
+      <c r="B26" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>47</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -4788,7 +4789,7 @@
       <c r="L26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="39"/>
+      <c r="M26" s="24"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
@@ -4796,922 +4797,10 @@
     </row>
     <row r="27" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
-      <c r="B27" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="23"/>
-    </row>
-    <row r="28" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q28" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-    </row>
-    <row r="30" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="I30" s="25"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="25"/>
-      <c r="P30" s="25"/>
-      <c r="Q30" s="26"/>
-    </row>
-    <row r="31" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="28"/>
-      <c r="Q31" s="29"/>
-    </row>
-    <row r="32" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="B30:G32"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="K30:Q32"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="H30:J32"/>
-    <mergeCell ref="N27:Q27"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="M13:Q13"/>
-    <mergeCell ref="J4:Q4"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="J5:Q5"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="J6:Q6"/>
-    <mergeCell ref="M11:Q11"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="M9:Q9"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="M26:Q26"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="M14:Q14"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="C26:J26"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="C23:J23"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="B22:J22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436AFDF8-E0FA-4EB7-84A4-E574156E8964}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.5546875" customWidth="1"/>
-    <col min="2" max="17" width="12.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:17" ht="56.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="23"/>
-    </row>
-    <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="23"/>
-    </row>
-    <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="23"/>
-    </row>
-    <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="35" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="23"/>
-    </row>
-    <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="23"/>
-    </row>
-    <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="23"/>
-    </row>
-    <row r="8" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="39"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="23"/>
-    </row>
-    <row r="9" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M9" s="39"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="23"/>
-    </row>
-    <row r="10" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M10" s="39"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="23"/>
-    </row>
-    <row r="11" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="39"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="23"/>
-    </row>
-    <row r="12" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M12" s="39"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="23"/>
-    </row>
-    <row r="13" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M13" s="39"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="23"/>
-    </row>
-    <row r="14" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="39"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="23"/>
-    </row>
-    <row r="15" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="23"/>
-    </row>
-    <row r="16" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="23"/>
-    </row>
-    <row r="17" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="23"/>
-    </row>
-    <row r="18" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M18" s="39"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="23"/>
-    </row>
-    <row r="19" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M19" s="39"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="22"/>
-      <c r="Q19" s="23"/>
-    </row>
-    <row r="20" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M20" s="39"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="23"/>
-    </row>
-    <row r="21" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M21" s="39"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="22"/>
-      <c r="Q21" s="23"/>
-    </row>
-    <row r="22" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M22" s="39"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="23"/>
-    </row>
-    <row r="23" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M23" s="39"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="23"/>
-    </row>
-    <row r="24" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M24" s="39"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="23"/>
-    </row>
-    <row r="25" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M25" s="39"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="23"/>
-    </row>
-    <row r="26" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M26" s="39"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="23"/>
-    </row>
-    <row r="27" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
       <c r="B27" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D27" s="22"/>
@@ -5727,7 +4816,7 @@
       <c r="L27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="39"/>
+      <c r="M27" s="24"/>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
@@ -5735,24 +4824,24 @@
     </row>
     <row r="28" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="38"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="29"/>
       <c r="K28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M28" s="41" t="s">
+      <c r="M28" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N28" s="22"/>
@@ -5765,7 +4854,7 @@
       <c r="B29" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="25" t="s">
         <v>52</v>
       </c>
       <c r="D29" s="22"/>
@@ -5781,7 +4870,7 @@
       <c r="L29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M29" s="39"/>
+      <c r="M29" s="24"/>
       <c r="N29" s="22"/>
       <c r="O29" s="22"/>
       <c r="P29" s="22"/>
@@ -5792,7 +4881,7 @@
       <c r="B30" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="26" t="s">
         <v>54</v>
       </c>
       <c r="D30" s="22"/>
@@ -5808,7 +4897,7 @@
       <c r="L30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M30" s="39"/>
+      <c r="M30" s="24"/>
       <c r="N30" s="22"/>
       <c r="O30" s="22"/>
       <c r="P30" s="22"/>
@@ -5819,8 +4908,8 @@
       <c r="B31" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="34" t="s">
-        <v>91</v>
+      <c r="C31" s="25" t="s">
+        <v>88</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -5835,7 +4924,7 @@
       <c r="L31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M31" s="39"/>
+      <c r="M31" s="24"/>
       <c r="N31" s="22"/>
       <c r="O31" s="22"/>
       <c r="P31" s="22"/>
@@ -5846,8 +4935,8 @@
       <c r="B32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="33" t="s">
-        <v>92</v>
+      <c r="C32" s="26" t="s">
+        <v>89</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -5862,7 +4951,7 @@
       <c r="L32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="39"/>
+      <c r="M32" s="24"/>
       <c r="N32" s="22"/>
       <c r="O32" s="22"/>
       <c r="P32" s="22"/>
@@ -5873,7 +4962,7 @@
       <c r="B33" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="25" t="s">
         <v>60</v>
       </c>
       <c r="D33" s="22"/>
@@ -5889,7 +4978,7 @@
       <c r="L33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M33" s="39"/>
+      <c r="M33" s="24"/>
       <c r="N33" s="22"/>
       <c r="O33" s="22"/>
       <c r="P33" s="22"/>
@@ -5897,7 +4986,7 @@
     </row>
     <row r="34" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11"/>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C34" s="22"/>
@@ -5911,7 +5000,7 @@
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
       <c r="M34" s="23"/>
-      <c r="N34" s="21" t="s">
+      <c r="N34" s="33" t="s">
         <v>62</v>
       </c>
       <c r="O34" s="22"/>
@@ -6014,67 +5103,75 @@
     </row>
     <row r="37" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
-      <c r="B37" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="I37" s="25"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="26"/>
+      <c r="B37" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L37" s="72"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="72"/>
+      <c r="O37" s="72"/>
+      <c r="P37" s="72"/>
+      <c r="Q37" s="72"/>
     </row>
     <row r="38" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="29"/>
+      <c r="B38" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="73"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="73"/>
+      <c r="K38" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
     </row>
     <row r="39" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="32"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="72">
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="K37:Q37"/>
+    <mergeCell ref="B38:G39"/>
+    <mergeCell ref="K38:Q39"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="C23:J23"/>
@@ -6121,8 +5218,6 @@
     <mergeCell ref="C18:J18"/>
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="J5:Q5"/>
-    <mergeCell ref="B37:G39"/>
-    <mergeCell ref="K37:Q39"/>
     <mergeCell ref="C20:J20"/>
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="M11:Q11"/>
@@ -6151,7 +5246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6163,7 +5258,7 @@
     <row r="1" spans="1:17" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:17" ht="56.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="22"/>
@@ -6178,17 +5273,17 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
-      <c r="O2" s="43"/>
+      <c r="O2" s="35"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="44"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="22"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="46" t="s">
-        <v>93</v>
+      <c r="E3" s="34" t="s">
+        <v>90</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
@@ -6199,13 +5294,13 @@
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="23"/>
-      <c r="O3" s="43"/>
+      <c r="O3" s="35"/>
       <c r="P3" s="22"/>
       <c r="Q3" s="23"/>
     </row>
     <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="22"/>
@@ -6215,7 +5310,7 @@
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="K4" s="22"/>
@@ -6228,7 +5323,7 @@
     </row>
     <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="22"/>
@@ -6238,7 +5333,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="22"/>
@@ -6251,8 +5346,8 @@
     </row>
     <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="45" t="s">
-        <v>159</v>
+      <c r="B6" s="39" t="s">
+        <v>156</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -6261,8 +5356,8 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="35" t="s">
-        <v>171</v>
+      <c r="J6" s="32" t="s">
+        <v>168</v>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
@@ -6274,24 +5369,24 @@
     </row>
     <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="22"/>
@@ -6304,8 +5399,8 @@
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="34" t="s">
-        <v>95</v>
+      <c r="C8" s="25" t="s">
+        <v>92</v>
       </c>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
@@ -6320,7 +5415,7 @@
       <c r="L8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="39"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
@@ -6331,8 +5426,8 @@
       <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>96</v>
+      <c r="C9" s="26" t="s">
+        <v>93</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
@@ -6347,7 +5442,7 @@
       <c r="L9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="39"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
@@ -6358,8 +5453,8 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>97</v>
+      <c r="C10" s="25" t="s">
+        <v>94</v>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
@@ -6374,7 +5469,7 @@
       <c r="L10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
@@ -6385,8 +5480,8 @@
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>98</v>
+      <c r="C11" s="26" t="s">
+        <v>95</v>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
@@ -6401,7 +5496,7 @@
       <c r="L11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="39"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
@@ -6412,8 +5507,8 @@
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>99</v>
+      <c r="C12" s="25" t="s">
+        <v>96</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
@@ -6428,7 +5523,7 @@
       <c r="L12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="39"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
@@ -6439,8 +5534,8 @@
       <c r="B13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>100</v>
+      <c r="C13" s="26" t="s">
+        <v>97</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
@@ -6455,7 +5550,7 @@
       <c r="L13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
@@ -6466,8 +5561,8 @@
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="34" t="s">
-        <v>101</v>
+      <c r="C14" s="25" t="s">
+        <v>98</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
@@ -6482,7 +5577,7 @@
       <c r="L14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="39"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
@@ -6493,8 +5588,8 @@
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>102</v>
+      <c r="C15" s="26" t="s">
+        <v>99</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="22"/>
@@ -6509,7 +5604,7 @@
       <c r="L15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="39"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
@@ -6520,7 +5615,7 @@
       <c r="B16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="25" t="s">
         <v>26</v>
       </c>
       <c r="D16" s="22"/>
@@ -6536,7 +5631,7 @@
       <c r="L16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="39"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
@@ -6547,48 +5642,48 @@
       <c r="B17" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="63"/>
+      <c r="C17" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="55"/>
       <c r="K17" s="19" t="s">
         <v>12</v>
       </c>
       <c r="L17" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="M17" s="64"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="59"/>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="60"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="51"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="52"/>
     </row>
     <row r="18" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="38"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="29"/>
       <c r="K18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="41" t="s">
+      <c r="M18" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N18" s="22"/>
@@ -6601,7 +5696,7 @@
       <c r="B19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="22"/>
@@ -6617,7 +5712,7 @@
       <c r="L19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
@@ -6628,7 +5723,7 @@
       <c r="B20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="25" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="22"/>
@@ -6644,7 +5739,7 @@
       <c r="L20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M20" s="39"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
@@ -6655,7 +5750,7 @@
       <c r="B21" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="26" t="s">
         <v>35</v>
       </c>
       <c r="D21" s="22"/>
@@ -6671,7 +5766,7 @@
       <c r="L21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="39"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
@@ -6682,7 +5777,7 @@
       <c r="B22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="25" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="22"/>
@@ -6698,7 +5793,7 @@
       <c r="L22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M22" s="39"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
@@ -6709,7 +5804,7 @@
       <c r="B23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="26" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="22"/>
@@ -6725,7 +5820,7 @@
       <c r="L23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M23" s="39"/>
+      <c r="M23" s="24"/>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
@@ -6736,8 +5831,8 @@
       <c r="B24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="34" t="s">
-        <v>104</v>
+      <c r="C24" s="25" t="s">
+        <v>101</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -6752,7 +5847,7 @@
       <c r="L24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -6763,8 +5858,8 @@
       <c r="B25" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>105</v>
+      <c r="C25" s="26" t="s">
+        <v>102</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -6779,7 +5874,7 @@
       <c r="L25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M25" s="39"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
@@ -6790,23 +5885,23 @@
       <c r="B26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="57"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="49"/>
       <c r="K26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="39"/>
+      <c r="M26" s="24"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
@@ -6817,7 +5912,7 @@
       <c r="B27" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D27" s="22"/>
@@ -6833,7 +5928,7 @@
       <c r="L27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="39"/>
+      <c r="M27" s="24"/>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
@@ -6844,31 +5939,31 @@
       <c r="B28" s="8">
         <v>20</v>
       </c>
-      <c r="C28" s="55" t="s">
+      <c r="C28" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="57"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="49"/>
       <c r="K28" s="16" t="s">
         <v>12</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M28" s="58"/>
-      <c r="N28" s="59"/>
-      <c r="O28" s="59"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="60"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="51"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="52"/>
     </row>
     <row r="29" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="22"/>
@@ -6882,7 +5977,7 @@
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
       <c r="M29" s="23"/>
-      <c r="N29" s="21" t="s">
+      <c r="N29" s="33" t="s">
         <v>62</v>
       </c>
       <c r="O29" s="22"/>
@@ -6985,70 +6080,78 @@
     </row>
     <row r="32" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11"/>
-      <c r="B32" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="I32" s="25"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="26"/>
+      <c r="B32" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
     </row>
     <row r="33" spans="2:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
-      <c r="Q33" s="29"/>
+      <c r="B33" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="70"/>
     </row>
     <row r="34" spans="2:17" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="32"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="73"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="70"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="70"/>
+      <c r="Q34" s="70"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.3">
       <c r="J45" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="62">
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="B33:G34"/>
+    <mergeCell ref="K33:Q34"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="C23:J23"/>
     <mergeCell ref="C8:J8"/>
@@ -7090,9 +6193,7 @@
     <mergeCell ref="C27:J27"/>
     <mergeCell ref="M27:Q27"/>
     <mergeCell ref="M26:Q26"/>
-    <mergeCell ref="K32:Q34"/>
     <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="B32:G34"/>
     <mergeCell ref="C28:J28"/>
     <mergeCell ref="N29:Q29"/>
     <mergeCell ref="C24:J24"/>
@@ -7115,7 +6216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7127,7 +6228,7 @@
     <row r="1" spans="1:17" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:17" ht="56.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="22"/>
@@ -7142,17 +6243,17 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
-      <c r="O2" s="43"/>
+      <c r="O2" s="35"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="44"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="22"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="46" t="s">
-        <v>156</v>
+      <c r="E3" s="34" t="s">
+        <v>153</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
@@ -7163,13 +6264,13 @@
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="23"/>
-      <c r="O3" s="43"/>
+      <c r="O3" s="35"/>
       <c r="P3" s="22"/>
       <c r="Q3" s="23"/>
     </row>
     <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="22"/>
@@ -7179,7 +6280,7 @@
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="K4" s="22"/>
@@ -7192,7 +6293,7 @@
     </row>
     <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="22"/>
@@ -7202,7 +6303,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="22"/>
@@ -7215,8 +6316,8 @@
     </row>
     <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="45" t="s">
-        <v>172</v>
+      <c r="B6" s="39" t="s">
+        <v>169</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -7225,8 +6326,8 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="35" t="s">
-        <v>163</v>
+      <c r="J6" s="32" t="s">
+        <v>160</v>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
@@ -7238,24 +6339,24 @@
     </row>
     <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="22"/>
@@ -7268,7 +6369,7 @@
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="22"/>
@@ -7284,7 +6385,7 @@
       <c r="L8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="39"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
@@ -7295,8 +6396,8 @@
       <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="34" t="s">
-        <v>106</v>
+      <c r="C9" s="25" t="s">
+        <v>103</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
@@ -7311,7 +6412,7 @@
       <c r="L9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="39"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
@@ -7322,8 +6423,8 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>107</v>
+      <c r="C10" s="25" t="s">
+        <v>104</v>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
@@ -7338,7 +6439,7 @@
       <c r="L10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
@@ -7349,8 +6450,8 @@
       <c r="B11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="34" t="s">
-        <v>108</v>
+      <c r="C11" s="25" t="s">
+        <v>105</v>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
@@ -7365,7 +6466,7 @@
       <c r="L11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="39"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
@@ -7376,8 +6477,8 @@
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>109</v>
+      <c r="C12" s="25" t="s">
+        <v>106</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
@@ -7392,7 +6493,7 @@
       <c r="L12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="39"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
@@ -7403,8 +6504,8 @@
       <c r="B13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="34" t="s">
-        <v>110</v>
+      <c r="C13" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
@@ -7419,7 +6520,7 @@
       <c r="L13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
@@ -7430,8 +6531,8 @@
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="34" t="s">
-        <v>111</v>
+      <c r="C14" s="25" t="s">
+        <v>108</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
@@ -7446,7 +6547,7 @@
       <c r="L14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="39"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
@@ -7457,8 +6558,8 @@
       <c r="B15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="34" t="s">
-        <v>112</v>
+      <c r="C15" s="25" t="s">
+        <v>109</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="22"/>
@@ -7473,7 +6574,7 @@
       <c r="L15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="39"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
@@ -7484,8 +6585,8 @@
       <c r="B16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="34" t="s">
-        <v>113</v>
+      <c r="C16" s="25" t="s">
+        <v>110</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
@@ -7500,7 +6601,7 @@
       <c r="L16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="39"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
@@ -7511,8 +6612,8 @@
       <c r="B17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="34" t="s">
-        <v>114</v>
+      <c r="C17" s="25" t="s">
+        <v>111</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
@@ -7527,19 +6628,19 @@
       <c r="L17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M17" s="70"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="72"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="63"/>
+      <c r="P17" s="63"/>
+      <c r="Q17" s="64"/>
     </row>
     <row r="18" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="34" t="s">
-        <v>115</v>
+      <c r="C18" s="25" t="s">
+        <v>112</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -7554,7 +6655,7 @@
       <c r="L18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="39"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
@@ -7565,8 +6666,8 @@
       <c r="B19" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="34" t="s">
-        <v>116</v>
+      <c r="C19" s="25" t="s">
+        <v>113</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -7581,7 +6682,7 @@
       <c r="L19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
@@ -7592,7 +6693,7 @@
       <c r="B20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="25" t="s">
         <v>28</v>
       </c>
       <c r="D20" s="22"/>
@@ -7608,7 +6709,7 @@
       <c r="L20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M20" s="39"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
@@ -7616,24 +6717,24 @@
     </row>
     <row r="21" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="38"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="29"/>
       <c r="K21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="41" t="s">
+      <c r="M21" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N21" s="22"/>
@@ -7646,7 +6747,7 @@
       <c r="B22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="25" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="22"/>
@@ -7662,7 +6763,7 @@
       <c r="L22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M22" s="39"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
@@ -7673,7 +6774,7 @@
       <c r="B23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="25" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="22"/>
@@ -7689,7 +6790,7 @@
       <c r="L23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M23" s="39"/>
+      <c r="M23" s="24"/>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
@@ -7700,7 +6801,7 @@
       <c r="B24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="25" t="s">
         <v>35</v>
       </c>
       <c r="D24" s="22"/>
@@ -7716,7 +6817,7 @@
       <c r="L24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -7727,7 +6828,7 @@
       <c r="B25" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" s="25" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="22"/>
@@ -7743,7 +6844,7 @@
       <c r="L25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M25" s="39"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
@@ -7754,7 +6855,7 @@
       <c r="B26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D26" s="22"/>
@@ -7770,7 +6871,7 @@
       <c r="L26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="39"/>
+      <c r="M26" s="24"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
@@ -7781,8 +6882,8 @@
       <c r="B27" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="34" t="s">
-        <v>117</v>
+      <c r="C27" s="25" t="s">
+        <v>114</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -7797,17 +6898,17 @@
       <c r="L27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="66"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="67"/>
-      <c r="Q27" s="68"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="59"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="60"/>
     </row>
     <row r="28" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D28" s="22"/>
@@ -7823,17 +6924,17 @@
       <c r="L28" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="M28" s="69"/>
-      <c r="N28" s="69"/>
-      <c r="O28" s="69"/>
-      <c r="P28" s="69"/>
-      <c r="Q28" s="69"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="61"/>
+      <c r="O28" s="61"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="61"/>
     </row>
     <row r="29" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="25" t="s">
         <v>45</v>
       </c>
       <c r="D29" s="22"/>
@@ -7849,17 +6950,17 @@
       <c r="L29" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="M29" s="69"/>
-      <c r="N29" s="69"/>
-      <c r="O29" s="69"/>
-      <c r="P29" s="69"/>
-      <c r="Q29" s="69"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="61"/>
+      <c r="O29" s="61"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="61"/>
     </row>
     <row r="30" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D30" s="22"/>
@@ -7875,17 +6976,17 @@
       <c r="L30" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="M30" s="69"/>
-      <c r="N30" s="69"/>
-      <c r="O30" s="69"/>
-      <c r="P30" s="69"/>
-      <c r="Q30" s="69"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="61"/>
     </row>
     <row r="31" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" s="25" t="s">
         <v>49</v>
       </c>
       <c r="D31" s="22"/>
@@ -7901,18 +7002,18 @@
       <c r="L31" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="M31" s="69"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="69"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="69"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
     </row>
     <row r="32" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="34" t="s">
-        <v>118</v>
+      <c r="C32" s="25" t="s">
+        <v>115</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -7927,18 +7028,18 @@
       <c r="L32" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="M32" s="69"/>
-      <c r="N32" s="69"/>
-      <c r="O32" s="69"/>
-      <c r="P32" s="69"/>
-      <c r="Q32" s="69"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="61"/>
+      <c r="O32" s="61"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="61"/>
     </row>
     <row r="33" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>155</v>
+        <v>116</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>152</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -7953,15 +7054,15 @@
       <c r="L33" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="M33" s="69"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="69"/>
-      <c r="P33" s="69"/>
-      <c r="Q33" s="69"/>
+      <c r="M33" s="61"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="61"/>
+      <c r="P33" s="61"/>
+      <c r="Q33" s="61"/>
     </row>
     <row r="34" spans="1:17" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A34" s="11"/>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C34" s="22"/>
@@ -7975,7 +7076,7 @@
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
       <c r="M34" s="23"/>
-      <c r="N34" s="21" t="s">
+      <c r="N34" s="33" t="s">
         <v>62</v>
       </c>
       <c r="O34" s="22"/>
@@ -8078,70 +7179,76 @@
     </row>
     <row r="37" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
-      <c r="B37" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="I37" s="25"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="26"/>
+      <c r="B37" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L37" s="72"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="72"/>
+      <c r="O37" s="72"/>
+      <c r="P37" s="72"/>
+      <c r="Q37" s="72"/>
     </row>
     <row r="38" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="29"/>
+      <c r="B38" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="73"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="73"/>
+      <c r="K38" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
     </row>
     <row r="39" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="32"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="B37:G39"/>
+  <mergeCells count="72">
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="K37:Q37"/>
+    <mergeCell ref="B38:G39"/>
+    <mergeCell ref="K38:Q39"/>
     <mergeCell ref="H37:J39"/>
-    <mergeCell ref="K37:Q39"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="B3:D3"/>
@@ -8215,7 +7322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8227,7 +7334,7 @@
     <row r="1" spans="1:17" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:17" ht="56.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="22"/>
@@ -8242,17 +7349,17 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
-      <c r="O2" s="43"/>
+      <c r="O2" s="35"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="44"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="22"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="46" t="s">
-        <v>120</v>
+      <c r="E3" s="34" t="s">
+        <v>117</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
@@ -8263,13 +7370,13 @@
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="23"/>
-      <c r="O3" s="43"/>
+      <c r="O3" s="35"/>
       <c r="P3" s="22"/>
       <c r="Q3" s="23"/>
     </row>
     <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="22"/>
@@ -8279,7 +7386,7 @@
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="K4" s="22"/>
@@ -8292,7 +7399,7 @@
     </row>
     <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="22"/>
@@ -8302,7 +7409,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="22"/>
@@ -8315,8 +7422,8 @@
     </row>
     <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="45" t="s">
-        <v>173</v>
+      <c r="B6" s="39" t="s">
+        <v>170</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -8325,8 +7432,8 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="35" t="s">
-        <v>164</v>
+      <c r="J6" s="32" t="s">
+        <v>161</v>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
@@ -8338,8 +7445,8 @@
     </row>
     <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="73" t="s">
-        <v>94</v>
+      <c r="B7" s="65" t="s">
+        <v>91</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
@@ -8355,7 +7462,7 @@
       <c r="L7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="22"/>
@@ -8368,8 +7475,8 @@
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="34" t="s">
-        <v>95</v>
+      <c r="C8" s="25" t="s">
+        <v>92</v>
       </c>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
@@ -8384,7 +7491,7 @@
       <c r="L8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="39"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
@@ -8395,8 +7502,8 @@
       <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>96</v>
+      <c r="C9" s="26" t="s">
+        <v>93</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
@@ -8411,7 +7518,7 @@
       <c r="L9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="39"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
@@ -8422,8 +7529,8 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>97</v>
+      <c r="C10" s="25" t="s">
+        <v>94</v>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
@@ -8438,7 +7545,7 @@
       <c r="L10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
@@ -8449,8 +7556,8 @@
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>98</v>
+      <c r="C11" s="26" t="s">
+        <v>95</v>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
@@ -8465,7 +7572,7 @@
       <c r="L11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="39"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
@@ -8476,8 +7583,8 @@
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>121</v>
+      <c r="C12" s="25" t="s">
+        <v>118</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
@@ -8492,7 +7599,7 @@
       <c r="L12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="39"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
@@ -8503,8 +7610,8 @@
       <c r="B13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>122</v>
+      <c r="C13" s="26" t="s">
+        <v>119</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
@@ -8519,7 +7626,7 @@
       <c r="L13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
@@ -8530,8 +7637,8 @@
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="34" t="s">
-        <v>123</v>
+      <c r="C14" s="25" t="s">
+        <v>120</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
@@ -8546,7 +7653,7 @@
       <c r="L14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="39"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
@@ -8557,8 +7664,8 @@
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>124</v>
+      <c r="C15" s="26" t="s">
+        <v>121</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="22"/>
@@ -8573,7 +7680,7 @@
       <c r="L15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="39"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
@@ -8584,7 +7691,7 @@
       <c r="B16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" s="25" t="s">
         <v>26</v>
       </c>
       <c r="D16" s="22"/>
@@ -8600,7 +7707,7 @@
       <c r="L16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="39"/>
+      <c r="M16" s="24"/>
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
@@ -8611,34 +7718,34 @@
       <c r="B17" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="75"/>
+      <c r="C17" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="67"/>
       <c r="K17" s="15" t="s">
         <v>12</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="M17" s="70"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="72"/>
+      <c r="M17" s="62"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="63"/>
+      <c r="P17" s="63"/>
+      <c r="Q17" s="64"/>
     </row>
     <row r="18" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="76"/>
+      <c r="C18" s="68"/>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -8652,7 +7759,7 @@
       <c r="L18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="41" t="s">
+      <c r="M18" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N18" s="22"/>
@@ -8665,7 +7772,7 @@
       <c r="B19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="26" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="22"/>
@@ -8681,7 +7788,7 @@
       <c r="L19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
@@ -8692,7 +7799,7 @@
       <c r="B20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" s="25" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="22"/>
@@ -8708,7 +7815,7 @@
       <c r="L20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M20" s="39"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
@@ -8719,7 +7826,7 @@
       <c r="B21" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="26" t="s">
         <v>35</v>
       </c>
       <c r="D21" s="22"/>
@@ -8735,7 +7842,7 @@
       <c r="L21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="39"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
@@ -8746,7 +7853,7 @@
       <c r="B22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" s="25" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="22"/>
@@ -8762,7 +7869,7 @@
       <c r="L22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M22" s="39"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
@@ -8773,7 +7880,7 @@
       <c r="B23" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="26" t="s">
         <v>39</v>
       </c>
       <c r="D23" s="22"/>
@@ -8789,7 +7896,7 @@
       <c r="L23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M23" s="39"/>
+      <c r="M23" s="24"/>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
@@ -8800,8 +7907,8 @@
       <c r="B24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="34" t="s">
-        <v>104</v>
+      <c r="C24" s="25" t="s">
+        <v>101</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -8816,7 +7923,7 @@
       <c r="L24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -8827,8 +7934,8 @@
       <c r="B25" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>125</v>
+      <c r="C25" s="26" t="s">
+        <v>122</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -8843,7 +7950,7 @@
       <c r="L25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M25" s="39"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
@@ -8854,7 +7961,7 @@
       <c r="B26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" s="25" t="s">
         <v>45</v>
       </c>
       <c r="D26" s="22"/>
@@ -8870,7 +7977,7 @@
       <c r="L26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="39"/>
+      <c r="M26" s="24"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
@@ -8881,7 +7988,7 @@
       <c r="B27" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D27" s="22"/>
@@ -8897,7 +8004,7 @@
       <c r="L27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="39"/>
+      <c r="M27" s="24"/>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
@@ -8908,7 +8015,7 @@
       <c r="B28" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="25" t="s">
         <v>49</v>
       </c>
       <c r="D28" s="22"/>
@@ -8924,15 +8031,15 @@
       <c r="L28" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M28" s="58"/>
-      <c r="N28" s="59"/>
-      <c r="O28" s="59"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="60"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="51"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="52"/>
     </row>
     <row r="29" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="22"/>
@@ -8946,7 +8053,7 @@
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
       <c r="M29" s="23"/>
-      <c r="N29" s="21" t="s">
+      <c r="N29" s="33" t="s">
         <v>62</v>
       </c>
       <c r="O29" s="22"/>
@@ -9049,67 +8156,75 @@
     </row>
     <row r="32" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11"/>
-      <c r="B32" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="I32" s="25"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="26"/>
+      <c r="B32" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
     </row>
     <row r="33" spans="2:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
-      <c r="Q33" s="29"/>
+      <c r="B33" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="70"/>
     </row>
     <row r="34" spans="2:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="32"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="73"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="70"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="70"/>
+      <c r="O34" s="70"/>
+      <c r="P34" s="70"/>
+      <c r="Q34" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="62">
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="B33:G34"/>
+    <mergeCell ref="K33:Q34"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="C23:J23"/>
     <mergeCell ref="C8:J8"/>
@@ -9151,9 +8266,7 @@
     <mergeCell ref="C27:J27"/>
     <mergeCell ref="M27:Q27"/>
     <mergeCell ref="M26:Q26"/>
-    <mergeCell ref="K32:Q34"/>
     <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="B32:G34"/>
     <mergeCell ref="C28:J28"/>
     <mergeCell ref="N29:Q29"/>
     <mergeCell ref="C24:J24"/>
@@ -9177,7 +8290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9189,7 +8302,7 @@
     <row r="1" spans="1:17" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:17" ht="56.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="22"/>
@@ -9204,17 +8317,17 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
-      <c r="O2" s="43"/>
+      <c r="O2" s="35"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="44"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="22"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="46" t="s">
-        <v>126</v>
+      <c r="E3" s="34" t="s">
+        <v>123</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
@@ -9225,13 +8338,13 @@
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="23"/>
-      <c r="O3" s="43"/>
+      <c r="O3" s="35"/>
       <c r="P3" s="22"/>
       <c r="Q3" s="23"/>
     </row>
     <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="22"/>
@@ -9241,7 +8354,7 @@
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="K4" s="22"/>
@@ -9254,7 +8367,7 @@
     </row>
     <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="22"/>
@@ -9264,7 +8377,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="22"/>
@@ -9277,8 +8390,8 @@
     </row>
     <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="45" t="s">
-        <v>174</v>
+      <c r="B6" s="39" t="s">
+        <v>171</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -9287,8 +8400,8 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="35" t="s">
-        <v>165</v>
+      <c r="J6" s="32" t="s">
+        <v>162</v>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
@@ -9300,24 +8413,24 @@
     </row>
     <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="22"/>
@@ -9330,7 +8443,7 @@
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="22"/>
@@ -9346,7 +8459,7 @@
       <c r="L8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="39"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
@@ -9357,8 +8470,8 @@
       <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>127</v>
+      <c r="C9" s="26" t="s">
+        <v>124</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
@@ -9373,7 +8486,7 @@
       <c r="L9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="39"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
@@ -9384,8 +8497,8 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>128</v>
+      <c r="C10" s="25" t="s">
+        <v>125</v>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
@@ -9400,7 +8513,7 @@
       <c r="L10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
@@ -9411,8 +8524,8 @@
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>129</v>
+      <c r="C11" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
@@ -9427,7 +8540,7 @@
       <c r="L11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="39"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
@@ -9438,8 +8551,8 @@
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>130</v>
+      <c r="C12" s="25" t="s">
+        <v>127</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
@@ -9454,7 +8567,7 @@
       <c r="L12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="39"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
@@ -9465,8 +8578,8 @@
       <c r="B13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>131</v>
+      <c r="C13" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
@@ -9481,7 +8594,7 @@
       <c r="L13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
@@ -9492,7 +8605,7 @@
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="25" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="22"/>
@@ -9508,7 +8621,7 @@
       <c r="L14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="39"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
@@ -9519,8 +8632,8 @@
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>132</v>
+      <c r="C15" s="26" t="s">
+        <v>129</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="22"/>
@@ -9535,7 +8648,7 @@
       <c r="L15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="39"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
@@ -9543,24 +8656,24 @@
     </row>
     <row r="16" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="38"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="29"/>
       <c r="K16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="41" t="s">
+      <c r="M16" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N16" s="22"/>
@@ -9573,7 +8686,7 @@
       <c r="B17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="25" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="22"/>
@@ -9589,7 +8702,7 @@
       <c r="L17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M17" s="39"/>
+      <c r="M17" s="24"/>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
       <c r="P17" s="22"/>
@@ -9600,7 +8713,7 @@
       <c r="B18" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="26" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="22"/>
@@ -9616,7 +8729,7 @@
       <c r="L18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="39"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
@@ -9627,7 +8740,7 @@
       <c r="B19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="22"/>
@@ -9643,7 +8756,7 @@
       <c r="L19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
@@ -9654,8 +8767,8 @@
       <c r="B20" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>133</v>
+      <c r="C20" s="26" t="s">
+        <v>130</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -9670,7 +8783,7 @@
       <c r="L20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M20" s="39"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
@@ -9681,7 +8794,7 @@
       <c r="B21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="25" t="s">
         <v>45</v>
       </c>
       <c r="D21" s="22"/>
@@ -9697,7 +8810,7 @@
       <c r="L21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="39"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
@@ -9708,7 +8821,7 @@
       <c r="B22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D22" s="22"/>
@@ -9724,7 +8837,7 @@
       <c r="L22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M22" s="39"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
@@ -9732,24 +8845,24 @@
     </row>
     <row r="23" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="38"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="29"/>
       <c r="K23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="41" t="s">
+      <c r="M23" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N23" s="22"/>
@@ -9762,8 +8875,8 @@
       <c r="B24" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="34" t="s">
-        <v>134</v>
+      <c r="C24" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -9778,7 +8891,7 @@
       <c r="L24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -9789,8 +8902,8 @@
       <c r="B25" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>135</v>
+      <c r="C25" s="26" t="s">
+        <v>132</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -9805,7 +8918,7 @@
       <c r="L25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M25" s="39"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
@@ -9816,8 +8929,8 @@
       <c r="B26" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="34" t="s">
-        <v>92</v>
+      <c r="C26" s="25" t="s">
+        <v>89</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -9832,7 +8945,7 @@
       <c r="L26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="39"/>
+      <c r="M26" s="24"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
@@ -9843,7 +8956,7 @@
       <c r="B27" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="26" t="s">
         <v>60</v>
       </c>
       <c r="D27" s="22"/>
@@ -9859,7 +8972,7 @@
       <c r="L27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="39"/>
+      <c r="M27" s="24"/>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
@@ -9867,7 +8980,7 @@
     </row>
     <row r="28" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="22"/>
@@ -9881,7 +8994,7 @@
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
       <c r="M28" s="23"/>
-      <c r="N28" s="21" t="s">
+      <c r="N28" s="33" t="s">
         <v>62</v>
       </c>
       <c r="O28" s="22"/>
@@ -9984,70 +9097,1014 @@
     </row>
     <row r="31" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
-      <c r="B31" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="I31" s="25"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="25"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="26"/>
+      <c r="B31" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
     </row>
     <row r="32" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="29"/>
+      <c r="B32" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="70"/>
     </row>
     <row r="33" spans="2:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="32"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="K31:Q33"/>
+  <mergeCells count="60">
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="B32:G33"/>
+    <mergeCell ref="K32:Q33"/>
     <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="B31:G33"/>
+    <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="M27:Q27"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="J4:Q4"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="N28:Q28"/>
+    <mergeCell ref="H31:J33"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="J5:Q5"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="M9:Q9"/>
+    <mergeCell ref="C26:J26"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="B28:M28"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="J6:Q6"/>
+    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="C10:J10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:Q33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.5546875" customWidth="1"/>
+    <col min="2" max="17" width="12.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:17" ht="56.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
+      <c r="B2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="23"/>
+    </row>
+    <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="23"/>
+    </row>
+    <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="23"/>
+    </row>
+    <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="23"/>
+    </row>
+    <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="23"/>
+    </row>
+    <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="23"/>
+    </row>
+    <row r="8" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="24"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="23"/>
+    </row>
+    <row r="9" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M9" s="24"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="23"/>
+    </row>
+    <row r="10" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="24"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="23"/>
+    </row>
+    <row r="11" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" s="24"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="23"/>
+    </row>
+    <row r="12" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M12" s="24"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="23"/>
+    </row>
+    <row r="13" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="24"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="23"/>
+    </row>
+    <row r="14" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="24"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="23"/>
+    </row>
+    <row r="15" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="24"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="23"/>
+    </row>
+    <row r="16" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="23"/>
+    </row>
+    <row r="17" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="24"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="23"/>
+    </row>
+    <row r="18" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="24"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="23"/>
+    </row>
+    <row r="19" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M19" s="24"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="23"/>
+    </row>
+    <row r="20" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11"/>
+      <c r="B20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M20" s="24"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="23"/>
+    </row>
+    <row r="21" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11"/>
+      <c r="B21" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M21" s="24"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="23"/>
+    </row>
+    <row r="22" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M22" s="24"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="23"/>
+    </row>
+    <row r="23" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="23"/>
+    </row>
+    <row r="24" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M24" s="24"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="23"/>
+    </row>
+    <row r="25" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" s="24"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="23"/>
+    </row>
+    <row r="26" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M26" s="24"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="23"/>
+    </row>
+    <row r="27" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27" s="24"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="23"/>
+    </row>
+    <row r="28" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="23"/>
+    </row>
+    <row r="29" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11"/>
+      <c r="B29" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q29" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11"/>
+      <c r="B30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+    </row>
+    <row r="31" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11"/>
+      <c r="B31" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+    </row>
+    <row r="32" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="70"/>
+    </row>
+    <row r="33" spans="2:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="70"/>
+    </row>
+  </sheetData>
+  <mergeCells count="60">
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="B32:G33"/>
+    <mergeCell ref="K32:Q33"/>
+    <mergeCell ref="M23:Q23"/>
     <mergeCell ref="M14:Q14"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="C13:J13"/>
@@ -10110,7 +10167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10121,7 +10178,7 @@
     <row r="1" spans="1:17" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:17" ht="56.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="22"/>
@@ -10136,17 +10193,17 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
-      <c r="O2" s="43"/>
+      <c r="O2" s="35"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="44"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="22"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="77" t="s">
-        <v>136</v>
+      <c r="E3" s="34" t="s">
+        <v>138</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
@@ -10157,13 +10214,13 @@
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="23"/>
-      <c r="O3" s="43"/>
+      <c r="O3" s="35"/>
       <c r="P3" s="22"/>
       <c r="Q3" s="23"/>
     </row>
     <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="22"/>
@@ -10173,7 +10230,7 @@
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="K4" s="22"/>
@@ -10186,7 +10243,7 @@
     </row>
     <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="22"/>
@@ -10196,7 +10253,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="22"/>
@@ -10209,8 +10266,8 @@
     </row>
     <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="45" t="s">
-        <v>162</v>
+      <c r="B6" s="39" t="s">
+        <v>158</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -10219,8 +10276,8 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="35" t="s">
-        <v>166</v>
+      <c r="J6" s="32" t="s">
+        <v>164</v>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
@@ -10232,24 +10289,24 @@
     </row>
     <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="22"/>
@@ -10262,7 +10319,7 @@
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="22"/>
@@ -10278,7 +10335,7 @@
       <c r="L8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="39"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
@@ -10289,8 +10346,8 @@
       <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>137</v>
+      <c r="C9" s="26" t="s">
+        <v>139</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
@@ -10305,7 +10362,7 @@
       <c r="L9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="39"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
@@ -10316,8 +10373,8 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>138</v>
+      <c r="C10" s="25" t="s">
+        <v>140</v>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
@@ -10332,7 +10389,7 @@
       <c r="L10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
@@ -10343,8 +10400,8 @@
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>129</v>
+      <c r="C11" s="26" t="s">
+        <v>141</v>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
@@ -10359,7 +10416,7 @@
       <c r="L11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="39"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
@@ -10370,8 +10427,8 @@
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>139</v>
+      <c r="C12" s="25" t="s">
+        <v>142</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
@@ -10386,7 +10443,7 @@
       <c r="L12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="39"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
@@ -10397,8 +10454,8 @@
       <c r="B13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>140</v>
+      <c r="C13" s="26" t="s">
+        <v>143</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
@@ -10413,7 +10470,7 @@
       <c r="L13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
@@ -10424,7 +10481,7 @@
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" s="25" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="22"/>
@@ -10440,7 +10497,7 @@
       <c r="L14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="39"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
@@ -10451,8 +10508,8 @@
       <c r="B15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>132</v>
+      <c r="C15" s="26" t="s">
+        <v>144</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="22"/>
@@ -10467,7 +10524,7 @@
       <c r="L15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="39"/>
+      <c r="M15" s="24"/>
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
@@ -10475,24 +10532,24 @@
     </row>
     <row r="16" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="38"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="29"/>
       <c r="K16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="41" t="s">
+      <c r="M16" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N16" s="22"/>
@@ -10505,7 +10562,7 @@
       <c r="B17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="25" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="22"/>
@@ -10521,7 +10578,7 @@
       <c r="L17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M17" s="39"/>
+      <c r="M17" s="24"/>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
       <c r="P17" s="22"/>
@@ -10532,7 +10589,7 @@
       <c r="B18" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="26" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="22"/>
@@ -10548,7 +10605,7 @@
       <c r="L18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="39"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
@@ -10559,7 +10616,7 @@
       <c r="B19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="25" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="22"/>
@@ -10575,7 +10632,7 @@
       <c r="L19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
@@ -10586,8 +10643,8 @@
       <c r="B20" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>133</v>
+      <c r="C20" s="26" t="s">
+        <v>145</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -10602,7 +10659,7 @@
       <c r="L20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M20" s="39"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
@@ -10613,7 +10670,7 @@
       <c r="B21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="25" t="s">
         <v>45</v>
       </c>
       <c r="D21" s="22"/>
@@ -10629,7 +10686,7 @@
       <c r="L21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="39"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
@@ -10640,7 +10697,7 @@
       <c r="B22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D22" s="22"/>
@@ -10656,7 +10713,7 @@
       <c r="L22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M22" s="39"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
@@ -10664,24 +10721,24 @@
     </row>
     <row r="23" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="38"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="29"/>
       <c r="K23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="41" t="s">
+      <c r="M23" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N23" s="22"/>
@@ -10694,7 +10751,7 @@
       <c r="B24" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="25" t="s">
         <v>52</v>
       </c>
       <c r="D24" s="22"/>
@@ -10710,7 +10767,7 @@
       <c r="L24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -10721,8 +10778,8 @@
       <c r="B25" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>135</v>
+      <c r="C25" s="26" t="s">
+        <v>54</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -10737,7 +10794,7 @@
       <c r="L25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M25" s="39"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
@@ -10748,8 +10805,8 @@
       <c r="B26" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="34" t="s">
-        <v>92</v>
+      <c r="C26" s="25" t="s">
+        <v>89</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -10764,7 +10821,7 @@
       <c r="L26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="39"/>
+      <c r="M26" s="24"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
@@ -10775,7 +10832,7 @@
       <c r="B27" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="26" t="s">
         <v>60</v>
       </c>
       <c r="D27" s="22"/>
@@ -10791,7 +10848,7 @@
       <c r="L27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="39"/>
+      <c r="M27" s="24"/>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
@@ -10799,7 +10856,7 @@
     </row>
     <row r="28" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="21" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="22"/>
@@ -10813,7 +10870,7 @@
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
       <c r="M28" s="23"/>
-      <c r="N28" s="21" t="s">
+      <c r="N28" s="33" t="s">
         <v>62</v>
       </c>
       <c r="O28" s="22"/>
@@ -10916,70 +10973,76 @@
     </row>
     <row r="31" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
-      <c r="B31" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="I31" s="25"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="25"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="26"/>
+      <c r="B31" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
     </row>
     <row r="32" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="29"/>
+      <c r="B32" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="70"/>
     </row>
     <row r="33" spans="2:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="32"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="K31:Q33"/>
+  <mergeCells count="60">
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="B32:G33"/>
+    <mergeCell ref="K32:Q33"/>
     <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="B31:G33"/>
     <mergeCell ref="M14:Q14"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="C13:J13"/>
@@ -11042,8 +11105,8 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:Q33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" customWidth="1"/>
@@ -11053,7 +11116,7 @@
     <row r="1" spans="1:17" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:17" ht="56.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="22"/>
@@ -11068,17 +11131,17 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
-      <c r="O2" s="43"/>
+      <c r="O2" s="35"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="23"/>
     </row>
     <row r="3" spans="1:17" ht="97.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="44"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="22"/>
       <c r="D3" s="23"/>
-      <c r="E3" s="46" t="s">
-        <v>141</v>
+      <c r="E3" s="34" t="s">
+        <v>146</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
@@ -11089,13 +11152,13 @@
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="23"/>
-      <c r="O3" s="43"/>
+      <c r="O3" s="35"/>
       <c r="P3" s="22"/>
       <c r="Q3" s="23"/>
     </row>
     <row r="4" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="22"/>
@@ -11105,7 +11168,7 @@
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="K4" s="22"/>
@@ -11118,7 +11181,7 @@
     </row>
     <row r="5" spans="1:17" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="22"/>
@@ -11128,7 +11191,7 @@
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="32" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="22"/>
@@ -11141,8 +11204,8 @@
     </row>
     <row r="6" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="45" t="s">
-        <v>161</v>
+      <c r="B6" s="39" t="s">
+        <v>154</v>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="22"/>
@@ -11151,8 +11214,8 @@
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="35" t="s">
-        <v>167</v>
+      <c r="J6" s="32" t="s">
+        <v>165</v>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
@@ -11164,24 +11227,24 @@
     </row>
     <row r="7" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
       <c r="K7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="36" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="22"/>
@@ -11194,7 +11257,7 @@
       <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="25" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="22"/>
@@ -11210,7 +11273,7 @@
       <c r="L8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="39"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
@@ -11221,8 +11284,8 @@
       <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>142</v>
+      <c r="C9" s="26" t="s">
+        <v>147</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
@@ -11237,7 +11300,7 @@
       <c r="L9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M9" s="39"/>
+      <c r="M9" s="24"/>
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
@@ -11248,8 +11311,8 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>143</v>
+      <c r="C10" s="25" t="s">
+        <v>148</v>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
@@ -11264,7 +11327,7 @@
       <c r="L10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M10" s="39"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
@@ -11275,8 +11338,8 @@
       <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>144</v>
+      <c r="C11" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
@@ -11291,7 +11354,7 @@
       <c r="L11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="39"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
@@ -11302,8 +11365,8 @@
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>145</v>
+      <c r="C12" s="25" t="s">
+        <v>150</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
@@ -11318,7 +11381,7 @@
       <c r="L12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M12" s="39"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
@@ -11329,8 +11392,8 @@
       <c r="B13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>146</v>
+      <c r="C13" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22"/>
@@ -11345,7 +11408,7 @@
       <c r="L13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="22"/>
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
@@ -11356,8 +11419,8 @@
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="34" t="s">
-        <v>26</v>
+      <c r="C14" s="25" t="s">
+        <v>144</v>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
@@ -11372,7 +11435,7 @@
       <c r="L14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="39"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
@@ -11380,26 +11443,26 @@
     </row>
     <row r="15" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11"/>
-      <c r="B15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M15" s="39"/>
+      <c r="B15" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="36" t="s">
+        <v>9</v>
+      </c>
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
@@ -11407,26 +11470,26 @@
     </row>
     <row r="16" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11"/>
-      <c r="B16" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="41" t="s">
-        <v>9</v>
-      </c>
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" s="24"/>
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
@@ -11434,11 +11497,11 @@
     </row>
     <row r="17" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="34" t="s">
-        <v>31</v>
+      <c r="C17" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
@@ -11453,7 +11516,7 @@
       <c r="L17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M17" s="39"/>
+      <c r="M17" s="24"/>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
       <c r="P17" s="22"/>
@@ -11461,11 +11524,11 @@
     </row>
     <row r="18" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="33" t="s">
-        <v>35</v>
+      <c r="C18" s="25" t="s">
+        <v>39</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -11480,7 +11543,7 @@
       <c r="L18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="39"/>
+      <c r="M18" s="24"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
@@ -11488,11 +11551,11 @@
     </row>
     <row r="19" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="34" t="s">
-        <v>39</v>
+      <c r="C19" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -11507,7 +11570,7 @@
       <c r="L19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M19" s="39"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
@@ -11515,11 +11578,11 @@
     </row>
     <row r="20" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>148</v>
+      <c r="C20" s="25" t="s">
+        <v>45</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -11534,7 +11597,7 @@
       <c r="L20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M20" s="39"/>
+      <c r="M20" s="24"/>
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
@@ -11542,11 +11605,11 @@
     </row>
     <row r="21" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="34" t="s">
-        <v>45</v>
+      <c r="C21" s="26" t="s">
+        <v>47</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -11561,7 +11624,7 @@
       <c r="L21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M21" s="39"/>
+      <c r="M21" s="24"/>
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
@@ -11569,26 +11632,26 @@
     </row>
     <row r="22" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
-      <c r="B22" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M22" s="39"/>
+      <c r="B22" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="36" t="s">
+        <v>9</v>
+      </c>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
@@ -11596,26 +11659,26 @@
     </row>
     <row r="23" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
-      <c r="B23" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="41" t="s">
-        <v>9</v>
-      </c>
+      <c r="B23" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" s="24"/>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
@@ -11623,11 +11686,11 @@
     </row>
     <row r="24" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="34" t="s">
-        <v>52</v>
+      <c r="C24" s="26" t="s">
+        <v>132</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -11642,7 +11705,7 @@
       <c r="L24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M24" s="39"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -11650,11 +11713,11 @@
     </row>
     <row r="25" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>54</v>
+      <c r="C25" s="25" t="s">
+        <v>89</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -11669,7 +11732,7 @@
       <c r="L25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M25" s="39"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
@@ -11677,11 +11740,11 @@
     </row>
     <row r="26" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="34" t="s">
-        <v>92</v>
+      <c r="C26" s="26" t="s">
+        <v>60</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -11696,7 +11759,7 @@
       <c r="L26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="39"/>
+      <c r="M26" s="24"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
@@ -11704,269 +11767,246 @@
     </row>
     <row r="27" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
-      <c r="B27" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>60</v>
-      </c>
+      <c r="B27" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="22"/>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
       <c r="I27" s="22"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M27" s="39"/>
-      <c r="N27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="33" t="s">
+        <v>62</v>
+      </c>
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
       <c r="Q27" s="23"/>
     </row>
     <row r="28" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
-      <c r="B28" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="23"/>
+      <c r="B28" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q28" s="6" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="29" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
-      <c r="B29" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="N29" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="P29" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q29" s="6" t="s">
-        <v>78</v>
-      </c>
+      <c r="B29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
     </row>
     <row r="30" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11"/>
-      <c r="B30" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
+      <c r="B30" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="71" t="s">
+        <v>173</v>
+      </c>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
     </row>
     <row r="31" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="I31" s="25"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="25"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="26"/>
+      <c r="B31" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="L31" s="70"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="70"/>
+      <c r="O31" s="70"/>
+      <c r="P31" s="70"/>
+      <c r="Q31" s="70"/>
     </row>
     <row r="32" spans="1:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="29"/>
-    </row>
-    <row r="33" spans="2:17" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="32"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="K31:Q33"/>
-    <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="B31:G33"/>
-    <mergeCell ref="M14:Q14"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="M27:Q27"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="M26:Q26"/>
-    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="B31:G32"/>
+    <mergeCell ref="K31:Q32"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="H30:J32"/>
+    <mergeCell ref="N27:Q27"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="J4:Q4"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="C8:J8"/>
-    <mergeCell ref="B16:J16"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B4:I4"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="J4:Q4"/>
-    <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="M13:Q13"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="N28:Q28"/>
-    <mergeCell ref="H31:J33"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="J5:Q5"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="M9:Q9"/>
-    <mergeCell ref="C26:J26"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="B28:M28"/>
+    <mergeCell ref="B5:I5"/>
     <mergeCell ref="C20:J20"/>
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="M11:Q11"/>
     <mergeCell ref="C25:J25"/>
     <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="M9:Q9"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="C26:J26"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="B22:J22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -1828,9 +1828,9 @@
       <c r="N2" s="13" t="n"/>
       <c r="O2" s="74" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="45" t="n"/>
@@ -3245,9 +3245,9 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="22" t="n"/>
@@ -4664,9 +4664,9 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="22" t="n"/>
@@ -5899,9 +5899,9 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="22" t="n"/>
@@ -7312,9 +7312,9 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="22" t="n"/>
@@ -8547,9 +8547,9 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="22" t="n"/>
@@ -9744,9 +9744,9 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="22" t="n"/>
@@ -10942,9 +10942,9 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="22" t="n"/>
@@ -12139,9 +12139,9 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="22" t="n"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -1828,7 +1828,7 @@
       <c r="N2" s="13" t="n"/>
       <c r="O2" s="74" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -3245,7 +3245,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -4664,7 +4664,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -5899,7 +5899,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -7312,7 +7312,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -8547,7 +8547,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -9744,7 +9744,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -10942,7 +10942,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -12139,7 +12139,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -1828,7 +1828,7 @@
       <c r="N2" s="13" t="n"/>
       <c r="O2" s="74" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F1
+          <t>No. de Documento             A9.I1.F2
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -3245,7 +3245,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F1
+          <t>No. de Documento             A9.I1.F2
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -4664,7 +4664,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F1
+          <t>No. de Documento             A9.I1.F2
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -5899,7 +5899,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F1
+          <t>No. de Documento             A9.I1.F2
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -7312,7 +7312,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F1
+          <t>No. de Documento             A9.I1.F2
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -8547,7 +8547,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F1
+          <t>No. de Documento             A9.I1.F2
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -9744,7 +9744,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F1
+          <t>No. de Documento             A9.I1.F2
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -10942,7 +10942,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F1
+          <t>No. de Documento             A9.I1.F2
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -12139,7 +12139,7 @@
       <c r="N2" s="23" t="n"/>
       <c r="O2" s="81" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F1
+          <t>No. de Documento             A9.I1.F2
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -5870,7 +5870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Q39"/>
+  <dimension ref="A2:Q41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
@@ -6901,252 +6901,267 @@
       <c r="Q33" s="46" t="n"/>
     </row>
     <row r="34" ht="17.4" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>CALENDARIO  DE  MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="C34" s="22" t="n"/>
+      <c r="B34" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>Verificación de continuidad en fusibles</t>
+        </is>
+      </c>
       <c r="D34" s="22" t="n"/>
       <c r="E34" s="22" t="n"/>
       <c r="F34" s="22" t="n"/>
       <c r="G34" s="22" t="n"/>
-      <c r="H34" s="22" t="n"/>
-      <c r="I34" s="22" t="n"/>
-      <c r="J34" s="22" t="n"/>
-      <c r="K34" s="22" t="n"/>
-      <c r="L34" s="22" t="n"/>
-      <c r="M34" s="23" t="n"/>
-      <c r="N34" s="33" t="inlineStr">
-        <is>
-          <t>VOLTAJE ALIMENTACIÓN</t>
-        </is>
-      </c>
-      <c r="O34" s="22" t="n"/>
-      <c r="P34" s="22" t="n"/>
-      <c r="Q34" s="23" t="n"/>
     </row>
     <row r="35" ht="17.4" customHeight="1">
       <c r="A35" s="11" t="n"/>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>ENE</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>FEB</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>ABR</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>DIC</t>
-        </is>
-      </c>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>VAC</t>
-        </is>
-      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>CALENDARIO  DE  MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="22" t="n"/>
+      <c r="K35" s="22" t="n"/>
+      <c r="L35" s="22" t="n"/>
+      <c r="M35" s="23" t="n"/>
+      <c r="N35" s="33" t="inlineStr">
+        <is>
+          <t>VOLTAJE ALIMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="O35" s="22" t="n"/>
+      <c r="P35" s="22" t="n"/>
+      <c r="Q35" s="23" t="n"/>
     </row>
     <row r="36" ht="17.4" customHeight="1">
       <c r="A36" s="11" t="n"/>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="n"/>
-      <c r="O36" s="6" t="n"/>
-      <c r="P36" s="6" t="n"/>
-      <c r="Q36" s="6" t="n"/>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>ABR</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>VAC</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="11" t="n"/>
-      <c r="B37" s="70" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="n"/>
+      <c r="Q37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="14.4" customHeight="1">
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C37" s="45" t="n"/>
-      <c r="D37" s="45" t="n"/>
-      <c r="E37" s="45" t="n"/>
-      <c r="F37" s="45" t="n"/>
-      <c r="G37" s="46" t="n"/>
-      <c r="H37" s="71" t="inlineStr">
+      <c r="C38" s="45" t="n"/>
+      <c r="D38" s="45" t="n"/>
+      <c r="E38" s="45" t="n"/>
+      <c r="F38" s="45" t="n"/>
+      <c r="G38" s="46" t="n"/>
+      <c r="H38" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
-      <c r="I37" s="75" t="n"/>
-      <c r="J37" s="75" t="n"/>
-      <c r="K37" s="72" t="inlineStr">
+      <c r="I38" s="75" t="n"/>
+      <c r="J38" s="75" t="n"/>
+      <c r="K38" s="72" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L37" s="45" t="n"/>
-      <c r="M37" s="45" t="n"/>
-      <c r="N37" s="45" t="n"/>
-      <c r="O37" s="45" t="n"/>
-      <c r="P37" s="45" t="n"/>
-      <c r="Q37" s="46" t="n"/>
-    </row>
-    <row r="38" ht="14.4" customHeight="1">
-      <c r="B38" s="70" t="inlineStr">
+      <c r="L38" s="45" t="n"/>
+      <c r="M38" s="45" t="n"/>
+      <c r="N38" s="45" t="n"/>
+      <c r="O38" s="45" t="n"/>
+      <c r="P38" s="45" t="n"/>
+      <c r="Q38" s="46" t="n"/>
+    </row>
+    <row r="39" ht="14.4" customHeight="1">
+      <c r="B39" s="70" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="C38" s="76" t="n"/>
-      <c r="D38" s="76" t="n"/>
-      <c r="E38" s="76" t="n"/>
-      <c r="F38" s="76" t="n"/>
-      <c r="G38" s="77" t="n"/>
-      <c r="K38" s="70" t="inlineStr">
+      <c r="C39" s="76" t="n"/>
+      <c r="D39" s="76" t="n"/>
+      <c r="E39" s="76" t="n"/>
+      <c r="F39" s="76" t="n"/>
+      <c r="G39" s="77" t="n"/>
+      <c r="K39" s="70" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="L38" s="76" t="n"/>
-      <c r="M38" s="76" t="n"/>
-      <c r="N38" s="76" t="n"/>
-      <c r="O38" s="76" t="n"/>
-      <c r="P38" s="76" t="n"/>
-      <c r="Q38" s="77" t="n"/>
-    </row>
-    <row r="39" ht="14.4" customHeight="1">
-      <c r="B39" s="78" t="n"/>
-      <c r="C39" s="79" t="n"/>
-      <c r="D39" s="79" t="n"/>
-      <c r="E39" s="79" t="n"/>
-      <c r="F39" s="79" t="n"/>
-      <c r="G39" s="80" t="n"/>
-      <c r="K39" s="78" t="n"/>
-      <c r="L39" s="79" t="n"/>
-      <c r="M39" s="79" t="n"/>
-      <c r="N39" s="79" t="n"/>
-      <c r="O39" s="79" t="n"/>
-      <c r="P39" s="79" t="n"/>
-      <c r="Q39" s="80" t="n"/>
-    </row>
+      <c r="L39" s="76" t="n"/>
+      <c r="M39" s="76" t="n"/>
+      <c r="N39" s="76" t="n"/>
+      <c r="O39" s="76" t="n"/>
+      <c r="P39" s="76" t="n"/>
+      <c r="Q39" s="77" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="78" t="n"/>
+      <c r="C40" s="79" t="n"/>
+      <c r="D40" s="79" t="n"/>
+      <c r="E40" s="79" t="n"/>
+      <c r="F40" s="79" t="n"/>
+      <c r="G40" s="80" t="n"/>
+      <c r="K40" s="78" t="n"/>
+      <c r="L40" s="79" t="n"/>
+      <c r="M40" s="79" t="n"/>
+      <c r="N40" s="79" t="n"/>
+      <c r="O40" s="79" t="n"/>
+      <c r="P40" s="79" t="n"/>
+      <c r="Q40" s="80" t="n"/>
+    </row>
+    <row r="41"/>
   </sheetData>
   <mergeCells count="72">
     <mergeCell ref="C30:J30"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -186,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -449,11 +449,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -652,6 +672,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5870,7 +5892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Q41"/>
+  <dimension ref="A2:Q40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
@@ -6343,16 +6365,10 @@
       <c r="P16" s="22" t="n"/>
       <c r="Q16" s="23" t="n"/>
     </row>
-    <row r="17" ht="25.05" customHeight="1">
+    <row r="17" customHeight="1">
       <c r="A17" s="11" t="n"/>
-      <c r="B17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>Limpieza de residuos de material en zonas de corte y transporte</t>
-        </is>
-      </c>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="25" t="n"/>
       <c r="D17" s="22" t="n"/>
       <c r="E17" s="22" t="n"/>
       <c r="F17" s="22" t="n"/>
@@ -6900,19 +6916,25 @@
       <c r="P33" s="45" t="n"/>
       <c r="Q33" s="46" t="n"/>
     </row>
-    <row r="34" ht="17.4" customHeight="1">
+    <row r="34" ht="25.05" customHeight="1">
       <c r="B34" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="C34" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de continuidad en fusibles</t>
-        </is>
-      </c>
+      <c r="C34" s="25" t="n"/>
       <c r="D34" s="22" t="n"/>
       <c r="E34" s="22" t="n"/>
       <c r="F34" s="22" t="n"/>
       <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="61" t="n"/>
+      <c r="N34" s="22" t="n"/>
+      <c r="O34" s="22" t="n"/>
+      <c r="P34" s="22" t="n"/>
+      <c r="Q34" s="23" t="n"/>
     </row>
     <row r="35" ht="17.4" customHeight="1">
       <c r="A35" s="11" t="n"/>
@@ -7031,65 +7053,29 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="23" t="n"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
           <t>(   )</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
+      <c r="I37" s="82" t="n"/>
+      <c r="J37" s="83" t="n"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
           <t>(   )</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="N37" s="6" t="n"/>
-      <c r="O37" s="6" t="n"/>
-      <c r="P37" s="6" t="n"/>
-      <c r="Q37" s="6" t="n"/>
+      <c r="L37" s="22" t="n"/>
+      <c r="M37" s="22" t="n"/>
+      <c r="N37" s="22" t="n"/>
+      <c r="O37" s="22" t="n"/>
+      <c r="P37" s="22" t="n"/>
+      <c r="Q37" s="23" t="n"/>
     </row>
     <row r="38" ht="14.4" customHeight="1">
       <c r="A38" s="11" t="n"/>
@@ -7098,53 +7084,43 @@
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C38" s="45" t="n"/>
-      <c r="D38" s="45" t="n"/>
-      <c r="E38" s="45" t="n"/>
-      <c r="F38" s="45" t="n"/>
-      <c r="G38" s="46" t="n"/>
-      <c r="H38" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fecha: </t>
-        </is>
-      </c>
-      <c r="I38" s="75" t="n"/>
-      <c r="J38" s="75" t="n"/>
+      <c r="C38" s="76" t="n"/>
+      <c r="D38" s="76" t="n"/>
+      <c r="E38" s="76" t="n"/>
+      <c r="F38" s="76" t="n"/>
+      <c r="G38" s="77" t="n"/>
+      <c r="H38" s="84" t="n"/>
+      <c r="J38" s="11" t="n"/>
       <c r="K38" s="72" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L38" s="45" t="n"/>
-      <c r="M38" s="45" t="n"/>
-      <c r="N38" s="45" t="n"/>
-      <c r="O38" s="45" t="n"/>
-      <c r="P38" s="45" t="n"/>
-      <c r="Q38" s="46" t="n"/>
+      <c r="L38" s="76" t="n"/>
+      <c r="M38" s="76" t="n"/>
+      <c r="N38" s="76" t="n"/>
+      <c r="O38" s="76" t="n"/>
+      <c r="P38" s="76" t="n"/>
+      <c r="Q38" s="77" t="n"/>
     </row>
     <row r="39" ht="14.4" customHeight="1">
-      <c r="B39" s="70" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="C39" s="76" t="n"/>
-      <c r="D39" s="76" t="n"/>
-      <c r="E39" s="76" t="n"/>
-      <c r="F39" s="76" t="n"/>
-      <c r="G39" s="77" t="n"/>
-      <c r="K39" s="70" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="L39" s="76" t="n"/>
-      <c r="M39" s="76" t="n"/>
-      <c r="N39" s="76" t="n"/>
-      <c r="O39" s="76" t="n"/>
-      <c r="P39" s="76" t="n"/>
-      <c r="Q39" s="77" t="n"/>
+      <c r="B39" s="78" t="n"/>
+      <c r="C39" s="79" t="n"/>
+      <c r="D39" s="79" t="n"/>
+      <c r="E39" s="79" t="n"/>
+      <c r="F39" s="79" t="n"/>
+      <c r="G39" s="80" t="n"/>
+      <c r="H39" s="85" t="n"/>
+      <c r="I39" s="30" t="n"/>
+      <c r="J39" s="31" t="n"/>
+      <c r="K39" s="78" t="n"/>
+      <c r="L39" s="79" t="n"/>
+      <c r="M39" s="79" t="n"/>
+      <c r="N39" s="79" t="n"/>
+      <c r="O39" s="79" t="n"/>
+      <c r="P39" s="79" t="n"/>
+      <c r="Q39" s="80" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="78" t="n"/>
@@ -7161,19 +7137,18 @@
       <c r="P40" s="79" t="n"/>
       <c r="Q40" s="80" t="n"/>
     </row>
-    <row r="41"/>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="M34:Q34"/>
     <mergeCell ref="C30:J30"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C33:J33"/>
     <mergeCell ref="C24:J24"/>
     <mergeCell ref="J5:Q5"/>
-    <mergeCell ref="N34:Q34"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="M9:Q9"/>
     <mergeCell ref="K37:Q37"/>
-    <mergeCell ref="B34:M34"/>
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="M20:Q20"/>
     <mergeCell ref="C29:J29"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -186,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -449,31 +449,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -672,8 +652,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5892,7 +5870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Q40"/>
+  <dimension ref="A2:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
@@ -6365,10 +6343,16 @@
       <c r="P16" s="22" t="n"/>
       <c r="Q16" s="23" t="n"/>
     </row>
-    <row r="17" customHeight="1">
+    <row r="17" ht="25.05" customHeight="1">
       <c r="A17" s="11" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="25" t="n"/>
+      <c r="B17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>Verificación de continuidad en fusibles</t>
+        </is>
+      </c>
       <c r="D17" s="22" t="n"/>
       <c r="E17" s="22" t="n"/>
       <c r="F17" s="22" t="n"/>
@@ -6916,11 +6900,14 @@
       <c r="P33" s="45" t="n"/>
       <c r="Q33" s="46" t="n"/>
     </row>
-    <row r="34" ht="25.05" customHeight="1">
-      <c r="B34" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="C34" s="25" t="n"/>
+    <row r="34" ht="17.4" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>CALENDARIO  DE  MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="n"/>
       <c r="D34" s="22" t="n"/>
       <c r="E34" s="22" t="n"/>
       <c r="F34" s="22" t="n"/>
@@ -6928,160 +6915,212 @@
       <c r="H34" s="22" t="n"/>
       <c r="I34" s="22" t="n"/>
       <c r="J34" s="22" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="14" t="n"/>
-      <c r="M34" s="61" t="n"/>
-      <c r="N34" s="22" t="n"/>
+      <c r="K34" s="22" t="n"/>
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="23" t="n"/>
+      <c r="N34" s="33" t="inlineStr">
+        <is>
+          <t>VOLTAJE ALIMENTACIÓN</t>
+        </is>
+      </c>
       <c r="O34" s="22" t="n"/>
       <c r="P34" s="22" t="n"/>
       <c r="Q34" s="23" t="n"/>
     </row>
     <row r="35" ht="17.4" customHeight="1">
       <c r="A35" s="11" t="n"/>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>CALENDARIO  DE  MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="22" t="n"/>
-      <c r="F35" s="22" t="n"/>
-      <c r="G35" s="22" t="n"/>
-      <c r="H35" s="22" t="n"/>
-      <c r="I35" s="22" t="n"/>
-      <c r="J35" s="22" t="n"/>
-      <c r="K35" s="22" t="n"/>
-      <c r="L35" s="22" t="n"/>
-      <c r="M35" s="23" t="n"/>
-      <c r="N35" s="33" t="inlineStr">
-        <is>
-          <t>VOLTAJE ALIMENTACIÓN</t>
-        </is>
-      </c>
-      <c r="O35" s="22" t="n"/>
-      <c r="P35" s="22" t="n"/>
-      <c r="Q35" s="23" t="n"/>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>ABR</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>VAC</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17.4" customHeight="1">
       <c r="A36" s="11" t="n"/>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>ENE</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>FEB</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>ABR</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>DIC</t>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
         </is>
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O36" s="6" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
+          <t>Entrada 220VAC</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="n"/>
+      <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>VAC</t>
+          <t>Salida 24VDC</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="11" t="n"/>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="22" t="n"/>
-      <c r="F37" s="22" t="n"/>
-      <c r="G37" s="23" t="n"/>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="I37" s="82" t="n"/>
-      <c r="J37" s="83" t="n"/>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L37" s="22" t="n"/>
-      <c r="M37" s="22" t="n"/>
-      <c r="N37" s="22" t="n"/>
-      <c r="O37" s="22" t="n"/>
-      <c r="P37" s="22" t="n"/>
-      <c r="Q37" s="23" t="n"/>
+      <c r="B37" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Realizo: </t>
+        </is>
+      </c>
+      <c r="C37" s="45" t="n"/>
+      <c r="D37" s="45" t="n"/>
+      <c r="E37" s="45" t="n"/>
+      <c r="F37" s="45" t="n"/>
+      <c r="G37" s="46" t="n"/>
+      <c r="H37" s="71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha: </t>
+        </is>
+      </c>
+      <c r="I37" s="75" t="n"/>
+      <c r="J37" s="75" t="n"/>
+      <c r="K37" s="72" t="inlineStr">
+        <is>
+          <t>Supervisor de Producción: 
+Firma: _____________________________</t>
+        </is>
+      </c>
+      <c r="L37" s="45" t="n"/>
+      <c r="M37" s="45" t="n"/>
+      <c r="N37" s="45" t="n"/>
+      <c r="O37" s="45" t="n"/>
+      <c r="P37" s="45" t="n"/>
+      <c r="Q37" s="46" t="n"/>
     </row>
     <row r="38" ht="14.4" customHeight="1">
-      <c r="A38" s="11" t="n"/>
       <c r="B38" s="70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Realizo: </t>
+          <t>Firma:</t>
         </is>
       </c>
       <c r="C38" s="76" t="n"/>
@@ -7089,12 +7128,9 @@
       <c r="E38" s="76" t="n"/>
       <c r="F38" s="76" t="n"/>
       <c r="G38" s="77" t="n"/>
-      <c r="H38" s="84" t="n"/>
-      <c r="J38" s="11" t="n"/>
-      <c r="K38" s="72" t="inlineStr">
-        <is>
-          <t>Supervisor de Producción: 
-Firma: _____________________________</t>
+      <c r="K38" s="70" t="inlineStr">
+        <is>
+          <t>Firma:</t>
         </is>
       </c>
       <c r="L38" s="76" t="n"/>
@@ -7111,9 +7147,6 @@
       <c r="E39" s="79" t="n"/>
       <c r="F39" s="79" t="n"/>
       <c r="G39" s="80" t="n"/>
-      <c r="H39" s="85" t="n"/>
-      <c r="I39" s="30" t="n"/>
-      <c r="J39" s="31" t="n"/>
       <c r="K39" s="78" t="n"/>
       <c r="L39" s="79" t="n"/>
       <c r="M39" s="79" t="n"/>
@@ -7122,33 +7155,18 @@
       <c r="P39" s="79" t="n"/>
       <c r="Q39" s="80" t="n"/>
     </row>
-    <row r="40">
-      <c r="B40" s="78" t="n"/>
-      <c r="C40" s="79" t="n"/>
-      <c r="D40" s="79" t="n"/>
-      <c r="E40" s="79" t="n"/>
-      <c r="F40" s="79" t="n"/>
-      <c r="G40" s="80" t="n"/>
-      <c r="K40" s="78" t="n"/>
-      <c r="L40" s="79" t="n"/>
-      <c r="M40" s="79" t="n"/>
-      <c r="N40" s="79" t="n"/>
-      <c r="O40" s="79" t="n"/>
-      <c r="P40" s="79" t="n"/>
-      <c r="Q40" s="80" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="C34:J34"/>
-    <mergeCell ref="M34:Q34"/>
     <mergeCell ref="C30:J30"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C33:J33"/>
     <mergeCell ref="C24:J24"/>
     <mergeCell ref="J5:Q5"/>
+    <mergeCell ref="N34:Q34"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="M9:Q9"/>
     <mergeCell ref="K37:Q37"/>
+    <mergeCell ref="B34:M34"/>
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="M20:Q20"/>
     <mergeCell ref="C29:J29"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -7077,13 +7077,13 @@
           <t>Entrada 220VAC</t>
         </is>
       </c>
-      <c r="O36" s="6" t="n"/>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>Salida 24VDC</t>
+        </is>
+      </c>
       <c r="P36" s="6" t="n"/>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>Salida 24VDC</t>
-        </is>
-      </c>
+      <c r="Q36" s="6" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="11" t="n"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -6991,24 +6991,16 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L1-L2</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>VAC</t>
-        </is>
-      </c>
+          <t>VDC</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="n"/>
+      <c r="Q35" s="6" t="n"/>
     </row>
     <row r="36" ht="17.4" customHeight="1">
       <c r="A36" s="11" t="n"/>
@@ -7072,16 +7064,8 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="N36" s="6" t="inlineStr">
-        <is>
-          <t>Entrada 220VAC</t>
-        </is>
-      </c>
-      <c r="O36" s="6" t="inlineStr">
-        <is>
-          <t>Salida 24VDC</t>
-        </is>
-      </c>
+      <c r="N36" s="6" t="n"/>
+      <c r="O36" s="6" t="n"/>
       <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="n"/>
     </row>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -453,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -652,6 +652,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6510,7 +6513,7 @@
       <c r="P21" s="22" t="n"/>
       <c r="Q21" s="23" t="n"/>
     </row>
-    <row r="22" ht="25.05" customHeight="1">
+    <row r="22" hidden="1" ht="25.05" customHeight="1">
       <c r="A22" s="11" t="n"/>
       <c r="B22" s="8" t="n">
         <v>14</v>
@@ -6609,7 +6612,7 @@
       <c r="P24" s="22" t="n"/>
       <c r="Q24" s="23" t="n"/>
     </row>
-    <row r="25" ht="25.05" customHeight="1">
+    <row r="25" hidden="1" ht="25.05" customHeight="1">
       <c r="A25" s="11" t="n"/>
       <c r="B25" s="8" t="n">
         <v>17</v>
@@ -7081,7 +7084,7 @@
       <c r="E37" s="45" t="n"/>
       <c r="F37" s="45" t="n"/>
       <c r="G37" s="46" t="n"/>
-      <c r="H37" s="71" t="inlineStr">
+      <c r="H37" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -12,9 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rotary Press" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prensa PL" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMESA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single Knife" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hojeadora Robust" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gapcutter" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calender K1 Easy" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single Knife" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hojeadora Robust" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gapcutter" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,11 +122,39 @@
       <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="001A5C2A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
       <name val="Calibri"/>
-      <sz val="9"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -185,8 +214,28 @@
         <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A5C2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAD8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -449,11 +498,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -511,19 +574,22 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -534,25 +600,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -560,21 +621,43 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -584,11 +667,9 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -601,9 +682,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -615,31 +693,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -647,13 +710,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1829,53 +1931,53 @@
       <c r="L2" s="13" t="n"/>
       <c r="M2" s="13" t="n"/>
       <c r="N2" s="13" t="n"/>
-      <c r="O2" s="74" t="inlineStr">
-        <is>
-          <t>No. de Documento             A9.I1.F2
-Revision:                                    00
-Fecha:                        08/06/2026</t>
-        </is>
-      </c>
-      <c r="P2" s="45" t="n"/>
-      <c r="Q2" s="46" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
-      <c r="B3" s="44" t="n"/>
-      <c r="C3" s="45" t="n"/>
-      <c r="D3" s="46" t="n"/>
-      <c r="E3" s="41" t="inlineStr">
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="51" t="n"/>
+      <c r="E3" s="44" t="inlineStr">
         <is>
           <t>MANTENIMIENTO PREVENTIVO   —   LAMINATOR MACHINERY – LAMINADORA</t>
         </is>
       </c>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="42" t="n"/>
-      <c r="O3" s="44" t="n"/>
-      <c r="P3" s="45" t="n"/>
-      <c r="Q3" s="46" t="n"/>
+      <c r="F3" s="45" t="n"/>
+      <c r="G3" s="45" t="n"/>
+      <c r="H3" s="45" t="n"/>
+      <c r="I3" s="45" t="n"/>
+      <c r="J3" s="45" t="n"/>
+      <c r="K3" s="45" t="n"/>
+      <c r="L3" s="45" t="n"/>
+      <c r="M3" s="45" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="49" t="n"/>
+      <c r="P3" s="50" t="n"/>
+      <c r="Q3" s="51" t="n"/>
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
       </c>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="31" t="n"/>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+      <c r="I4" s="48" t="n"/>
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
@@ -1890,7 +1992,7 @@
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
@@ -1902,7 +2004,7 @@
       <c r="G5" s="22" t="n"/>
       <c r="H5" s="22" t="n"/>
       <c r="I5" s="23" t="n"/>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
@@ -1917,7 +2019,7 @@
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Nombre de máquina:  Laminadora</t>
         </is>
@@ -1929,7 +2031,7 @@
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="23" t="n"/>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Número de máquina:  LM01</t>
         </is>
@@ -1944,7 +2046,7 @@
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO</t>
         </is>
@@ -1962,12 +2064,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -1984,7 +2086,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Inspección visual: ruidos, vibraciones y fugas</t>
         </is>
@@ -2006,7 +2108,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M8" s="24" t="n"/>
+      <c r="M8" s="21" t="n"/>
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="22" t="n"/>
@@ -2019,7 +2121,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Lubricación de rodillos laminadores y guías</t>
         </is>
@@ -2041,7 +2143,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M9" s="24" t="n"/>
+      <c r="M9" s="21" t="n"/>
       <c r="N9" s="22" t="n"/>
       <c r="O9" s="22" t="n"/>
       <c r="P9" s="22" t="n"/>
@@ -2054,7 +2156,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Revisión y ajuste de presión entre rodillos</t>
         </is>
@@ -2076,7 +2178,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M10" s="24" t="n"/>
+      <c r="M10" s="21" t="n"/>
       <c r="N10" s="22" t="n"/>
       <c r="O10" s="22" t="n"/>
       <c r="P10" s="22" t="n"/>
@@ -2089,7 +2191,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Inspección de rodillos (desgaste y paralelismo)</t>
         </is>
@@ -2111,7 +2213,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M11" s="24" t="n"/>
+      <c r="M11" s="21" t="n"/>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="22" t="n"/>
       <c r="P11" s="22" t="n"/>
@@ -2124,7 +2226,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Revisión de sistema de tensión de película/sustrato</t>
         </is>
@@ -2146,7 +2248,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M12" s="24" t="n"/>
+      <c r="M12" s="21" t="n"/>
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
       <c r="P12" s="22" t="n"/>
@@ -2159,7 +2261,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Verificación de unidad de desenrollado y rebobinado</t>
         </is>
@@ -2181,7 +2283,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M13" s="24" t="n"/>
+      <c r="M13" s="21" t="n"/>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="22" t="n"/>
       <c r="P13" s="22" t="n"/>
@@ -2194,7 +2296,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Revisión de correas y cadenas de transmisión</t>
         </is>
@@ -2216,7 +2318,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M14" s="24" t="n"/>
+      <c r="M14" s="21" t="n"/>
       <c r="N14" s="22" t="n"/>
       <c r="O14" s="22" t="n"/>
       <c r="P14" s="22" t="n"/>
@@ -2229,7 +2331,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Verificación de tornillería y fijaciones estructurales</t>
         </is>
@@ -2251,7 +2353,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M15" s="24" t="n"/>
+      <c r="M15" s="21" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
       <c r="P15" s="22" t="n"/>
@@ -2264,7 +2366,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
@@ -2286,7 +2388,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M16" s="24" t="n"/>
+      <c r="M16" s="21" t="n"/>
       <c r="N16" s="22" t="n"/>
       <c r="O16" s="22" t="n"/>
       <c r="P16" s="22" t="n"/>
@@ -2294,7 +2396,7 @@
     </row>
     <row r="17" ht="25.05" customHeight="1">
       <c r="A17" s="11" t="n"/>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
@@ -2312,12 +2414,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L17" s="36" t="inlineStr">
+      <c r="L17" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M17" s="36" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -2334,7 +2436,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Verificación visual del tablero (alarmas e indicadores)</t>
         </is>
@@ -2356,7 +2458,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n"/>
+      <c r="M18" s="21" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
       <c r="P18" s="22" t="n"/>
@@ -2369,7 +2471,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>Limpieza de tableros eléctricos y revisión de cableado</t>
         </is>
@@ -2391,7 +2493,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n"/>
+      <c r="M19" s="21" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
       <c r="P19" s="22" t="n"/>
@@ -2404,7 +2506,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Reapriete de terminales en tablero eléctrico</t>
         </is>
@@ -2426,7 +2528,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n"/>
+      <c r="M20" s="21" t="n"/>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
@@ -2439,7 +2541,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>Verificación de fusibles, contactores y relés térmicos</t>
         </is>
@@ -2461,7 +2563,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M21" s="24" t="n"/>
+      <c r="M21" s="21" t="n"/>
       <c r="N21" s="22" t="n"/>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="22" t="n"/>
@@ -2474,7 +2576,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Revisión de motores (temperatura, ruido y vibración)</t>
         </is>
@@ -2496,7 +2598,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M22" s="24" t="n"/>
+      <c r="M22" s="21" t="n"/>
       <c r="N22" s="22" t="n"/>
       <c r="O22" s="22" t="n"/>
       <c r="P22" s="22" t="n"/>
@@ -2509,7 +2611,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>Revisión de sensores y fotoceldas de detección</t>
         </is>
@@ -2531,7 +2633,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M23" s="24" t="n"/>
+      <c r="M23" s="21" t="n"/>
       <c r="N23" s="22" t="n"/>
       <c r="O23" s="22" t="n"/>
       <c r="P23" s="22" t="n"/>
@@ -2544,7 +2646,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Revisión de variadores de frecuencia</t>
         </is>
@@ -2566,7 +2668,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
+      <c r="M24" s="21" t="n"/>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
       <c r="P24" s="22" t="n"/>
@@ -2579,7 +2681,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>Prueba funcional de paros de emergencia</t>
         </is>
@@ -2601,7 +2703,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M25" s="24" t="n"/>
+      <c r="M25" s="21" t="n"/>
       <c r="N25" s="22" t="n"/>
       <c r="O25" s="22" t="n"/>
       <c r="P25" s="22" t="n"/>
@@ -2614,7 +2716,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Verificación de tierras físicas y continuidad</t>
         </is>
@@ -2636,7 +2738,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M26" s="24" t="n"/>
+      <c r="M26" s="21" t="n"/>
       <c r="N26" s="22" t="n"/>
       <c r="O26" s="22" t="n"/>
       <c r="P26" s="22" t="n"/>
@@ -2649,7 +2751,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>Termografía de tableros y conexiones</t>
         </is>
@@ -2671,7 +2773,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M27" s="24" t="n"/>
+      <c r="M27" s="21" t="n"/>
       <c r="N27" s="22" t="n"/>
       <c r="O27" s="22" t="n"/>
       <c r="P27" s="22" t="n"/>
@@ -2679,7 +2781,7 @@
     </row>
     <row r="28" ht="25.05" customHeight="1">
       <c r="A28" s="11" t="n"/>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  NEUMÁTICO</t>
         </is>
@@ -2697,12 +2799,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L28" s="36" t="inlineStr">
+      <c r="L28" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M28" s="36" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -2719,7 +2821,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Verificación de presión de trabajo y purga de condensados</t>
         </is>
@@ -2741,7 +2843,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M29" s="24" t="n"/>
+      <c r="M29" s="21" t="n"/>
       <c r="N29" s="22" t="n"/>
       <c r="O29" s="22" t="n"/>
       <c r="P29" s="22" t="n"/>
@@ -2754,7 +2856,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>Inspección de mangueras, racores y conexiones neumáticas</t>
         </is>
@@ -2776,7 +2878,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M30" s="24" t="n"/>
+      <c r="M30" s="21" t="n"/>
       <c r="N30" s="22" t="n"/>
       <c r="O30" s="22" t="n"/>
       <c r="P30" s="22" t="n"/>
@@ -2789,7 +2891,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Revisión de cilindros neumáticos (vástagos, sellos y fugas)</t>
         </is>
@@ -2811,7 +2913,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M31" s="24" t="n"/>
+      <c r="M31" s="21" t="n"/>
       <c r="N31" s="22" t="n"/>
       <c r="O31" s="22" t="n"/>
       <c r="P31" s="22" t="n"/>
@@ -2824,7 +2926,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>Limpieza/cambio de filtros de aire comprimido (FRL)</t>
         </is>
@@ -2846,7 +2948,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M32" s="24" t="n"/>
+      <c r="M32" s="21" t="n"/>
       <c r="N32" s="22" t="n"/>
       <c r="O32" s="22" t="n"/>
       <c r="P32" s="22" t="n"/>
@@ -2859,7 +2961,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Revisión y ajuste de válvulas solenoides</t>
         </is>
@@ -2881,7 +2983,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M33" s="24" t="n"/>
+      <c r="M33" s="21" t="n"/>
       <c r="N33" s="22" t="n"/>
       <c r="O33" s="22" t="n"/>
       <c r="P33" s="22" t="n"/>
@@ -2889,7 +2991,7 @@
     </row>
     <row r="34" ht="25.05" customHeight="1">
       <c r="A34" s="11" t="n"/>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
@@ -2905,7 +3007,7 @@
       <c r="K34" s="22" t="n"/>
       <c r="L34" s="22" t="n"/>
       <c r="M34" s="23" t="n"/>
-      <c r="N34" s="33" t="inlineStr">
+      <c r="N34" s="43" t="inlineStr">
         <is>
           <t>VOLTAJE ALIMENTACIÓN</t>
         </is>
@@ -3066,38 +3168,38 @@
     </row>
     <row r="37" ht="25.05" customHeight="1">
       <c r="A37" s="11" t="n"/>
-      <c r="B37" s="70" t="inlineStr">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C37" s="45" t="n"/>
-      <c r="D37" s="45" t="n"/>
-      <c r="E37" s="45" t="n"/>
-      <c r="F37" s="45" t="n"/>
-      <c r="G37" s="46" t="n"/>
-      <c r="H37" s="71" t="inlineStr">
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+      <c r="E37" s="50" t="n"/>
+      <c r="F37" s="50" t="n"/>
+      <c r="G37" s="51" t="n"/>
+      <c r="H37" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
       <c r="I37" s="75" t="n"/>
       <c r="J37" s="75" t="n"/>
-      <c r="K37" s="72" t="inlineStr">
+      <c r="K37" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L37" s="45" t="n"/>
-      <c r="M37" s="45" t="n"/>
-      <c r="N37" s="45" t="n"/>
-      <c r="O37" s="45" t="n"/>
-      <c r="P37" s="45" t="n"/>
-      <c r="Q37" s="46" t="n"/>
+      <c r="L37" s="50" t="n"/>
+      <c r="M37" s="50" t="n"/>
+      <c r="N37" s="50" t="n"/>
+      <c r="O37" s="50" t="n"/>
+      <c r="P37" s="50" t="n"/>
+      <c r="Q37" s="51" t="n"/>
     </row>
     <row r="38" ht="25.05" customHeight="1">
-      <c r="B38" s="70" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -3107,7 +3209,7 @@
       <c r="E38" s="76" t="n"/>
       <c r="F38" s="76" t="n"/>
       <c r="G38" s="77" t="n"/>
-      <c r="K38" s="70" t="inlineStr">
+      <c r="K38" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -3150,16 +3252,16 @@
     <mergeCell ref="B34:M34"/>
     <mergeCell ref="M20:Q20"/>
     <mergeCell ref="C29:J29"/>
-    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B28:J28"/>
     <mergeCell ref="C20:J20"/>
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="M11:Q11"/>
     <mergeCell ref="C25:J25"/>
-    <mergeCell ref="B28:J28"/>
     <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C16:J16"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="B37:G37"/>
     <mergeCell ref="C22:J22"/>
     <mergeCell ref="M22:Q22"/>
     <mergeCell ref="C31:J31"/>
@@ -3186,8 +3288,8 @@
     <mergeCell ref="M18:Q18"/>
     <mergeCell ref="M27:Q27"/>
     <mergeCell ref="C23:J23"/>
+    <mergeCell ref="K38:Q39"/>
     <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="K38:Q39"/>
     <mergeCell ref="C8:J8"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="M26:Q26"/>
@@ -3213,6 +3315,1166 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:Q32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="9.5546875" customWidth="1" min="1" max="1"/>
+    <col width="12.77734375" customWidth="1" min="2" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="7.8" customHeight="1"/>
+    <row r="2" ht="56.55" customHeight="1">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+      <c r="L2" s="22" t="n"/>
+      <c r="M2" s="22" t="n"/>
+      <c r="N2" s="23" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
+    </row>
+    <row r="3" ht="97.8" customHeight="1">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="38" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO PREVENTIVO   —   GAPCUTTER</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
+      <c r="K3" s="22" t="n"/>
+      <c r="L3" s="22" t="n"/>
+      <c r="M3" s="22" t="n"/>
+      <c r="N3" s="23" t="n"/>
+      <c r="O3" s="35" t="n"/>
+      <c r="P3" s="22" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+    </row>
+    <row r="4" ht="25.05" customHeight="1">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>Alcance: Equipos de Conversión – AD-PACK</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="22" t="n"/>
+      <c r="F4" s="22" t="n"/>
+      <c r="G4" s="22" t="n"/>
+      <c r="H4" s="22" t="n"/>
+      <c r="I4" s="23" t="n"/>
+      <c r="J4" s="33" t="inlineStr">
+        <is>
+          <t>Autor: Mariano Leyva</t>
+        </is>
+      </c>
+      <c r="K4" s="22" t="n"/>
+      <c r="L4" s="22" t="n"/>
+      <c r="M4" s="22" t="n"/>
+      <c r="N4" s="22" t="n"/>
+      <c r="O4" s="22" t="n"/>
+      <c r="P4" s="22" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+    </row>
+    <row r="5" ht="46.2" customHeight="1">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Tipo de mantenimiento:  Preventivo</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="23" t="n"/>
+      <c r="J5" s="33" t="inlineStr">
+        <is>
+          <t>Indicaciones: Usar equipo de seguridad.</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="22" t="n"/>
+      <c r="M5" s="22" t="n"/>
+      <c r="N5" s="22" t="n"/>
+      <c r="O5" s="22" t="n"/>
+      <c r="P5" s="22" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+    </row>
+    <row r="6" ht="25.05" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>Nombre de máquina:  Gap cutter</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t>Número de máquina:  GC01</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="22" t="n"/>
+      <c r="P6" s="22" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="25.05" customHeight="1">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MECÁNICO</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L7" s="27" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M7" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMENTARIOS </t>
+        </is>
+      </c>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+    </row>
+    <row r="8" ht="25.05" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Inspección visual: ruidos, vibraciones y fugas</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="23" t="n"/>
+    </row>
+    <row r="9" ht="25.05" customHeight="1">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Revisión de cuchillas de corte (filo, desgaste y sujeción)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="n"/>
+      <c r="P9" s="22" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+    </row>
+    <row r="10" ht="25.05" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Lubricación de guías, ejes y mecanismos de corte</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="25.05" customHeight="1">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>Verificación de alineación del sistema de corte</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="25.05" customHeight="1">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de rodillos de alimentación y presión</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="23" t="n"/>
+    </row>
+    <row r="13" ht="25.05" customHeight="1">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Verificación de tornillería y fijaciones estructurales</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="22" t="n"/>
+      <c r="P13" s="22" t="n"/>
+      <c r="Q13" s="23" t="n"/>
+    </row>
+    <row r="14" ht="25.05" customHeight="1">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Afilado o cambio de cuchillas (según desgaste)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="23" t="n"/>
+    </row>
+    <row r="15" ht="25.05" customHeight="1">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ELÉCTRICO</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L15" s="27" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M15" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMENTARIOS </t>
+        </is>
+      </c>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+    </row>
+    <row r="16" ht="25.05" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Verificación visual del tablero (alarmas e indicadores)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22" t="n"/>
+      <c r="P16" s="22" t="n"/>
+      <c r="Q16" s="23" t="n"/>
+    </row>
+    <row r="17" ht="25.05" customHeight="1">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>Reapriete de terminales en tablero eléctrico</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="23" t="n"/>
+    </row>
+    <row r="18" ht="25.05" customHeight="1">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de motores (temperatura, ruido y vibración)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="23" t="n"/>
+    </row>
+    <row r="19" ht="25.05" customHeight="1">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>Revisión de sensores y fotoceldas de posición</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="25.05" customHeight="1">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Prueba funcional de paros de emergencia</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="25.05" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>Verificación de tierras físicas y continuidad</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="23" t="n"/>
+    </row>
+    <row r="22" ht="25.05" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEUMÁTICO</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L22" s="27" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M22" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMENTARIOS </t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="22" t="n"/>
+      <c r="P22" s="22" t="n"/>
+      <c r="Q22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="25.05" customHeight="1">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de presión de trabajo y purga de condensados</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="22" t="n"/>
+      <c r="Q23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="25.05" customHeight="1">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>Inspección de mangueras, racores y cilindros neumáticos</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="25.05" customHeight="1">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Limpieza/cambio de filtros FRL</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="22" t="n"/>
+      <c r="P25" s="22" t="n"/>
+      <c r="Q25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="25.05" customHeight="1">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>Revisión y ajuste de válvulas solenoides</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22" t="n"/>
+      <c r="P26" s="22" t="n"/>
+      <c r="Q26" s="23" t="n"/>
+    </row>
+    <row r="27" ht="25.05" customHeight="1">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>CALENDARIO  DE  MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="22" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="23" t="n"/>
+      <c r="N27" s="43" t="inlineStr">
+        <is>
+          <t>VOLTAJE ALIMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="O27" s="22" t="n"/>
+      <c r="P27" s="22" t="n"/>
+      <c r="Q27" s="23" t="n"/>
+    </row>
+    <row r="28" ht="25.05" customHeight="1">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>ABR</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>VAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="25.05" customHeight="1">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n"/>
+      <c r="Q29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="25.05" customHeight="1">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Realizo: </t>
+        </is>
+      </c>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+      <c r="E30" s="50" t="n"/>
+      <c r="F30" s="50" t="n"/>
+      <c r="G30" s="51" t="n"/>
+      <c r="H30" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha: </t>
+        </is>
+      </c>
+      <c r="I30" s="75" t="n"/>
+      <c r="J30" s="75" t="n"/>
+      <c r="K30" s="40" t="inlineStr">
+        <is>
+          <t>Supervisor de Producción: 
+Firma: _____________________________</t>
+        </is>
+      </c>
+      <c r="L30" s="50" t="n"/>
+      <c r="M30" s="50" t="n"/>
+      <c r="N30" s="50" t="n"/>
+      <c r="O30" s="50" t="n"/>
+      <c r="P30" s="50" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+    </row>
+    <row r="31" ht="25.05" customHeight="1">
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="C31" s="76" t="n"/>
+      <c r="D31" s="76" t="n"/>
+      <c r="E31" s="76" t="n"/>
+      <c r="F31" s="76" t="n"/>
+      <c r="G31" s="77" t="n"/>
+      <c r="K31" s="39" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="L31" s="76" t="n"/>
+      <c r="M31" s="76" t="n"/>
+      <c r="N31" s="76" t="n"/>
+      <c r="O31" s="76" t="n"/>
+      <c r="P31" s="76" t="n"/>
+      <c r="Q31" s="77" t="n"/>
+    </row>
+    <row r="32" ht="25.05" customHeight="1">
+      <c r="B32" s="78" t="n"/>
+      <c r="C32" s="79" t="n"/>
+      <c r="D32" s="79" t="n"/>
+      <c r="E32" s="79" t="n"/>
+      <c r="F32" s="79" t="n"/>
+      <c r="G32" s="80" t="n"/>
+      <c r="K32" s="78" t="n"/>
+      <c r="L32" s="79" t="n"/>
+      <c r="M32" s="79" t="n"/>
+      <c r="N32" s="79" t="n"/>
+      <c r="O32" s="79" t="n"/>
+      <c r="P32" s="79" t="n"/>
+      <c r="Q32" s="80" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="J5:Q5"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="M9:Q9"/>
+    <mergeCell ref="N27:Q27"/>
+    <mergeCell ref="C26:J26"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="J6:Q6"/>
+    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="B31:G32"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="K31:Q32"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="J4:Q4"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="H30:J32"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="C18:J18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3229,7 +4491,7 @@
     <row r="1" ht="7.8" customHeight="1"/>
     <row r="2" ht="56.55" customHeight="1">
       <c r="A2" s="11" t="n"/>
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
@@ -3246,22 +4508,22 @@
       <c r="L2" s="22" t="n"/>
       <c r="M2" s="22" t="n"/>
       <c r="N2" s="23" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>No. de Documento             A9.I1.F2
-Revision:                                    00
-Fecha:                        08/06/2026</t>
-        </is>
-      </c>
-      <c r="P2" s="22" t="n"/>
-      <c r="Q2" s="23" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
       <c r="A3" s="11" t="n"/>
-      <c r="B3" s="38" t="n"/>
+      <c r="B3" s="36" t="n"/>
       <c r="C3" s="22" t="n"/>
       <c r="D3" s="23" t="n"/>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="38" t="inlineStr">
         <is>
           <t>MANTENIMIENTO PREVENTIVO   —   SLITTER REWINDER 3M EXX4011A+</t>
         </is>
@@ -3281,7 +4543,7 @@
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
@@ -3293,7 +4555,7 @@
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
       <c r="I4" s="23" t="n"/>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
@@ -3308,7 +4570,7 @@
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
@@ -3320,7 +4582,7 @@
       <c r="G5" s="22" t="n"/>
       <c r="H5" s="22" t="n"/>
       <c r="I5" s="23" t="n"/>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
@@ -3335,7 +4597,7 @@
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Nombre de máquina:  Cortadora  rebobinadora.</t>
         </is>
@@ -3347,7 +4609,7 @@
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="23" t="n"/>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Número de máquina:  SR01</t>
         </is>
@@ -3362,7 +4624,7 @@
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO</t>
         </is>
@@ -3380,12 +4642,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -3402,7 +4664,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Inspección visual: ruidos, vibraciones y fugas</t>
         </is>
@@ -3424,7 +4686,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M8" s="24" t="n"/>
+      <c r="M8" s="21" t="n"/>
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="22" t="n"/>
@@ -3437,7 +4699,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Lubricación de rodillos, guías y mecanismos de bobinado</t>
         </is>
@@ -3459,7 +4721,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M9" s="24" t="n"/>
+      <c r="M9" s="21" t="n"/>
       <c r="N9" s="22" t="n"/>
       <c r="O9" s="22" t="n"/>
       <c r="P9" s="22" t="n"/>
@@ -3472,7 +4734,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Inspección de cuchillas de corte (filo, alineación y sujeción)</t>
         </is>
@@ -3494,7 +4756,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M10" s="24" t="n"/>
+      <c r="M10" s="21" t="n"/>
       <c r="N10" s="22" t="n"/>
       <c r="O10" s="22" t="n"/>
       <c r="P10" s="22" t="n"/>
@@ -3507,7 +4769,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Revisión de frenos y embragues de rebobinado</t>
         </is>
@@ -3529,7 +4791,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M11" s="24" t="n"/>
+      <c r="M11" s="21" t="n"/>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="22" t="n"/>
       <c r="P11" s="22" t="n"/>
@@ -3542,7 +4804,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Verificación de alineación de ejes y bobinas</t>
         </is>
@@ -3564,7 +4826,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M12" s="24" t="n"/>
+      <c r="M12" s="21" t="n"/>
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
       <c r="P12" s="22" t="n"/>
@@ -3577,7 +4839,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Revisión de rodillos de contacto y jaladores</t>
         </is>
@@ -3599,7 +4861,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M13" s="24" t="n"/>
+      <c r="M13" s="21" t="n"/>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="22" t="n"/>
       <c r="P13" s="22" t="n"/>
@@ -3612,7 +4874,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Revisión y ajuste de tensión de correas y cadenas</t>
         </is>
@@ -3634,7 +4896,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M14" s="24" t="n"/>
+      <c r="M14" s="21" t="n"/>
       <c r="N14" s="22" t="n"/>
       <c r="O14" s="22" t="n"/>
       <c r="P14" s="22" t="n"/>
@@ -3647,7 +4909,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Verificación de tornillería y fijaciones estructurales</t>
         </is>
@@ -3669,7 +4931,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M15" s="24" t="n"/>
+      <c r="M15" s="21" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
       <c r="P15" s="22" t="n"/>
@@ -3682,7 +4944,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Overhaul – desmontaje y mantenimiento mayor</t>
         </is>
@@ -3704,7 +4966,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M16" s="24" t="n"/>
+      <c r="M16" s="21" t="n"/>
       <c r="N16" s="22" t="n"/>
       <c r="O16" s="22" t="n"/>
       <c r="P16" s="22" t="n"/>
@@ -3712,7 +4974,7 @@
     </row>
     <row r="17" ht="25.05" customHeight="1">
       <c r="A17" s="11" t="n"/>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
@@ -3730,12 +4992,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L17" s="36" t="inlineStr">
+      <c r="L17" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M17" s="36" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -3752,7 +5014,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Verificación visual del tablero (alarmas e indicadores)</t>
         </is>
@@ -3774,7 +5036,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n"/>
+      <c r="M18" s="21" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
       <c r="P18" s="22" t="n"/>
@@ -3787,7 +5049,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>Limpieza de tableros eléctricos y revisión de cableado</t>
         </is>
@@ -3809,7 +5071,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n"/>
+      <c r="M19" s="21" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
       <c r="P19" s="22" t="n"/>
@@ -3822,7 +5084,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Reapriete de terminales en tablero eléctrico</t>
         </is>
@@ -3844,7 +5106,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n"/>
+      <c r="M20" s="21" t="n"/>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
@@ -3857,7 +5119,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>Verificación de fusibles, contactores y relés térmicos</t>
         </is>
@@ -3879,7 +5141,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M21" s="24" t="n"/>
+      <c r="M21" s="21" t="n"/>
       <c r="N21" s="22" t="n"/>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="22" t="n"/>
@@ -3892,7 +5154,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Revisión de motores (temperatura, ruido y vibración)</t>
         </is>
@@ -3914,7 +5176,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M22" s="24" t="n"/>
+      <c r="M22" s="21" t="n"/>
       <c r="N22" s="22" t="n"/>
       <c r="O22" s="22" t="n"/>
       <c r="P22" s="22" t="n"/>
@@ -3927,7 +5189,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>Revisión de variadores de frecuencia (tensión y velocidad)</t>
         </is>
@@ -3949,7 +5211,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M23" s="24" t="n"/>
+      <c r="M23" s="21" t="n"/>
       <c r="N23" s="22" t="n"/>
       <c r="O23" s="22" t="n"/>
       <c r="P23" s="22" t="n"/>
@@ -3962,7 +5224,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Revisión de sensores y fotoceldas de detección de material</t>
         </is>
@@ -3984,7 +5246,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
+      <c r="M24" s="21" t="n"/>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
       <c r="P24" s="22" t="n"/>
@@ -3997,7 +5259,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>Prueba funcional de paros de emergencia</t>
         </is>
@@ -4019,7 +5281,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M25" s="24" t="n"/>
+      <c r="M25" s="21" t="n"/>
       <c r="N25" s="22" t="n"/>
       <c r="O25" s="22" t="n"/>
       <c r="P25" s="22" t="n"/>
@@ -4032,7 +5294,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Verificación de tierras físicas y continuidad</t>
         </is>
@@ -4054,7 +5316,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M26" s="24" t="n"/>
+      <c r="M26" s="21" t="n"/>
       <c r="N26" s="22" t="n"/>
       <c r="O26" s="22" t="n"/>
       <c r="P26" s="22" t="n"/>
@@ -4067,7 +5329,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>Termografía de tableros y conexiones</t>
         </is>
@@ -4089,7 +5351,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M27" s="24" t="n"/>
+      <c r="M27" s="21" t="n"/>
       <c r="N27" s="22" t="n"/>
       <c r="O27" s="22" t="n"/>
       <c r="P27" s="22" t="n"/>
@@ -4097,7 +5359,7 @@
     </row>
     <row r="28" ht="25.05" customHeight="1">
       <c r="A28" s="11" t="n"/>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  NEUMÁTICO</t>
         </is>
@@ -4115,12 +5377,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L28" s="36" t="inlineStr">
+      <c r="L28" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M28" s="36" t="inlineStr">
+      <c r="M28" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -4137,7 +5399,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Verificación de presión de trabajo y purga de condensados</t>
         </is>
@@ -4159,7 +5421,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M29" s="24" t="n"/>
+      <c r="M29" s="21" t="n"/>
       <c r="N29" s="22" t="n"/>
       <c r="O29" s="22" t="n"/>
       <c r="P29" s="22" t="n"/>
@@ -4172,7 +5434,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>Inspección de mangueras, racores y conexiones neumáticas</t>
         </is>
@@ -4194,7 +5456,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M30" s="24" t="n"/>
+      <c r="M30" s="21" t="n"/>
       <c r="N30" s="22" t="n"/>
       <c r="O30" s="22" t="n"/>
       <c r="P30" s="22" t="n"/>
@@ -4207,7 +5469,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Revisión de cilindros neumáticos de presión de rodillos</t>
         </is>
@@ -4229,7 +5491,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M31" s="24" t="n"/>
+      <c r="M31" s="21" t="n"/>
       <c r="N31" s="22" t="n"/>
       <c r="O31" s="22" t="n"/>
       <c r="P31" s="22" t="n"/>
@@ -4242,7 +5504,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>Limpieza/cambio de filtros FRL</t>
         </is>
@@ -4264,7 +5526,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M32" s="24" t="n"/>
+      <c r="M32" s="21" t="n"/>
       <c r="N32" s="22" t="n"/>
       <c r="O32" s="22" t="n"/>
       <c r="P32" s="22" t="n"/>
@@ -4277,7 +5539,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Revisión y ajuste de válvulas solenoides</t>
         </is>
@@ -4299,7 +5561,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M33" s="24" t="n"/>
+      <c r="M33" s="21" t="n"/>
       <c r="N33" s="22" t="n"/>
       <c r="O33" s="22" t="n"/>
       <c r="P33" s="22" t="n"/>
@@ -4307,7 +5569,7 @@
     </row>
     <row r="34" ht="25.05" customHeight="1">
       <c r="A34" s="11" t="n"/>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
@@ -4323,7 +5585,7 @@
       <c r="K34" s="22" t="n"/>
       <c r="L34" s="22" t="n"/>
       <c r="M34" s="23" t="n"/>
-      <c r="N34" s="33" t="inlineStr">
+      <c r="N34" s="43" t="inlineStr">
         <is>
           <t>VOLTAJE ALIMENTACIÓN</t>
         </is>
@@ -4484,38 +5746,38 @@
     </row>
     <row r="37" ht="25.05" customHeight="1">
       <c r="A37" s="11" t="n"/>
-      <c r="B37" s="70" t="inlineStr">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C37" s="45" t="n"/>
-      <c r="D37" s="45" t="n"/>
-      <c r="E37" s="45" t="n"/>
-      <c r="F37" s="45" t="n"/>
-      <c r="G37" s="46" t="n"/>
-      <c r="H37" s="71" t="inlineStr">
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+      <c r="E37" s="50" t="n"/>
+      <c r="F37" s="50" t="n"/>
+      <c r="G37" s="51" t="n"/>
+      <c r="H37" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
       <c r="I37" s="75" t="n"/>
       <c r="J37" s="75" t="n"/>
-      <c r="K37" s="72" t="inlineStr">
+      <c r="K37" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L37" s="45" t="n"/>
-      <c r="M37" s="45" t="n"/>
-      <c r="N37" s="45" t="n"/>
-      <c r="O37" s="45" t="n"/>
-      <c r="P37" s="45" t="n"/>
-      <c r="Q37" s="46" t="n"/>
+      <c r="L37" s="50" t="n"/>
+      <c r="M37" s="50" t="n"/>
+      <c r="N37" s="50" t="n"/>
+      <c r="O37" s="50" t="n"/>
+      <c r="P37" s="50" t="n"/>
+      <c r="Q37" s="51" t="n"/>
     </row>
     <row r="38" ht="25.05" customHeight="1">
-      <c r="B38" s="70" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -4525,7 +5787,7 @@
       <c r="E38" s="76" t="n"/>
       <c r="F38" s="76" t="n"/>
       <c r="G38" s="77" t="n"/>
-      <c r="K38" s="70" t="inlineStr">
+      <c r="K38" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -4569,15 +5831,15 @@
     <mergeCell ref="M20:Q20"/>
     <mergeCell ref="C29:J29"/>
     <mergeCell ref="B37:G37"/>
-    <mergeCell ref="C20:J20"/>
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="C20:J20"/>
     <mergeCell ref="C25:J25"/>
-    <mergeCell ref="B28:J28"/>
     <mergeCell ref="C10:J10"/>
+    <mergeCell ref="C16:J16"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="B28:J28"/>
     <mergeCell ref="C22:J22"/>
     <mergeCell ref="M22:Q22"/>
     <mergeCell ref="C31:J31"/>
@@ -4586,18 +5848,18 @@
     <mergeCell ref="M31:Q31"/>
     <mergeCell ref="C9:J9"/>
     <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="M16:Q16"/>
     <mergeCell ref="H37:J39"/>
     <mergeCell ref="J4:Q4"/>
     <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="C12:J12"/>
     <mergeCell ref="C21:J21"/>
     <mergeCell ref="M25:Q25"/>
     <mergeCell ref="M15:Q15"/>
     <mergeCell ref="B38:G39"/>
     <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="C11:J11"/>
     <mergeCell ref="M30:Q30"/>
-    <mergeCell ref="C11:J11"/>
     <mergeCell ref="M33:Q33"/>
     <mergeCell ref="M28:Q28"/>
     <mergeCell ref="C27:J27"/>
@@ -4648,7 +5910,7 @@
     <row r="1" ht="7.8" customHeight="1"/>
     <row r="2" ht="56.55" customHeight="1">
       <c r="A2" s="11" t="n"/>
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
@@ -4665,22 +5927,22 @@
       <c r="L2" s="22" t="n"/>
       <c r="M2" s="22" t="n"/>
       <c r="N2" s="23" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>No. de Documento             A9.I1.F2
-Revision:                                    00
-Fecha:                        08/06/2026</t>
-        </is>
-      </c>
-      <c r="P2" s="22" t="n"/>
-      <c r="Q2" s="23" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
       <c r="A3" s="11" t="n"/>
-      <c r="B3" s="38" t="n"/>
+      <c r="B3" s="36" t="n"/>
       <c r="C3" s="22" t="n"/>
       <c r="D3" s="23" t="n"/>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="38" t="inlineStr">
         <is>
           <t>MANTENIMIENTO PREVENTIVO   —   KOMATSU OBS45 – PRENSA OBDS</t>
         </is>
@@ -4700,7 +5962,7 @@
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
@@ -4712,7 +5974,7 @@
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
       <c r="I4" s="23" t="n"/>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
@@ -4727,7 +5989,7 @@
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
@@ -4739,7 +6001,7 @@
       <c r="G5" s="22" t="n"/>
       <c r="H5" s="22" t="n"/>
       <c r="I5" s="23" t="n"/>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
@@ -4754,7 +6016,7 @@
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Nombre de máquina:  Komatsu OBS45</t>
         </is>
@@ -4766,7 +6028,7 @@
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="23" t="n"/>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Número de máquina:  KO01</t>
         </is>
@@ -4781,7 +6043,7 @@
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO / HIDRÁULICO</t>
         </is>
@@ -4799,12 +6061,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -4821,7 +6083,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Inspección visual de estructura, cilindros y mangueras</t>
         </is>
@@ -4843,7 +6105,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M8" s="24" t="n"/>
+      <c r="M8" s="21" t="n"/>
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="22" t="n"/>
@@ -4856,7 +6118,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Verificación de nivel y calidad del aceite hidráulico</t>
         </is>
@@ -4878,7 +6140,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M9" s="24" t="n"/>
+      <c r="M9" s="21" t="n"/>
       <c r="N9" s="22" t="n"/>
       <c r="O9" s="22" t="n"/>
       <c r="P9" s="22" t="n"/>
@@ -4891,7 +6153,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Revisión de cilindros hidráulicos (vástagos, sellos y fugas)</t>
         </is>
@@ -4913,7 +6175,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M10" s="24" t="n"/>
+      <c r="M10" s="21" t="n"/>
       <c r="N10" s="22" t="n"/>
       <c r="O10" s="22" t="n"/>
       <c r="P10" s="22" t="n"/>
@@ -4926,7 +6188,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Limpieza de filtro de aceite hidráulico</t>
         </is>
@@ -4948,7 +6210,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M11" s="24" t="n"/>
+      <c r="M11" s="21" t="n"/>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="22" t="n"/>
       <c r="P11" s="22" t="n"/>
@@ -4961,7 +6223,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Revisión de bomba hidráulica (ruido, presión y temperatura)</t>
         </is>
@@ -4983,7 +6245,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M12" s="24" t="n"/>
+      <c r="M12" s="21" t="n"/>
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
       <c r="P12" s="22" t="n"/>
@@ -4996,7 +6258,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Verificación de válvulas de control y alivio de presión</t>
         </is>
@@ -5018,7 +6280,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M13" s="24" t="n"/>
+      <c r="M13" s="21" t="n"/>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="22" t="n"/>
       <c r="P13" s="22" t="n"/>
@@ -5031,7 +6293,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Revisión de guías y placas de desgaste de la prensa</t>
         </is>
@@ -5053,7 +6315,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M14" s="24" t="n"/>
+      <c r="M14" s="21" t="n"/>
       <c r="N14" s="22" t="n"/>
       <c r="O14" s="22" t="n"/>
       <c r="P14" s="22" t="n"/>
@@ -5066,7 +6328,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Lubricación de guías, columnas y mecanismos de cierre</t>
         </is>
@@ -5088,7 +6350,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M15" s="24" t="n"/>
+      <c r="M15" s="21" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
       <c r="P15" s="22" t="n"/>
@@ -5101,7 +6363,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Verificación de tornillería y fijaciones estructurales</t>
         </is>
@@ -5123,7 +6385,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M16" s="24" t="n"/>
+      <c r="M16" s="21" t="n"/>
       <c r="N16" s="22" t="n"/>
       <c r="O16" s="22" t="n"/>
       <c r="P16" s="22" t="n"/>
@@ -5136,7 +6398,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C17" s="53" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>Cambio de aceite hidráulico (programado)</t>
         </is>
@@ -5148,17 +6410,17 @@
       <c r="H17" s="22" t="n"/>
       <c r="I17" s="22" t="n"/>
       <c r="J17" s="23" t="n"/>
-      <c r="K17" s="56" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L17" s="56" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M17" s="56" t="n"/>
+      <c r="K17" s="62" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L17" s="62" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M17" s="62" t="n"/>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="22" t="n"/>
@@ -5166,12 +6428,12 @@
     </row>
     <row r="18" ht="25.05" customHeight="1">
       <c r="A18" s="11" t="n"/>
-      <c r="B18" s="65" t="inlineStr">
+      <c r="B18" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
       </c>
-      <c r="C18" s="57" t="n"/>
+      <c r="C18" s="58" t="n"/>
       <c r="D18" s="22" t="n"/>
       <c r="E18" s="22" t="n"/>
       <c r="F18" s="22" t="n"/>
@@ -5184,12 +6446,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L18" s="36" t="inlineStr">
+      <c r="L18" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M18" s="36" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -5206,7 +6468,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>Verificación visual del tablero (alarmas e indicadores)</t>
         </is>
@@ -5228,7 +6490,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n"/>
+      <c r="M19" s="21" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
       <c r="P19" s="22" t="n"/>
@@ -5241,7 +6503,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Limpieza de tableros eléctricos y revisión de cableado</t>
         </is>
@@ -5263,7 +6525,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n"/>
+      <c r="M20" s="21" t="n"/>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
@@ -5276,7 +6538,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>Reapriete de terminales en tablero eléctrico</t>
         </is>
@@ -5298,7 +6560,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M21" s="24" t="n"/>
+      <c r="M21" s="21" t="n"/>
       <c r="N21" s="22" t="n"/>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="22" t="n"/>
@@ -5311,7 +6573,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Verificación de fusibles, contactores y relés térmicos</t>
         </is>
@@ -5333,7 +6595,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M22" s="24" t="n"/>
+      <c r="M22" s="21" t="n"/>
       <c r="N22" s="22" t="n"/>
       <c r="O22" s="22" t="n"/>
       <c r="P22" s="22" t="n"/>
@@ -5346,7 +6608,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>Revisión de motores (temperatura, ruido y vibración)</t>
         </is>
@@ -5368,7 +6630,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M23" s="24" t="n"/>
+      <c r="M23" s="21" t="n"/>
       <c r="N23" s="22" t="n"/>
       <c r="O23" s="22" t="n"/>
       <c r="P23" s="22" t="n"/>
@@ -5381,7 +6643,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Revisión de sensores de posición y finales de carrera</t>
         </is>
@@ -5403,7 +6665,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
+      <c r="M24" s="21" t="n"/>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
       <c r="P24" s="22" t="n"/>
@@ -5416,7 +6678,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>Revisión de dispositivos de seguridad y cortina óptica</t>
         </is>
@@ -5438,7 +6700,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M25" s="24" t="n"/>
+      <c r="M25" s="21" t="n"/>
       <c r="N25" s="22" t="n"/>
       <c r="O25" s="22" t="n"/>
       <c r="P25" s="22" t="n"/>
@@ -5451,7 +6713,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Prueba funcional de paros de emergencia</t>
         </is>
@@ -5473,7 +6735,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M26" s="24" t="n"/>
+      <c r="M26" s="21" t="n"/>
       <c r="N26" s="22" t="n"/>
       <c r="O26" s="22" t="n"/>
       <c r="P26" s="22" t="n"/>
@@ -5486,7 +6748,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>Verificación de tierras físicas y continuidad</t>
         </is>
@@ -5508,7 +6770,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M27" s="24" t="n"/>
+      <c r="M27" s="21" t="n"/>
       <c r="N27" s="22" t="n"/>
       <c r="O27" s="22" t="n"/>
       <c r="P27" s="22" t="n"/>
@@ -5519,7 +6781,7 @@
       <c r="B28" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>Termografía de tableros y conexiones</t>
         </is>
@@ -5531,17 +6793,17 @@
       <c r="H28" s="22" t="n"/>
       <c r="I28" s="22" t="n"/>
       <c r="J28" s="23" t="n"/>
-      <c r="K28" s="50" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L28" s="50" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M28" s="50" t="n"/>
+      <c r="K28" s="52" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L28" s="52" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M28" s="52" t="n"/>
       <c r="N28" s="22" t="n"/>
       <c r="O28" s="22" t="n"/>
       <c r="P28" s="22" t="n"/>
@@ -5549,7 +6811,7 @@
     </row>
     <row r="29" ht="25.05" customHeight="1">
       <c r="A29" s="11" t="n"/>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
@@ -5565,7 +6827,7 @@
       <c r="K29" s="22" t="n"/>
       <c r="L29" s="22" t="n"/>
       <c r="M29" s="23" t="n"/>
-      <c r="N29" s="33" t="inlineStr">
+      <c r="N29" s="43" t="inlineStr">
         <is>
           <t>VOLTAJE ALIMENTACIÓN</t>
         </is>
@@ -5726,38 +6988,38 @@
     </row>
     <row r="32" ht="25.05" customHeight="1">
       <c r="A32" s="11" t="n"/>
-      <c r="B32" s="70" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C32" s="45" t="n"/>
-      <c r="D32" s="45" t="n"/>
-      <c r="E32" s="45" t="n"/>
-      <c r="F32" s="45" t="n"/>
-      <c r="G32" s="46" t="n"/>
-      <c r="H32" s="71" t="inlineStr">
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+      <c r="E32" s="50" t="n"/>
+      <c r="F32" s="50" t="n"/>
+      <c r="G32" s="51" t="n"/>
+      <c r="H32" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
       <c r="I32" s="75" t="n"/>
       <c r="J32" s="75" t="n"/>
-      <c r="K32" s="72" t="inlineStr">
+      <c r="K32" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L32" s="45" t="n"/>
-      <c r="M32" s="45" t="n"/>
-      <c r="N32" s="45" t="n"/>
-      <c r="O32" s="45" t="n"/>
-      <c r="P32" s="45" t="n"/>
-      <c r="Q32" s="46" t="n"/>
+      <c r="L32" s="50" t="n"/>
+      <c r="M32" s="50" t="n"/>
+      <c r="N32" s="50" t="n"/>
+      <c r="O32" s="50" t="n"/>
+      <c r="P32" s="50" t="n"/>
+      <c r="Q32" s="51" t="n"/>
     </row>
     <row r="33" ht="25.05" customHeight="1">
-      <c r="B33" s="70" t="inlineStr">
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -5767,7 +7029,7 @@
       <c r="E33" s="76" t="n"/>
       <c r="F33" s="76" t="n"/>
       <c r="G33" s="77" t="n"/>
-      <c r="K33" s="70" t="inlineStr">
+      <c r="K33" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -5799,6 +7061,7 @@
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="B33:G34"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C24:J24"/>
     <mergeCell ref="J5:Q5"/>
@@ -5854,13 +7117,12 @@
     <mergeCell ref="M14:Q14"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C13:J13"/>
     <mergeCell ref="C19:J19"/>
-    <mergeCell ref="C13:J13"/>
     <mergeCell ref="M19:Q19"/>
     <mergeCell ref="N29:Q29"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="C18:J18"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B33:G34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5883,7 +7145,7 @@
     <row r="1" ht="7.8" customHeight="1"/>
     <row r="2" ht="56.55" customHeight="1">
       <c r="A2" s="11" t="n"/>
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
@@ -5900,22 +7162,22 @@
       <c r="L2" s="22" t="n"/>
       <c r="M2" s="22" t="n"/>
       <c r="N2" s="23" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>No. de Documento             A9.I1.F2
-Revision:                                    00
-Fecha:                        08/06/2026</t>
-        </is>
-      </c>
-      <c r="P2" s="22" t="n"/>
-      <c r="Q2" s="23" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
       <c r="A3" s="11" t="n"/>
-      <c r="B3" s="38" t="n"/>
+      <c r="B3" s="36" t="n"/>
       <c r="C3" s="22" t="n"/>
       <c r="D3" s="23" t="n"/>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="38" t="inlineStr">
         <is>
           <t>MANTENIMIENTO PREVENTIVO   — Rotary Press</t>
         </is>
@@ -5935,7 +7197,7 @@
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
@@ -5947,7 +7209,7 @@
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
       <c r="I4" s="23" t="n"/>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
@@ -5962,7 +7224,7 @@
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
@@ -5974,7 +7236,7 @@
       <c r="G5" s="22" t="n"/>
       <c r="H5" s="22" t="n"/>
       <c r="I5" s="23" t="n"/>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
@@ -5989,7 +7251,7 @@
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Nombre de máquina:  Prensa de rodillos rotativos</t>
         </is>
@@ -6001,7 +7263,7 @@
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="23" t="n"/>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Número de máquina:  RP01</t>
         </is>
@@ -6016,7 +7278,7 @@
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO</t>
         </is>
@@ -6034,12 +7296,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -6051,12 +7313,14 @@
     </row>
     <row r="8" ht="25.05" customHeight="1">
       <c r="A8" s="11" t="n"/>
-      <c r="B8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>Inspección visual: ruidos, vibraciones y fugas en mecanismos</t>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Inspección visual: ruidos, vibraciones y fugas</t>
         </is>
       </c>
       <c r="D8" s="22" t="n"/>
@@ -6076,7 +7340,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M8" s="24" t="n"/>
+      <c r="M8" s="21" t="n"/>
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="22" t="n"/>
@@ -6084,12 +7348,14 @@
     </row>
     <row r="9" ht="25.05" customHeight="1">
       <c r="A9" s="11" t="n"/>
-      <c r="B9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>Lubricación de engranajes helicoidales del eje de transmisión principal</t>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Lubricación de engranajes de gusano (worm gears) del sistema de transmisión</t>
         </is>
       </c>
       <c r="D9" s="22" t="n"/>
@@ -6109,7 +7375,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M9" s="24" t="n"/>
+      <c r="M9" s="21" t="n"/>
       <c r="N9" s="22" t="n"/>
       <c r="O9" s="22" t="n"/>
       <c r="P9" s="22" t="n"/>
@@ -6117,12 +7383,14 @@
     </row>
     <row r="10" ht="25.05" customHeight="1">
       <c r="A10" s="11" t="n"/>
-      <c r="B10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de rodillos de transporte y presión (desgaste, ajuste y limpieza)</t>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Revisión del eje de transmisión en línea (in-line drive shaft)</t>
         </is>
       </c>
       <c r="D10" s="22" t="n"/>
@@ -6142,7 +7410,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M10" s="24" t="n"/>
+      <c r="M10" s="21" t="n"/>
       <c r="N10" s="22" t="n"/>
       <c r="O10" s="22" t="n"/>
       <c r="P10" s="22" t="n"/>
@@ -6150,12 +7418,14 @@
     </row>
     <row r="11" ht="25.05" customHeight="1">
       <c r="A11" s="11" t="n"/>
-      <c r="B11" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="25" t="inlineStr">
-        <is>
-          <t>Inspección y limpieza de rodillos de arrastre de material (knurled)</t>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de estaciones de desenrollado (unwind) y reembobinado (rewind)</t>
         </is>
       </c>
       <c r="D11" s="22" t="n"/>
@@ -6175,7 +7445,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M11" s="24" t="n"/>
+      <c r="M11" s="21" t="n"/>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="22" t="n"/>
       <c r="P11" s="22" t="n"/>
@@ -6183,12 +7453,14 @@
     </row>
     <row r="12" ht="25.05" customHeight="1">
       <c r="A12" s="11" t="n"/>
-      <c r="B12" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>Revisión del sistema de troquel rotativo (desgaste de cuchillas y presión de corte)</t>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Inspección de rodillos de silicona anti-adherente (laminación y outboard)</t>
         </is>
       </c>
       <c r="D12" s="22" t="n"/>
@@ -6208,7 +7480,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M12" s="24" t="n"/>
+      <c r="M12" s="21" t="n"/>
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
       <c r="P12" s="22" t="n"/>
@@ -6216,12 +7488,14 @@
     </row>
     <row r="13" ht="25.05" customHeight="1">
       <c r="A13" s="11" t="n"/>
-      <c r="B13" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de rodamientos del eje principal (temperatura y ruido)</t>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Revisión del sistema de corte y troquel rotativo (desgaste y presión de corte)</t>
         </is>
       </c>
       <c r="D13" s="22" t="n"/>
@@ -6241,7 +7515,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M13" s="24" t="n"/>
+      <c r="M13" s="21" t="n"/>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="22" t="n"/>
       <c r="P13" s="22" t="n"/>
@@ -6249,12 +7523,14 @@
     </row>
     <row r="14" ht="25.05" customHeight="1">
       <c r="A14" s="11" t="n"/>
-      <c r="B14" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de alineación y tensión del material en sistema de guía</t>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de tensión del sustrato / material (web tension)</t>
         </is>
       </c>
       <c r="D14" s="22" t="n"/>
@@ -6274,7 +7550,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M14" s="24" t="n"/>
+      <c r="M14" s="21" t="n"/>
       <c r="N14" s="22" t="n"/>
       <c r="O14" s="22" t="n"/>
       <c r="P14" s="22" t="n"/>
@@ -6282,12 +7558,14 @@
     </row>
     <row r="15" ht="25.05" customHeight="1">
       <c r="A15" s="11" t="n"/>
-      <c r="B15" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de la transmisión por engranajes helicoidales (holgura y lubricación)</t>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Revisión del sistema de slitting (cuchillas de navaja, tijera o presión)</t>
         </is>
       </c>
       <c r="D15" s="22" t="n"/>
@@ -6307,7 +7585,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M15" s="24" t="n"/>
+      <c r="M15" s="21" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
       <c r="P15" s="22" t="n"/>
@@ -6315,12 +7593,14 @@
     </row>
     <row r="16" ht="25.05" customHeight="1">
       <c r="A16" s="11" t="n"/>
-      <c r="B16" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de la estación de corte: ajuste y alineación de rodillos</t>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de pines de localización fija de estaciones modulares</t>
         </is>
       </c>
       <c r="D16" s="22" t="n"/>
@@ -6340,7 +7620,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M16" s="24" t="n"/>
+      <c r="M16" s="21" t="n"/>
       <c r="N16" s="22" t="n"/>
       <c r="O16" s="22" t="n"/>
       <c r="P16" s="22" t="n"/>
@@ -6348,12 +7628,14 @@
     </row>
     <row r="17" ht="25.05" customHeight="1">
       <c r="A17" s="11" t="n"/>
-      <c r="B17" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de continuidad en fusibles</t>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de embrague/freno de resorte del desenrollador (spring clutch)</t>
         </is>
       </c>
       <c r="D17" s="22" t="n"/>
@@ -6373,7 +7655,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M17" s="62" t="n"/>
+      <c r="M17" s="67" t="n"/>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="22" t="n"/>
@@ -6381,12 +7663,14 @@
     </row>
     <row r="18" ht="25.05" customHeight="1">
       <c r="A18" s="11" t="n"/>
-      <c r="B18" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de tornillos y sujetadores de estaciones modulares</t>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Revisión del sistema de guía de material (web guide electrónico)</t>
         </is>
       </c>
       <c r="D18" s="22" t="n"/>
@@ -6406,7 +7690,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n"/>
+      <c r="M18" s="21" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
       <c r="P18" s="22" t="n"/>
@@ -6414,12 +7698,14 @@
     </row>
     <row r="19" ht="25.05" customHeight="1">
       <c r="A19" s="11" t="n"/>
-      <c r="B19" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de sellos y protecciones mecánicas</t>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Limpieza general de la máquina y estaciones</t>
         </is>
       </c>
       <c r="D19" s="22" t="n"/>
@@ -6439,7 +7725,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n"/>
+      <c r="M19" s="21" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
       <c r="P19" s="22" t="n"/>
@@ -6447,12 +7733,14 @@
     </row>
     <row r="20" ht="25.05" customHeight="1">
       <c r="A20" s="11" t="n"/>
-      <c r="B20" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>Limpieza general de la máquina y estaciones</t>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Overhaul – desmontaje y mantenimiento mayor</t>
         </is>
       </c>
       <c r="D20" s="22" t="n"/>
@@ -6472,7 +7760,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n"/>
+      <c r="M20" s="21" t="n"/>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
@@ -6480,7 +7768,7 @@
     </row>
     <row r="21" ht="25.05" customHeight="1">
       <c r="A21" s="11" t="n"/>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
@@ -6498,12 +7786,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L21" s="36" t="inlineStr">
+      <c r="L21" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M21" s="36" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -6513,14 +7801,16 @@
       <c r="P21" s="22" t="n"/>
       <c r="Q21" s="23" t="n"/>
     </row>
-    <row r="22" hidden="1" ht="25.05" customHeight="1">
+    <row r="22" ht="25.05" customHeight="1">
       <c r="A22" s="11" t="n"/>
-      <c r="B22" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C22" s="25" t="inlineStr">
-        <is>
-          <t>Verificación voltaje bifásico 220-240VAC (L1-L2) en alimentación principal</t>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Verificación visual del tablero (alarmas e indicadores)</t>
         </is>
       </c>
       <c r="D22" s="22" t="n"/>
@@ -6540,7 +7830,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M22" s="24" t="n"/>
+      <c r="M22" s="21" t="n"/>
       <c r="N22" s="22" t="n"/>
       <c r="O22" s="22" t="n"/>
       <c r="P22" s="22" t="n"/>
@@ -6548,12 +7838,14 @@
     </row>
     <row r="23" ht="25.05" customHeight="1">
       <c r="A23" s="11" t="n"/>
-      <c r="B23" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="C23" s="25" t="inlineStr">
-        <is>
-          <t>Revisión variador Schneider ATV12HU22M2 (A1): temperatura, parámetros y alarmas</t>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Limpieza de tableros eléctricos y revisión de cableado</t>
         </is>
       </c>
       <c r="D23" s="22" t="n"/>
@@ -6573,7 +7865,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M23" s="24" t="n"/>
+      <c r="M23" s="21" t="n"/>
       <c r="N23" s="22" t="n"/>
       <c r="O23" s="22" t="n"/>
       <c r="P23" s="22" t="n"/>
@@ -6581,12 +7873,14 @@
     </row>
     <row r="24" ht="25.05" customHeight="1">
       <c r="A24" s="11" t="n"/>
-      <c r="B24" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C24" s="25" t="inlineStr">
-        <is>
-          <t>Revisión protección de motor Schneider GV2ME14 (QF1): ajuste 4-8A</t>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Reapriete de terminales en tablero eléctrico</t>
         </is>
       </c>
       <c r="D24" s="22" t="n"/>
@@ -6606,20 +7900,22 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
+      <c r="M24" s="21" t="n"/>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
       <c r="P24" s="22" t="n"/>
       <c r="Q24" s="23" t="n"/>
     </row>
-    <row r="25" hidden="1" ht="25.05" customHeight="1">
+    <row r="25" ht="25.05" customHeight="1">
       <c r="A25" s="11" t="n"/>
-      <c r="B25" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="C25" s="25" t="inlineStr">
-        <is>
-          <t>Medición fuente 24VDC Omron S8VK-C06024 (GD1) con multímetro (nominal: 24V ±5%)</t>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de fusibles, contactores y relés térmicos</t>
         </is>
       </c>
       <c r="D25" s="22" t="n"/>
@@ -6639,7 +7935,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M25" s="24" t="n"/>
+      <c r="M25" s="21" t="n"/>
       <c r="N25" s="22" t="n"/>
       <c r="O25" s="22" t="n"/>
       <c r="P25" s="22" t="n"/>
@@ -6647,12 +7943,14 @@
     </row>
     <row r="26" ht="25.05" customHeight="1">
       <c r="A26" s="11" t="n"/>
-      <c r="B26" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C26" s="25" t="inlineStr">
-        <is>
-          <t>Revisión módulos I/O Phoenix Contact (A2): estado de LEDs y conexiones</t>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de motores (temperatura, ruido y vibración)</t>
         </is>
       </c>
       <c r="D26" s="22" t="n"/>
@@ -6672,7 +7970,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M26" s="24" t="n"/>
+      <c r="M26" s="21" t="n"/>
       <c r="N26" s="22" t="n"/>
       <c r="O26" s="22" t="n"/>
       <c r="P26" s="22" t="n"/>
@@ -6680,12 +7978,14 @@
     </row>
     <row r="27" ht="25.05" customHeight="1">
       <c r="A27" s="11" t="n"/>
-      <c r="B27" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C27" s="25" t="inlineStr">
-        <is>
-          <t>Revisión interruptores termomagnéticos Poll Weber 32A 600V</t>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Revisión del servo motor brushless principal</t>
         </is>
       </c>
       <c r="D27" s="22" t="n"/>
@@ -6705,19 +8005,21 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M27" s="58" t="n"/>
-      <c r="N27" s="82" t="n"/>
-      <c r="O27" s="82" t="n"/>
-      <c r="P27" s="82" t="n"/>
-      <c r="Q27" s="83" t="n"/>
+      <c r="M27" s="63" t="n"/>
+      <c r="N27" s="81" t="n"/>
+      <c r="O27" s="81" t="n"/>
+      <c r="P27" s="81" t="n"/>
+      <c r="Q27" s="82" t="n"/>
     </row>
     <row r="28" ht="25.05" customHeight="1">
-      <c r="B28" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>Limpieza y revisión de tablero eléctrico y cableado</t>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de variadores de frecuencia</t>
         </is>
       </c>
       <c r="D28" s="22" t="n"/>
@@ -6737,19 +8039,21 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M28" s="61" t="n"/>
-      <c r="N28" s="45" t="n"/>
-      <c r="O28" s="45" t="n"/>
-      <c r="P28" s="45" t="n"/>
-      <c r="Q28" s="46" t="n"/>
+      <c r="M28" s="66" t="n"/>
+      <c r="N28" s="50" t="n"/>
+      <c r="O28" s="50" t="n"/>
+      <c r="P28" s="50" t="n"/>
+      <c r="Q28" s="51" t="n"/>
     </row>
     <row r="29" ht="25.05" customHeight="1">
-      <c r="B29" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C29" s="25" t="inlineStr">
-        <is>
-          <t>Reapriete de terminales en tablero eléctrico</t>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Prueba funcional de paros de emergencia</t>
         </is>
       </c>
       <c r="D29" s="22" t="n"/>
@@ -6769,19 +8073,21 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M29" s="61" t="n"/>
-      <c r="N29" s="45" t="n"/>
-      <c r="O29" s="45" t="n"/>
-      <c r="P29" s="45" t="n"/>
-      <c r="Q29" s="46" t="n"/>
+      <c r="M29" s="66" t="n"/>
+      <c r="N29" s="50" t="n"/>
+      <c r="O29" s="50" t="n"/>
+      <c r="P29" s="50" t="n"/>
+      <c r="Q29" s="51" t="n"/>
     </row>
     <row r="30" ht="25.05" customHeight="1">
-      <c r="B30" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>Prueba funcional pantalla táctil HMI Guidolin Girotto (Software v.1.02)</t>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de tierras físicas y continuidad</t>
         </is>
       </c>
       <c r="D30" s="22" t="n"/>
@@ -6801,19 +8107,21 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M30" s="61" t="n"/>
-      <c r="N30" s="45" t="n"/>
-      <c r="O30" s="45" t="n"/>
-      <c r="P30" s="45" t="n"/>
-      <c r="Q30" s="46" t="n"/>
+      <c r="M30" s="66" t="n"/>
+      <c r="N30" s="50" t="n"/>
+      <c r="O30" s="50" t="n"/>
+      <c r="P30" s="50" t="n"/>
+      <c r="Q30" s="51" t="n"/>
     </row>
     <row r="31" ht="25.05" customHeight="1">
-      <c r="B31" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>Prueba de ciclo START/STOP desde panel de operador HMI</t>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Termografía de tableros y conexiones</t>
         </is>
       </c>
       <c r="D31" s="22" t="n"/>
@@ -6833,19 +8141,21 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M31" s="61" t="n"/>
-      <c r="N31" s="45" t="n"/>
-      <c r="O31" s="45" t="n"/>
-      <c r="P31" s="45" t="n"/>
-      <c r="Q31" s="46" t="n"/>
+      <c r="M31" s="66" t="n"/>
+      <c r="N31" s="50" t="n"/>
+      <c r="O31" s="50" t="n"/>
+      <c r="P31" s="50" t="n"/>
+      <c r="Q31" s="51" t="n"/>
     </row>
     <row r="32" ht="25.05" customHeight="1">
-      <c r="B32" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C32" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de tierras físicas y continuidad</t>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Revisión del sensor ultrasónico/sonar de tensión de material</t>
         </is>
       </c>
       <c r="D32" s="22" t="n"/>
@@ -6865,19 +8175,21 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M32" s="61" t="n"/>
-      <c r="N32" s="45" t="n"/>
-      <c r="O32" s="45" t="n"/>
-      <c r="P32" s="45" t="n"/>
-      <c r="Q32" s="46" t="n"/>
+      <c r="M32" s="66" t="n"/>
+      <c r="N32" s="50" t="n"/>
+      <c r="O32" s="50" t="n"/>
+      <c r="P32" s="50" t="n"/>
+      <c r="Q32" s="51" t="n"/>
     </row>
     <row r="33" ht="25.05" customHeight="1">
-      <c r="B33" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>Prueba funcional de paros de emergencia y dispositivos de seguridad</t>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de pantalla táctil (PLC 4") y respaldo de trabajos guardados</t>
         </is>
       </c>
       <c r="D33" s="22" t="n"/>
@@ -6897,15 +8209,15 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M33" s="61" t="n"/>
-      <c r="N33" s="45" t="n"/>
-      <c r="O33" s="45" t="n"/>
-      <c r="P33" s="45" t="n"/>
-      <c r="Q33" s="46" t="n"/>
+      <c r="M33" s="66" t="n"/>
+      <c r="N33" s="50" t="n"/>
+      <c r="O33" s="50" t="n"/>
+      <c r="P33" s="50" t="n"/>
+      <c r="Q33" s="51" t="n"/>
     </row>
     <row r="34" ht="17.4" customHeight="1">
       <c r="A34" s="11" t="n"/>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
@@ -6921,7 +8233,7 @@
       <c r="K34" s="22" t="n"/>
       <c r="L34" s="22" t="n"/>
       <c r="M34" s="23" t="n"/>
-      <c r="N34" s="33" t="inlineStr">
+      <c r="N34" s="43" t="inlineStr">
         <is>
           <t>VOLTAJE ALIMENTACIÓN</t>
         </is>
@@ -6994,16 +8306,24 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>L1-L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>VDC</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="n"/>
-      <c r="Q35" s="6" t="n"/>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>VAC</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17.4" customHeight="1">
       <c r="A36" s="11" t="n"/>
@@ -7074,38 +8394,38 @@
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="11" t="n"/>
-      <c r="B37" s="70" t="inlineStr">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C37" s="45" t="n"/>
-      <c r="D37" s="45" t="n"/>
-      <c r="E37" s="45" t="n"/>
-      <c r="F37" s="45" t="n"/>
-      <c r="G37" s="46" t="n"/>
-      <c r="H37" s="84" t="inlineStr">
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+      <c r="E37" s="50" t="n"/>
+      <c r="F37" s="50" t="n"/>
+      <c r="G37" s="51" t="n"/>
+      <c r="H37" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
       <c r="I37" s="75" t="n"/>
       <c r="J37" s="75" t="n"/>
-      <c r="K37" s="72" t="inlineStr">
+      <c r="K37" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L37" s="45" t="n"/>
-      <c r="M37" s="45" t="n"/>
-      <c r="N37" s="45" t="n"/>
-      <c r="O37" s="45" t="n"/>
-      <c r="P37" s="45" t="n"/>
-      <c r="Q37" s="46" t="n"/>
+      <c r="L37" s="50" t="n"/>
+      <c r="M37" s="50" t="n"/>
+      <c r="N37" s="50" t="n"/>
+      <c r="O37" s="50" t="n"/>
+      <c r="P37" s="50" t="n"/>
+      <c r="Q37" s="51" t="n"/>
     </row>
     <row r="38" ht="14.4" customHeight="1">
-      <c r="B38" s="70" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -7115,7 +8435,7 @@
       <c r="E38" s="76" t="n"/>
       <c r="F38" s="76" t="n"/>
       <c r="G38" s="77" t="n"/>
-      <c r="K38" s="70" t="inlineStr">
+      <c r="K38" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -7160,8 +8480,8 @@
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="C25:J25"/>
     <mergeCell ref="C20:J20"/>
-    <mergeCell ref="C25:J25"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="C16:J16"/>
     <mergeCell ref="E3:N3"/>
@@ -7172,19 +8492,19 @@
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="M13:Q13"/>
     <mergeCell ref="M31:Q31"/>
+    <mergeCell ref="C9:J9"/>
     <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="C9:J9"/>
     <mergeCell ref="M16:Q16"/>
     <mergeCell ref="H37:J39"/>
     <mergeCell ref="J4:Q4"/>
+    <mergeCell ref="M12:Q12"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="M30:Q30"/>
-    <mergeCell ref="M25:Q25"/>
     <mergeCell ref="M15:Q15"/>
     <mergeCell ref="B38:G39"/>
-    <mergeCell ref="M12:Q12"/>
     <mergeCell ref="M21:Q21"/>
     <mergeCell ref="C11:J11"/>
+    <mergeCell ref="M25:Q25"/>
     <mergeCell ref="M33:Q33"/>
     <mergeCell ref="M28:Q28"/>
     <mergeCell ref="B4:I4"/>
@@ -7209,10 +8529,10 @@
     <mergeCell ref="M23:Q23"/>
     <mergeCell ref="M32:Q32"/>
     <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="B5:I5"/>
     <mergeCell ref="C28:J28"/>
-    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="C13:J13"/>
     <mergeCell ref="C19:J19"/>
-    <mergeCell ref="C13:J13"/>
     <mergeCell ref="M19:Q19"/>
     <mergeCell ref="B21:J21"/>
     <mergeCell ref="C18:J18"/>
@@ -7238,7 +8558,7 @@
     <row r="1" ht="7.8" customHeight="1"/>
     <row r="2" ht="56.55" customHeight="1">
       <c r="A2" s="11" t="n"/>
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
@@ -7255,22 +8575,22 @@
       <c r="L2" s="22" t="n"/>
       <c r="M2" s="22" t="n"/>
       <c r="N2" s="23" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>No. de Documento             A9.I1.F2
-Revision:                                    00
-Fecha:                        08/06/2026</t>
-        </is>
-      </c>
-      <c r="P2" s="22" t="n"/>
-      <c r="Q2" s="23" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
       <c r="A3" s="11" t="n"/>
-      <c r="B3" s="38" t="n"/>
+      <c r="B3" s="36" t="n"/>
       <c r="C3" s="22" t="n"/>
       <c r="D3" s="23" t="n"/>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="38" t="inlineStr">
         <is>
           <t>MANTENIMIENTO PREVENTIVO   —   PRENSA PL</t>
         </is>
@@ -7290,7 +8610,7 @@
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
@@ -7302,7 +8622,7 @@
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
       <c r="I4" s="23" t="n"/>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
@@ -7317,7 +8637,7 @@
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
@@ -7329,7 +8649,7 @@
       <c r="G5" s="22" t="n"/>
       <c r="H5" s="22" t="n"/>
       <c r="I5" s="23" t="n"/>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
@@ -7344,7 +8664,7 @@
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Nombre de máquina  Prensa PL</t>
         </is>
@@ -7356,7 +8676,7 @@
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="23" t="n"/>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Número de máquina:  PL01</t>
         </is>
@@ -7371,7 +8691,7 @@
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO / HIDRÁULICO</t>
         </is>
@@ -7389,12 +8709,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -7411,7 +8731,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Inspección visual de estructura, cilindros y mangueras</t>
         </is>
@@ -7433,7 +8753,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M8" s="24" t="n"/>
+      <c r="M8" s="21" t="n"/>
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="22" t="n"/>
@@ -7446,7 +8766,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Verificación de nivel y calidad del aceite hidráulico</t>
         </is>
@@ -7468,7 +8788,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M9" s="24" t="n"/>
+      <c r="M9" s="21" t="n"/>
       <c r="N9" s="22" t="n"/>
       <c r="O9" s="22" t="n"/>
       <c r="P9" s="22" t="n"/>
@@ -7481,7 +8801,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Revisión de cilindros hidráulicos (vástagos, sellos y fugas)</t>
         </is>
@@ -7503,7 +8823,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M10" s="24" t="n"/>
+      <c r="M10" s="21" t="n"/>
       <c r="N10" s="22" t="n"/>
       <c r="O10" s="22" t="n"/>
       <c r="P10" s="22" t="n"/>
@@ -7516,7 +8836,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Limpieza de filtro de aceite hidráulico</t>
         </is>
@@ -7538,7 +8858,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M11" s="24" t="n"/>
+      <c r="M11" s="21" t="n"/>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="22" t="n"/>
       <c r="P11" s="22" t="n"/>
@@ -7551,7 +8871,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Revisión de bomba hidráulica (ruido y temperatura)</t>
         </is>
@@ -7573,7 +8893,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M12" s="24" t="n"/>
+      <c r="M12" s="21" t="n"/>
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
       <c r="P12" s="22" t="n"/>
@@ -7586,7 +8906,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Revisión de sistema de cierre y apertura de molde</t>
         </is>
@@ -7608,7 +8928,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M13" s="24" t="n"/>
+      <c r="M13" s="21" t="n"/>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="22" t="n"/>
       <c r="P13" s="22" t="n"/>
@@ -7621,7 +8941,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Verificación de paralelismo de platinas</t>
         </is>
@@ -7643,7 +8963,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M14" s="24" t="n"/>
+      <c r="M14" s="21" t="n"/>
       <c r="N14" s="22" t="n"/>
       <c r="O14" s="22" t="n"/>
       <c r="P14" s="22" t="n"/>
@@ -7656,7 +8976,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Lubricación de guías y columnas de la prensa</t>
         </is>
@@ -7678,7 +8998,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M15" s="24" t="n"/>
+      <c r="M15" s="21" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
       <c r="P15" s="22" t="n"/>
@@ -7691,7 +9011,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Verificación de tornillería y fijaciones estructurales</t>
         </is>
@@ -7713,7 +9033,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M16" s="24" t="n"/>
+      <c r="M16" s="21" t="n"/>
       <c r="N16" s="22" t="n"/>
       <c r="O16" s="22" t="n"/>
       <c r="P16" s="22" t="n"/>
@@ -7726,7 +9046,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C17" s="53" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>Cambio de aceite hidráulico (programado)</t>
         </is>
@@ -7738,17 +9058,17 @@
       <c r="H17" s="22" t="n"/>
       <c r="I17" s="22" t="n"/>
       <c r="J17" s="23" t="n"/>
-      <c r="K17" s="62" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L17" s="62" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M17" s="62" t="n"/>
+      <c r="K17" s="67" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L17" s="67" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M17" s="67" t="n"/>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="22" t="n"/>
@@ -7756,12 +9076,12 @@
     </row>
     <row r="18" ht="25.05" customHeight="1">
       <c r="A18" s="11" t="n"/>
-      <c r="B18" s="65" t="inlineStr">
+      <c r="B18" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
       </c>
-      <c r="C18" s="68" t="n"/>
+      <c r="C18" s="70" t="n"/>
       <c r="D18" s="22" t="n"/>
       <c r="E18" s="22" t="n"/>
       <c r="F18" s="22" t="n"/>
@@ -7774,12 +9094,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L18" s="36" t="inlineStr">
+      <c r="L18" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M18" s="36" t="inlineStr">
+      <c r="M18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -7796,7 +9116,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>Verificación visual del tablero (alarmas e indicadores)</t>
         </is>
@@ -7818,7 +9138,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n"/>
+      <c r="M19" s="21" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
       <c r="P19" s="22" t="n"/>
@@ -7831,7 +9151,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Limpieza de tableros eléctricos y revisión de cableado</t>
         </is>
@@ -7853,7 +9173,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n"/>
+      <c r="M20" s="21" t="n"/>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
@@ -7866,7 +9186,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>Reapriete de terminales en tablero eléctrico</t>
         </is>
@@ -7888,7 +9208,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M21" s="24" t="n"/>
+      <c r="M21" s="21" t="n"/>
       <c r="N21" s="22" t="n"/>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="22" t="n"/>
@@ -7901,7 +9221,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Verificación de fusibles, contactores y relés térmicos</t>
         </is>
@@ -7923,7 +9243,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M22" s="24" t="n"/>
+      <c r="M22" s="21" t="n"/>
       <c r="N22" s="22" t="n"/>
       <c r="O22" s="22" t="n"/>
       <c r="P22" s="22" t="n"/>
@@ -7936,7 +9256,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>Revisión de motores (temperatura, ruido y vibración)</t>
         </is>
@@ -7958,7 +9278,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M23" s="24" t="n"/>
+      <c r="M23" s="21" t="n"/>
       <c r="N23" s="22" t="n"/>
       <c r="O23" s="22" t="n"/>
       <c r="P23" s="22" t="n"/>
@@ -7971,7 +9291,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Revisión de sensores de posición y finales de carrera</t>
         </is>
@@ -7993,7 +9313,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
+      <c r="M24" s="21" t="n"/>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
       <c r="P24" s="22" t="n"/>
@@ -8006,7 +9326,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>Revisión de dispositivos de seguridad</t>
         </is>
@@ -8028,7 +9348,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M25" s="24" t="n"/>
+      <c r="M25" s="21" t="n"/>
       <c r="N25" s="22" t="n"/>
       <c r="O25" s="22" t="n"/>
       <c r="P25" s="22" t="n"/>
@@ -8041,7 +9361,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Prueba funcional de paros de emergencia</t>
         </is>
@@ -8063,7 +9383,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M26" s="24" t="n"/>
+      <c r="M26" s="21" t="n"/>
       <c r="N26" s="22" t="n"/>
       <c r="O26" s="22" t="n"/>
       <c r="P26" s="22" t="n"/>
@@ -8076,7 +9396,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>Verificación de tierras físicas y continuidad</t>
         </is>
@@ -8098,7 +9418,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M27" s="24" t="n"/>
+      <c r="M27" s="21" t="n"/>
       <c r="N27" s="22" t="n"/>
       <c r="O27" s="22" t="n"/>
       <c r="P27" s="22" t="n"/>
@@ -8111,7 +9431,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>Termografía de tableros y conexiones</t>
         </is>
@@ -8123,17 +9443,17 @@
       <c r="H28" s="22" t="n"/>
       <c r="I28" s="22" t="n"/>
       <c r="J28" s="23" t="n"/>
-      <c r="K28" s="50" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L28" s="50" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M28" s="50" t="n"/>
+      <c r="K28" s="52" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L28" s="52" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M28" s="52" t="n"/>
       <c r="N28" s="22" t="n"/>
       <c r="O28" s="22" t="n"/>
       <c r="P28" s="22" t="n"/>
@@ -8141,7 +9461,7 @@
     </row>
     <row r="29" ht="25.05" customHeight="1">
       <c r="A29" s="11" t="n"/>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
@@ -8157,7 +9477,7 @@
       <c r="K29" s="22" t="n"/>
       <c r="L29" s="22" t="n"/>
       <c r="M29" s="23" t="n"/>
-      <c r="N29" s="33" t="inlineStr">
+      <c r="N29" s="43" t="inlineStr">
         <is>
           <t>VOLTAJE ALIMENTACIÓN</t>
         </is>
@@ -8318,38 +9638,38 @@
     </row>
     <row r="32" ht="25.05" customHeight="1">
       <c r="A32" s="11" t="n"/>
-      <c r="B32" s="70" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C32" s="45" t="n"/>
-      <c r="D32" s="45" t="n"/>
-      <c r="E32" s="45" t="n"/>
-      <c r="F32" s="45" t="n"/>
-      <c r="G32" s="46" t="n"/>
-      <c r="H32" s="71" t="inlineStr">
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+      <c r="E32" s="50" t="n"/>
+      <c r="F32" s="50" t="n"/>
+      <c r="G32" s="51" t="n"/>
+      <c r="H32" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
       <c r="I32" s="75" t="n"/>
       <c r="J32" s="75" t="n"/>
-      <c r="K32" s="72" t="inlineStr">
+      <c r="K32" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L32" s="45" t="n"/>
-      <c r="M32" s="45" t="n"/>
-      <c r="N32" s="45" t="n"/>
-      <c r="O32" s="45" t="n"/>
-      <c r="P32" s="45" t="n"/>
-      <c r="Q32" s="46" t="n"/>
+      <c r="L32" s="50" t="n"/>
+      <c r="M32" s="50" t="n"/>
+      <c r="N32" s="50" t="n"/>
+      <c r="O32" s="50" t="n"/>
+      <c r="P32" s="50" t="n"/>
+      <c r="Q32" s="51" t="n"/>
     </row>
     <row r="33" ht="25.05" customHeight="1">
-      <c r="B33" s="70" t="inlineStr">
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -8359,7 +9679,7 @@
       <c r="E33" s="76" t="n"/>
       <c r="F33" s="76" t="n"/>
       <c r="G33" s="77" t="n"/>
-      <c r="K33" s="70" t="inlineStr">
+      <c r="K33" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -8388,6 +9708,7 @@
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="B33:G34"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C24:J24"/>
     <mergeCell ref="J5:Q5"/>
@@ -8443,13 +9764,12 @@
     <mergeCell ref="M14:Q14"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C13:J13"/>
     <mergeCell ref="C19:J19"/>
-    <mergeCell ref="C13:J13"/>
     <mergeCell ref="M19:Q19"/>
     <mergeCell ref="N29:Q29"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="C18:J18"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B33:G34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -8473,7 +9793,7 @@
     <row r="1" ht="7.8" customHeight="1"/>
     <row r="2" ht="56.55" customHeight="1">
       <c r="A2" s="11" t="n"/>
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
@@ -8490,22 +9810,22 @@
       <c r="L2" s="22" t="n"/>
       <c r="M2" s="22" t="n"/>
       <c r="N2" s="23" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>No. de Documento             A9.I1.F2
-Revision:                                    00
-Fecha:                        08/06/2026</t>
-        </is>
-      </c>
-      <c r="P2" s="22" t="n"/>
-      <c r="Q2" s="23" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
       <c r="A3" s="11" t="n"/>
-      <c r="B3" s="38" t="n"/>
+      <c r="B3" s="36" t="n"/>
       <c r="C3" s="22" t="n"/>
       <c r="D3" s="23" t="n"/>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="38" t="inlineStr">
         <is>
           <t>MANTENIMIENTO PREVENTIVO   —   IMESA – CORTADORA</t>
         </is>
@@ -8525,7 +9845,7 @@
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
@@ -8537,7 +9857,7 @@
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
       <c r="I4" s="23" t="n"/>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
@@ -8552,7 +9872,7 @@
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
@@ -8564,7 +9884,7 @@
       <c r="G5" s="22" t="n"/>
       <c r="H5" s="22" t="n"/>
       <c r="I5" s="23" t="n"/>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
@@ -8579,7 +9899,7 @@
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Nombre de máquina:  Imesa 558</t>
         </is>
@@ -8591,7 +9911,7 @@
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="23" t="n"/>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Número de máquina:  IM01</t>
         </is>
@@ -8606,7 +9926,7 @@
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO</t>
         </is>
@@ -8624,12 +9944,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -8646,7 +9966,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Inspección visual: ruidos, vibraciones y fugas</t>
         </is>
@@ -8668,7 +9988,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M8" s="24" t="n"/>
+      <c r="M8" s="21" t="n"/>
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="22" t="n"/>
@@ -8681,7 +10001,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Revisión de cuchilla (filo, estado y sujeción)</t>
         </is>
@@ -8703,7 +10023,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M9" s="24" t="n"/>
+      <c r="M9" s="21" t="n"/>
       <c r="N9" s="22" t="n"/>
       <c r="O9" s="22" t="n"/>
       <c r="P9" s="22" t="n"/>
@@ -8716,7 +10036,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Revisión de contracuchilla (desgaste y alineación)</t>
         </is>
@@ -8738,7 +10058,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M10" s="24" t="n"/>
+      <c r="M10" s="21" t="n"/>
       <c r="N10" s="22" t="n"/>
       <c r="O10" s="22" t="n"/>
       <c r="P10" s="22" t="n"/>
@@ -8751,7 +10071,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Lubricación de guías y mecanismo de corte</t>
         </is>
@@ -8773,7 +10093,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M11" s="24" t="n"/>
+      <c r="M11" s="21" t="n"/>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="22" t="n"/>
       <c r="P11" s="22" t="n"/>
@@ -8786,7 +10106,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Revisión de sistema de presión de sujetador de material</t>
         </is>
@@ -8808,7 +10128,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M12" s="24" t="n"/>
+      <c r="M12" s="21" t="n"/>
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
       <c r="P12" s="22" t="n"/>
@@ -8821,7 +10141,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Verificación de mesa y guías de alimentación</t>
         </is>
@@ -8843,7 +10163,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M13" s="24" t="n"/>
+      <c r="M13" s="21" t="n"/>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="22" t="n"/>
       <c r="P13" s="22" t="n"/>
@@ -8856,7 +10176,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Verificación de tornillería y fijaciones estructurales</t>
         </is>
@@ -8878,7 +10198,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M14" s="24" t="n"/>
+      <c r="M14" s="21" t="n"/>
       <c r="N14" s="22" t="n"/>
       <c r="O14" s="22" t="n"/>
       <c r="P14" s="22" t="n"/>
@@ -8891,7 +10211,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Afilado o cambio de cuchilla (según desgaste)</t>
         </is>
@@ -8913,7 +10233,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M15" s="24" t="n"/>
+      <c r="M15" s="21" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
       <c r="P15" s="22" t="n"/>
@@ -8921,7 +10241,7 @@
     </row>
     <row r="16" ht="25.05" customHeight="1">
       <c r="A16" s="11" t="n"/>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
@@ -8939,12 +10259,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L16" s="36" t="inlineStr">
+      <c r="L16" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M16" s="36" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -8961,7 +10281,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Verificación visual del tablero (alarmas e indicadores)</t>
         </is>
@@ -8983,7 +10303,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M17" s="24" t="n"/>
+      <c r="M17" s="21" t="n"/>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="22" t="n"/>
@@ -8996,7 +10316,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>Reapriete de terminales en tablero eléctrico</t>
         </is>
@@ -9018,7 +10338,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n"/>
+      <c r="M18" s="21" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
       <c r="P18" s="22" t="n"/>
@@ -9031,7 +10351,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>Revisión de motores (temperatura, ruido y vibración)</t>
         </is>
@@ -9053,7 +10373,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n"/>
+      <c r="M19" s="21" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
       <c r="P19" s="22" t="n"/>
@@ -9066,7 +10386,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>Revisión de dispositivos de seguridad y paro de emergencia</t>
         </is>
@@ -9088,7 +10408,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n"/>
+      <c r="M20" s="21" t="n"/>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
@@ -9101,7 +10421,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C21" s="25" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>Prueba funcional de paros de emergencia</t>
         </is>
@@ -9123,7 +10443,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M21" s="24" t="n"/>
+      <c r="M21" s="21" t="n"/>
       <c r="N21" s="22" t="n"/>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="22" t="n"/>
@@ -9136,7 +10456,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Verificación de tierras físicas y continuidad</t>
         </is>
@@ -9158,7 +10478,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M22" s="24" t="n"/>
+      <c r="M22" s="21" t="n"/>
       <c r="N22" s="22" t="n"/>
       <c r="O22" s="22" t="n"/>
       <c r="P22" s="22" t="n"/>
@@ -9166,7 +10486,7 @@
     </row>
     <row r="23" ht="25.05" customHeight="1">
       <c r="A23" s="11" t="n"/>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  NEUMÁTICO</t>
         </is>
@@ -9184,12 +10504,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L23" s="36" t="inlineStr">
+      <c r="L23" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M23" s="36" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -9206,7 +10526,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Verificación de presión de trabajo neumático</t>
         </is>
@@ -9228,7 +10548,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
+      <c r="M24" s="21" t="n"/>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
       <c r="P24" s="22" t="n"/>
@@ -9241,7 +10561,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>Inspección de mangueras, racores y cilindros neumáticos</t>
         </is>
@@ -9263,7 +10583,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M25" s="24" t="n"/>
+      <c r="M25" s="21" t="n"/>
       <c r="N25" s="22" t="n"/>
       <c r="O25" s="22" t="n"/>
       <c r="P25" s="22" t="n"/>
@@ -9276,7 +10596,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Limpieza/cambio de filtros FRL</t>
         </is>
@@ -9298,7 +10618,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M26" s="24" t="n"/>
+      <c r="M26" s="21" t="n"/>
       <c r="N26" s="22" t="n"/>
       <c r="O26" s="22" t="n"/>
       <c r="P26" s="22" t="n"/>
@@ -9311,7 +10631,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>Revisión y ajuste de válvulas solenoides</t>
         </is>
@@ -9333,7 +10653,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M27" s="24" t="n"/>
+      <c r="M27" s="21" t="n"/>
       <c r="N27" s="22" t="n"/>
       <c r="O27" s="22" t="n"/>
       <c r="P27" s="22" t="n"/>
@@ -9341,7 +10661,7 @@
     </row>
     <row r="28" ht="25.05" customHeight="1">
       <c r="A28" s="11" t="n"/>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
@@ -9357,7 +10677,7 @@
       <c r="K28" s="22" t="n"/>
       <c r="L28" s="22" t="n"/>
       <c r="M28" s="23" t="n"/>
-      <c r="N28" s="33" t="inlineStr">
+      <c r="N28" s="43" t="inlineStr">
         <is>
           <t>VOLTAJE ALIMENTACIÓN</t>
         </is>
@@ -9518,38 +10838,38 @@
     </row>
     <row r="31" ht="25.05" customHeight="1">
       <c r="A31" s="11" t="n"/>
-      <c r="B31" s="70" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="45" t="n"/>
-      <c r="F31" s="45" t="n"/>
-      <c r="G31" s="46" t="n"/>
-      <c r="H31" s="71" t="inlineStr">
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+      <c r="E31" s="50" t="n"/>
+      <c r="F31" s="50" t="n"/>
+      <c r="G31" s="51" t="n"/>
+      <c r="H31" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
       <c r="I31" s="75" t="n"/>
       <c r="J31" s="75" t="n"/>
-      <c r="K31" s="72" t="inlineStr">
+      <c r="K31" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L31" s="45" t="n"/>
-      <c r="M31" s="45" t="n"/>
-      <c r="N31" s="45" t="n"/>
-      <c r="O31" s="45" t="n"/>
-      <c r="P31" s="45" t="n"/>
-      <c r="Q31" s="46" t="n"/>
+      <c r="L31" s="50" t="n"/>
+      <c r="M31" s="50" t="n"/>
+      <c r="N31" s="50" t="n"/>
+      <c r="O31" s="50" t="n"/>
+      <c r="P31" s="50" t="n"/>
+      <c r="Q31" s="51" t="n"/>
     </row>
     <row r="32" ht="25.05" customHeight="1">
-      <c r="B32" s="70" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -9559,7 +10879,7 @@
       <c r="E32" s="76" t="n"/>
       <c r="F32" s="76" t="n"/>
       <c r="G32" s="77" t="n"/>
-      <c r="K32" s="70" t="inlineStr">
+      <c r="K32" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -9660,1195 +10980,1020 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Q33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="B1:N42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.5546875" customWidth="1" min="1" max="1"/>
-    <col width="12.77734375" customWidth="1" min="2" max="17"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="7.8" customHeight="1"/>
-    <row r="2" ht="56.55" customHeight="1">
-      <c r="A2" s="11" t="n"/>
-      <c r="B2" s="37" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="B1" s="83" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
       </c>
-      <c r="C2" s="22" t="n"/>
-      <c r="D2" s="22" t="n"/>
-      <c r="E2" s="22" t="n"/>
-      <c r="F2" s="22" t="n"/>
-      <c r="G2" s="22" t="n"/>
-      <c r="H2" s="22" t="n"/>
-      <c r="I2" s="22" t="n"/>
-      <c r="J2" s="22" t="n"/>
-      <c r="K2" s="22" t="n"/>
-      <c r="L2" s="22" t="n"/>
-      <c r="M2" s="22" t="n"/>
-      <c r="N2" s="23" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>No. de Documento             A9.I1.F2
-Revision:                                    00
-Fecha:                        08/06/2026</t>
-        </is>
-      </c>
-      <c r="P2" s="22" t="n"/>
-      <c r="Q2" s="23" t="n"/>
-    </row>
-    <row r="3" ht="97.8" customHeight="1">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="38" t="n"/>
-      <c r="C3" s="22" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="69" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO PREVENTIVO      SINGLE KNIFE 
-CORTADORA DE CUCHILLA ÚNICA</t>
-        </is>
-      </c>
-      <c r="F3" s="22" t="n"/>
-      <c r="G3" s="22" t="n"/>
-      <c r="H3" s="22" t="n"/>
-      <c r="I3" s="22" t="n"/>
-      <c r="J3" s="22" t="n"/>
-      <c r="K3" s="22" t="n"/>
-      <c r="L3" s="22" t="n"/>
-      <c r="M3" s="22" t="n"/>
-      <c r="N3" s="23" t="n"/>
-      <c r="O3" s="35" t="n"/>
-      <c r="P3" s="22" t="n"/>
-      <c r="Q3" s="23" t="n"/>
-    </row>
-    <row r="4" ht="25.05" customHeight="1">
-      <c r="A4" s="11" t="n"/>
-      <c r="B4" s="39" t="inlineStr">
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="84" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO PREVENTIVO   —   CALENDER K1 EASY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="B3" s="85" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
       </c>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n"/>
-      <c r="E4" s="22" t="n"/>
-      <c r="F4" s="22" t="n"/>
-      <c r="G4" s="22" t="n"/>
-      <c r="H4" s="22" t="n"/>
-      <c r="I4" s="23" t="n"/>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="I3" s="85" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
       </c>
-      <c r="K4" s="22" t="n"/>
-      <c r="L4" s="22" t="n"/>
-      <c r="M4" s="22" t="n"/>
-      <c r="N4" s="22" t="n"/>
-      <c r="O4" s="22" t="n"/>
-      <c r="P4" s="22" t="n"/>
-      <c r="Q4" s="23" t="n"/>
-    </row>
-    <row r="5" ht="46.2" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="39" t="inlineStr">
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="85" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="22" t="n"/>
-      <c r="G5" s="22" t="n"/>
-      <c r="H5" s="22" t="n"/>
-      <c r="I5" s="23" t="n"/>
-      <c r="J5" s="32" t="inlineStr">
-        <is>
-          <t>Indicaciones: Usar equipo de seguridad.</t>
-        </is>
-      </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="22" t="n"/>
-      <c r="M5" s="22" t="n"/>
-      <c r="N5" s="22" t="n"/>
-      <c r="O5" s="22" t="n"/>
-      <c r="P5" s="22" t="n"/>
-      <c r="Q5" s="23" t="n"/>
-    </row>
-    <row r="6" ht="25.05" customHeight="1">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>Nombre de máquina:  Cuchilla Simple</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="n"/>
-      <c r="H6" s="22" t="n"/>
-      <c r="I6" s="23" t="n"/>
-      <c r="J6" s="32" t="inlineStr">
-        <is>
-          <t>Número de máquina:  SK01</t>
-        </is>
-      </c>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="22" t="n"/>
-      <c r="M6" s="22" t="n"/>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="22" t="n"/>
-      <c r="P6" s="22" t="n"/>
-      <c r="Q6" s="23" t="n"/>
-    </row>
-    <row r="7" ht="25.05" customHeight="1">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="I4" s="85" t="inlineStr">
+        <is>
+          <t>Indicaciones: Usar EPP. Para revisiones eléctricas: PARO TOTAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="85" t="inlineStr">
+        <is>
+          <t>Nombre de máquina:  Calender K1 Easy</t>
+        </is>
+      </c>
+      <c r="I5" s="85" t="inlineStr">
+        <is>
+          <t>Número de máquina:  K1-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="B6" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="23" t="n"/>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K6" s="87" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L6" s="87" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMENTARIOS </t>
-        </is>
-      </c>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="23" t="n"/>
-    </row>
-    <row r="8" ht="25.05" customHeight="1">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="M6" s="87" t="inlineStr">
+        <is>
+          <t>COMENTARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="88" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>Inspección visual: ruidos, vibraciones y fugas</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="23" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M8" s="24" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="22" t="n"/>
-      <c r="P8" s="22" t="n"/>
-      <c r="Q8" s="23" t="n"/>
-    </row>
-    <row r="9" ht="25.05" customHeight="1">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="C7" s="89" t="inlineStr">
+        <is>
+          <t>Inspección visual: ruidos, vibraciones y fugas en rodillos</t>
+        </is>
+      </c>
+      <c r="K7" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L7" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M7" s="91" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="92" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Inspección de cuchilla (filo, estado y sujeción)</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M9" s="24" t="n"/>
-      <c r="N9" s="22" t="n"/>
-      <c r="O9" s="22" t="n"/>
-      <c r="P9" s="22" t="n"/>
-      <c r="Q9" s="23" t="n"/>
-    </row>
-    <row r="10" ht="25.05" customHeight="1">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="C8" s="93" t="inlineStr">
+        <is>
+          <t>Lubricación de rodillos de calandria (baleros y chumaceras)</t>
+        </is>
+      </c>
+      <c r="K8" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L8" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M8" s="95" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="88" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de guía trasera y escuadras de corte</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="23" t="n"/>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M10" s="24" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="22" t="n"/>
-      <c r="P10" s="22" t="n"/>
-      <c r="Q10" s="23" t="n"/>
-    </row>
-    <row r="11" ht="25.05" customHeight="1">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="C9" s="89" t="inlineStr">
+        <is>
+          <t>Revisión y lubricación de cadena de transmisión y sprockets</t>
+        </is>
+      </c>
+      <c r="K9" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L9" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M9" s="91" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="92" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>Lubricación de guías y mecanismo de corte</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="22" t="n"/>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M11" s="24" t="n"/>
-      <c r="N11" s="22" t="n"/>
-      <c r="O11" s="22" t="n"/>
-      <c r="P11" s="22" t="n"/>
-      <c r="Q11" s="23" t="n"/>
-    </row>
-    <row r="12" ht="25.05" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="C10" s="93" t="inlineStr">
+        <is>
+          <t>Verificación de tensión de cadena (deflexión máx. 1% de longitud)</t>
+        </is>
+      </c>
+      <c r="K10" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L10" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M10" s="95" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="88" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de sistema de presión neumática sujetador</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="22" t="n"/>
-      <c r="I12" s="22" t="n"/>
-      <c r="J12" s="23" t="n"/>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M12" s="24" t="n"/>
-      <c r="N12" s="22" t="n"/>
-      <c r="O12" s="22" t="n"/>
-      <c r="P12" s="22" t="n"/>
-      <c r="Q12" s="23" t="n"/>
-    </row>
-    <row r="13" ht="25.05" customHeight="1">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="C11" s="89" t="inlineStr">
+        <is>
+          <t>Revisión de caja reductora: nivel y calidad de aceite</t>
+        </is>
+      </c>
+      <c r="K11" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L11" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M11" s="91" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="92" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>Verificación de mesa de trabajo y alineación</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="22" t="n"/>
-      <c r="I13" s="22" t="n"/>
-      <c r="J13" s="23" t="n"/>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M13" s="24" t="n"/>
-      <c r="N13" s="22" t="n"/>
-      <c r="O13" s="22" t="n"/>
-      <c r="P13" s="22" t="n"/>
-      <c r="Q13" s="23" t="n"/>
-    </row>
-    <row r="14" ht="25.05" customHeight="1">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="C12" s="93" t="inlineStr">
+        <is>
+          <t>Verificación de alineación y paralelismo de rodillos</t>
+        </is>
+      </c>
+      <c r="K12" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L12" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M12" s="95" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="88" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de tornillería y fijaciones estructurales</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="22" t="n"/>
-      <c r="I14" s="22" t="n"/>
-      <c r="J14" s="23" t="n"/>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M14" s="24" t="n"/>
-      <c r="N14" s="22" t="n"/>
-      <c r="O14" s="22" t="n"/>
-      <c r="P14" s="22" t="n"/>
-      <c r="Q14" s="23" t="n"/>
-    </row>
-    <row r="15" ht="25.05" customHeight="1">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="C13" s="89" t="inlineStr">
+        <is>
+          <t>Limpieza de rodillos y superficie de contacto (residuos de material)</t>
+        </is>
+      </c>
+      <c r="K13" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L13" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M13" s="91" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="92" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>Afilado o cambio de cuchilla (según desgaste)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="22" t="n"/>
-      <c r="J15" s="23" t="n"/>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M15" s="24" t="n"/>
-      <c r="N15" s="22" t="n"/>
-      <c r="O15" s="22" t="n"/>
-      <c r="P15" s="22" t="n"/>
-      <c r="Q15" s="23" t="n"/>
-    </row>
-    <row r="16" ht="25.05" customHeight="1">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="C14" s="93" t="inlineStr">
+        <is>
+          <t>Revisión de tornillería y fijaciones estructurales</t>
+        </is>
+      </c>
+      <c r="K14" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L14" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M14" s="95" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C15" s="89" t="inlineStr">
+        <is>
+          <t>Verificación del servo motor TECO JSMA-PSC44BK (temperatura y vibración)</t>
+        </is>
+      </c>
+      <c r="K15" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L15" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M15" s="91" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
       </c>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="22" t="n"/>
-      <c r="H16" s="22" t="n"/>
-      <c r="I16" s="22" t="n"/>
-      <c r="J16" s="23" t="n"/>
-      <c r="K16" s="1" t="inlineStr">
+      <c r="K16" s="87" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L16" s="36" t="inlineStr">
+      <c r="L16" s="87" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M16" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMENTARIOS </t>
-        </is>
-      </c>
-      <c r="N16" s="22" t="n"/>
-      <c r="O16" s="22" t="n"/>
-      <c r="P16" s="22" t="n"/>
-      <c r="Q16" s="23" t="n"/>
-    </row>
-    <row r="17" ht="25.05" customHeight="1">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>Verificación visual del tablero (alarmas e indicadores)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="22" t="n"/>
-      <c r="I17" s="22" t="n"/>
-      <c r="J17" s="23" t="n"/>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M17" s="24" t="n"/>
-      <c r="N17" s="22" t="n"/>
-      <c r="O17" s="22" t="n"/>
-      <c r="P17" s="22" t="n"/>
-      <c r="Q17" s="23" t="n"/>
-    </row>
-    <row r="18" ht="25.05" customHeight="1">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="M16" s="87" t="inlineStr">
+        <is>
+          <t>COMENTARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>Reapriete de terminales en tablero eléctrico</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="23" t="n"/>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M18" s="24" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="22" t="n"/>
-      <c r="P18" s="22" t="n"/>
-      <c r="Q18" s="23" t="n"/>
-    </row>
-    <row r="19" ht="25.05" customHeight="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="C17" s="89" t="inlineStr">
+        <is>
+          <t>Verificación del HMI MCU 01 TS: alarmas, indicadores y pantalla táctil</t>
+        </is>
+      </c>
+      <c r="K17" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L17" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M17" s="91" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="92" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de motores (temperatura, ruido y vibración)</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="23" t="n"/>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M19" s="24" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="23" t="n"/>
-    </row>
-    <row r="20" ht="25.05" customHeight="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="C18" s="93" t="inlineStr">
+        <is>
+          <t>Limpieza de tablero eléctrico y revisión de cableado y ducterías</t>
+        </is>
+      </c>
+      <c r="K18" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L18" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M18" s="95" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="88" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Revisión de dispositivos de seguridad y paro de emergencia</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="23" t="n"/>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M20" s="24" t="n"/>
-      <c r="N20" s="22" t="n"/>
-      <c r="O20" s="22" t="n"/>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="23" t="n"/>
-    </row>
-    <row r="21" ht="25.05" customHeight="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="C19" s="89" t="inlineStr">
+        <is>
+          <t>Reapriete de terminales y conexiones eléctricas</t>
+        </is>
+      </c>
+      <c r="K19" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L19" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M19" s="91" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="92" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C21" s="25" t="inlineStr">
-        <is>
-          <t>Prueba funcional de paros de emergencia</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="23" t="n"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M21" s="24" t="n"/>
-      <c r="N21" s="22" t="n"/>
-      <c r="O21" s="22" t="n"/>
-      <c r="P21" s="22" t="n"/>
-      <c r="Q21" s="23" t="n"/>
-    </row>
-    <row r="22" ht="25.05" customHeight="1">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="C20" s="93" t="inlineStr">
+        <is>
+          <t>Revisión de portafusibles Lovato FB01 B 2P: 2FU1, 6FU1, 7FU1</t>
+        </is>
+      </c>
+      <c r="K20" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L20" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M20" s="95" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="88" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Verificación de tierras físicas y continuidad</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="22" t="n"/>
-      <c r="F22" s="22" t="n"/>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="22" t="n"/>
-      <c r="I22" s="22" t="n"/>
-      <c r="J22" s="23" t="n"/>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M22" s="24" t="n"/>
-      <c r="N22" s="22" t="n"/>
-      <c r="O22" s="22" t="n"/>
-      <c r="P22" s="22" t="n"/>
-      <c r="Q22" s="23" t="n"/>
-    </row>
-    <row r="23" ht="25.05" customHeight="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEUMÁTICO</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="22" t="n"/>
-      <c r="I23" s="22" t="n"/>
-      <c r="J23" s="23" t="n"/>
-      <c r="K23" s="1" t="inlineStr">
+      <c r="C21" s="89" t="inlineStr">
+        <is>
+          <t>Verificación del relé de seguridad Allen-Bradley MSR126.1T (7K1)</t>
+        </is>
+      </c>
+      <c r="K21" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L21" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M21" s="91" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="92" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C22" s="93" t="inlineStr">
+        <is>
+          <t>Revisión del servo drive TECO: parámetros, fallas y conexiones</t>
+        </is>
+      </c>
+      <c r="K22" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L22" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M22" s="95" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="88" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C23" s="89" t="inlineStr">
+        <is>
+          <t>Verificación de fuente de poder Omron S8VK-C12024 (salida 24 VDC)</t>
+        </is>
+      </c>
+      <c r="K23" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L23" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M23" s="91" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="92" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C24" s="93" t="inlineStr">
+        <is>
+          <t>Revisión del relevador SSR RM1A48D50 (7KPR1): temperatura y sujeción</t>
+        </is>
+      </c>
+      <c r="K24" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L24" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M24" s="95" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="88" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C25" s="89" t="inlineStr">
+        <is>
+          <t>Prueba funcional: paro de emergencia y botón REAJUSTE EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="K25" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L25" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M25" s="91" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C26" s="93" t="inlineStr">
+        <is>
+          <t>Verificación de interruptor de seguridad Pizzato (funcionamiento y ajuste)</t>
+        </is>
+      </c>
+      <c r="K26" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L26" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M26" s="95" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="88" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C27" s="89" t="inlineStr">
+        <is>
+          <t>Revisión del módulo I/O SHS DIN (señales de entrada/salida)</t>
+        </is>
+      </c>
+      <c r="K27" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L27" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M27" s="91" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="92" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C28" s="93" t="inlineStr">
+        <is>
+          <t>Verificación del interruptor principal ABB OT25F4N2 (2QS1)</t>
+        </is>
+      </c>
+      <c r="K28" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L28" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M28" s="95" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="88" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C29" s="89" t="inlineStr">
+        <is>
+          <t>Verificación de tierras físicas y continuidad de tierra</t>
+        </is>
+      </c>
+      <c r="K29" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L29" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M29" s="91" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CALENTAMIENTO</t>
+        </is>
+      </c>
+      <c r="K30" s="87" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L23" s="36" t="inlineStr">
+      <c r="L30" s="87" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M23" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMENTARIOS </t>
-        </is>
-      </c>
-      <c r="N23" s="22" t="n"/>
-      <c r="O23" s="22" t="n"/>
-      <c r="P23" s="22" t="n"/>
-      <c r="Q23" s="23" t="n"/>
-    </row>
-    <row r="24" ht="25.05" customHeight="1">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C24" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de presión de trabajo y purga de condensados</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="22" t="n"/>
-      <c r="I24" s="22" t="n"/>
-      <c r="J24" s="23" t="n"/>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M24" s="24" t="n"/>
-      <c r="N24" s="22" t="n"/>
-      <c r="O24" s="22" t="n"/>
-      <c r="P24" s="22" t="n"/>
-      <c r="Q24" s="23" t="n"/>
-    </row>
-    <row r="25" ht="25.05" customHeight="1">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Inspección de mangueras, racores y cilindros neumáticos</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="22" t="n"/>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="22" t="n"/>
-      <c r="J25" s="23" t="n"/>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M25" s="24" t="n"/>
-      <c r="N25" s="22" t="n"/>
-      <c r="O25" s="22" t="n"/>
-      <c r="P25" s="22" t="n"/>
-      <c r="Q25" s="23" t="n"/>
-    </row>
-    <row r="26" ht="25.05" customHeight="1">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C26" s="25" t="inlineStr">
-        <is>
-          <t>Limpieza/cambio de filtros FRL</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="22" t="n"/>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="22" t="n"/>
-      <c r="I26" s="22" t="n"/>
-      <c r="J26" s="23" t="n"/>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M26" s="24" t="n"/>
-      <c r="N26" s="22" t="n"/>
-      <c r="O26" s="22" t="n"/>
-      <c r="P26" s="22" t="n"/>
-      <c r="Q26" s="23" t="n"/>
-    </row>
-    <row r="27" ht="25.05" customHeight="1">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Revisión y ajuste de válvulas solenoides</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="22" t="n"/>
-      <c r="H27" s="22" t="n"/>
-      <c r="I27" s="22" t="n"/>
-      <c r="J27" s="23" t="n"/>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M27" s="24" t="n"/>
-      <c r="N27" s="22" t="n"/>
-      <c r="O27" s="22" t="n"/>
-      <c r="P27" s="22" t="n"/>
-      <c r="Q27" s="23" t="n"/>
-    </row>
-    <row r="28" ht="25.05" customHeight="1">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="M30" s="87" t="inlineStr">
+        <is>
+          <t>COMENTARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="88" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C31" s="89" t="inlineStr">
+        <is>
+          <t>Verificación de temperatura de trabajo de rodillos calefactores</t>
+        </is>
+      </c>
+      <c r="K31" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L31" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M31" s="91" t="n"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="92" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C32" s="93" t="inlineStr">
+        <is>
+          <t>Limpieza de resistencias calefactoras (polvo y residuos de material)</t>
+        </is>
+      </c>
+      <c r="K32" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L32" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M32" s="95" t="n"/>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C33" s="89" t="inlineStr">
+        <is>
+          <t>Calibración de termocuplas y verificación de control de temperatura</t>
+        </is>
+      </c>
+      <c r="K33" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L33" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M33" s="91" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="92" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C34" s="93" t="inlineStr">
+        <is>
+          <t>Medición eléctrica de resistencias calefactoras: continuidad y ohms</t>
+        </is>
+      </c>
+      <c r="K34" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L34" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M34" s="95" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="88" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C35" s="89" t="inlineStr">
+        <is>
+          <t>Verificación del SSR RM1A48D50 como control de calefacción (7KPR1)</t>
+        </is>
+      </c>
+      <c r="K35" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L35" s="90" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M35" s="91" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C36" s="93" t="inlineStr">
+        <is>
+          <t>Verificación de uniformidad de calor en todos los rodillos</t>
+        </is>
+      </c>
+      <c r="K36" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L36" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M36" s="95" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="96" t="inlineStr">
         <is>
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
       </c>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="22" t="n"/>
-      <c r="F28" s="22" t="n"/>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="22" t="n"/>
-      <c r="I28" s="22" t="n"/>
-      <c r="J28" s="22" t="n"/>
-      <c r="K28" s="22" t="n"/>
-      <c r="L28" s="22" t="n"/>
-      <c r="M28" s="23" t="n"/>
-      <c r="N28" s="33" t="inlineStr">
-        <is>
-          <t>VOLTAJE ALIMENTACIÓN</t>
-        </is>
-      </c>
-      <c r="O28" s="22" t="n"/>
-      <c r="P28" s="22" t="n"/>
-      <c r="Q28" s="23" t="n"/>
-    </row>
-    <row r="29" ht="25.05" customHeight="1">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="10" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="B38" s="97" t="inlineStr">
         <is>
           <t>ENE</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C38" s="97" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D38" s="97" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E38" s="97" t="inlineStr">
         <is>
           <t>ABR</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F38" s="97" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G38" s="97" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H38" s="97" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I38" s="97" t="inlineStr">
         <is>
           <t>AGO</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J38" s="97" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K38" s="97" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L38" s="97" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M38" s="97" t="inlineStr">
         <is>
           <t>DIC</t>
         </is>
       </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O29" s="6" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>VAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="25.05" customHeight="1">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="n"/>
-      <c r="O30" s="6" t="n"/>
-      <c r="P30" s="6" t="n"/>
-      <c r="Q30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="25.05" customHeight="1">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="70" t="inlineStr">
+    </row>
+    <row r="39">
+      <c r="B39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="C39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="D39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="E39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="F39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="G39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="H39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="I39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="J39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="K39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M39" s="94" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="50" customHeight="1">
+      <c r="B41" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="45" t="n"/>
-      <c r="F31" s="45" t="n"/>
-      <c r="G31" s="46" t="n"/>
-      <c r="H31" s="71" t="inlineStr">
+      <c r="H41" s="98" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
-      <c r="I31" s="75" t="n"/>
-      <c r="J31" s="75" t="n"/>
-      <c r="K31" s="72" t="inlineStr">
-        <is>
-          <t>Supervisor de Producción: 
+      <c r="J41" s="99" t="inlineStr">
+        <is>
+          <t>Supervisor de Mantenimiento:
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L31" s="45" t="n"/>
-      <c r="M31" s="45" t="n"/>
-      <c r="N31" s="45" t="n"/>
-      <c r="O31" s="45" t="n"/>
-      <c r="P31" s="45" t="n"/>
-      <c r="Q31" s="46" t="n"/>
-    </row>
-    <row r="32" ht="25.05" customHeight="1">
-      <c r="B32" s="70" t="inlineStr">
+    </row>
+    <row r="42">
+      <c r="B42" s="98" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="C32" s="76" t="n"/>
-      <c r="D32" s="76" t="n"/>
-      <c r="E32" s="76" t="n"/>
-      <c r="F32" s="76" t="n"/>
-      <c r="G32" s="77" t="n"/>
-      <c r="K32" s="70" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="L32" s="76" t="n"/>
-      <c r="M32" s="76" t="n"/>
-      <c r="N32" s="76" t="n"/>
-      <c r="O32" s="76" t="n"/>
-      <c r="P32" s="76" t="n"/>
-      <c r="Q32" s="77" t="n"/>
-    </row>
-    <row r="33" ht="25.05" customHeight="1">
-      <c r="B33" s="78" t="n"/>
-      <c r="C33" s="79" t="n"/>
-      <c r="D33" s="79" t="n"/>
-      <c r="E33" s="79" t="n"/>
-      <c r="F33" s="79" t="n"/>
-      <c r="G33" s="80" t="n"/>
-      <c r="K33" s="78" t="n"/>
-      <c r="L33" s="79" t="n"/>
-      <c r="M33" s="79" t="n"/>
-      <c r="N33" s="79" t="n"/>
-      <c r="O33" s="79" t="n"/>
-      <c r="P33" s="79" t="n"/>
-      <c r="Q33" s="80" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="N28:Q28"/>
-    <mergeCell ref="H31:J33"/>
+  <mergeCells count="75">
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="B37:N37"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="M34:N34"/>
     <mergeCell ref="C15:J15"/>
-    <mergeCell ref="K32:Q33"/>
+    <mergeCell ref="C33:J33"/>
     <mergeCell ref="C24:J24"/>
-    <mergeCell ref="J5:Q5"/>
-    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="M9:N9"/>
     <mergeCell ref="C14:J14"/>
-    <mergeCell ref="B32:G33"/>
-    <mergeCell ref="M9:Q9"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="C35:J35"/>
     <mergeCell ref="C26:J26"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="B28:M28"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I5:N5"/>
     <mergeCell ref="C20:J20"/>
-    <mergeCell ref="J6:Q6"/>
-    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="B4:H4"/>
     <mergeCell ref="C25:J25"/>
+    <mergeCell ref="M10:N10"/>
     <mergeCell ref="C10:J10"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="M31:N31"/>
     <mergeCell ref="C22:J22"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="C31:J31"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B30:J30"/>
     <mergeCell ref="C9:J9"/>
-    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M7:N7"/>
     <mergeCell ref="C12:J12"/>
-    <mergeCell ref="J4:Q4"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M21:N21"/>
     <mergeCell ref="C21:J21"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M30:N30"/>
     <mergeCell ref="C11:J11"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M27:N27"/>
     <mergeCell ref="C27:J27"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="M27:Q27"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="J41:N41"/>
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="C23:J23"/>
     <mergeCell ref="C8:J8"/>
     <mergeCell ref="B16:J16"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M26:N26"/>
     <mergeCell ref="C17:J17"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="M14:Q14"/>
-    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="C32:J32"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="M19:N19"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C19:J19"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="B4:I4"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10868,7 +12013,7 @@
     <row r="1" ht="7.8" customHeight="1"/>
     <row r="2" ht="56.55" customHeight="1">
       <c r="A2" s="11" t="n"/>
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
@@ -10885,24 +12030,25 @@
       <c r="L2" s="22" t="n"/>
       <c r="M2" s="22" t="n"/>
       <c r="N2" s="23" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>No. de Documento             A9.I1.F2
-Revision:                                    00
-Fecha:                        08/06/2026</t>
-        </is>
-      </c>
-      <c r="P2" s="22" t="n"/>
-      <c r="Q2" s="23" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
       <c r="A3" s="11" t="n"/>
-      <c r="B3" s="38" t="n"/>
+      <c r="B3" s="36" t="n"/>
       <c r="C3" s="22" t="n"/>
       <c r="D3" s="23" t="n"/>
-      <c r="E3" s="34" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO PREVENTIVO   —   HOJEADORA ROBUST</t>
+      <c r="E3" s="74" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO PREVENTIVO      SINGLE KNIFE 
+CORTADORA DE CUCHILLA ÚNICA</t>
         </is>
       </c>
       <c r="F3" s="22" t="n"/>
@@ -10920,7 +12066,7 @@
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
@@ -10932,7 +12078,7 @@
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
       <c r="I4" s="23" t="n"/>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
@@ -10947,7 +12093,7 @@
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
@@ -10959,7 +12105,7 @@
       <c r="G5" s="22" t="n"/>
       <c r="H5" s="22" t="n"/>
       <c r="I5" s="23" t="n"/>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
@@ -10974,9 +12120,9 @@
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>Nombre de máquina:  Hojeadora Robust.</t>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>Nombre de máquina:  Cuchilla Simple</t>
         </is>
       </c>
       <c r="C6" s="22" t="n"/>
@@ -10986,9 +12132,9 @@
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="23" t="n"/>
-      <c r="J6" s="32" t="inlineStr">
-        <is>
-          <t>Número de máquina:  HR01</t>
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t>Número de máquina:  SK01</t>
         </is>
       </c>
       <c r="K6" s="22" t="n"/>
@@ -11001,7 +12147,7 @@
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO</t>
         </is>
@@ -11019,12 +12165,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -11041,7 +12187,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Inspección visual: ruidos, vibraciones y fugas</t>
         </is>
@@ -11063,7 +12209,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M8" s="24" t="n"/>
+      <c r="M8" s="21" t="n"/>
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="22" t="n"/>
@@ -11076,9 +12222,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Lubricación de rodillos de alimentación y guías</t>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Inspección de cuchilla (filo, estado y sujeción)</t>
         </is>
       </c>
       <c r="D9" s="22" t="n"/>
@@ -11098,7 +12244,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M9" s="24" t="n"/>
+      <c r="M9" s="21" t="n"/>
       <c r="N9" s="22" t="n"/>
       <c r="O9" s="22" t="n"/>
       <c r="P9" s="22" t="n"/>
@@ -11111,9 +12257,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de cuchillas circulares (filo y estado)</t>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de guía trasera y escuadras de corte</t>
         </is>
       </c>
       <c r="D10" s="22" t="n"/>
@@ -11133,7 +12279,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M10" s="24" t="n"/>
+      <c r="M10" s="21" t="n"/>
       <c r="N10" s="22" t="n"/>
       <c r="O10" s="22" t="n"/>
       <c r="P10" s="22" t="n"/>
@@ -11146,9 +12292,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>Revisión del sistema de separación de hojas</t>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>Lubricación de guías y mecanismo de corte</t>
         </is>
       </c>
       <c r="D11" s="22" t="n"/>
@@ -11168,7 +12314,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M11" s="24" t="n"/>
+      <c r="M11" s="21" t="n"/>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="22" t="n"/>
       <c r="P11" s="22" t="n"/>
@@ -11181,9 +12327,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de alineación de rodillos transportadores</t>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de sistema de presión neumática sujetador</t>
         </is>
       </c>
       <c r="D12" s="22" t="n"/>
@@ -11203,7 +12349,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M12" s="24" t="n"/>
+      <c r="M12" s="21" t="n"/>
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
       <c r="P12" s="22" t="n"/>
@@ -11216,9 +12362,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>Revisión de correas de transporte (tensión y desgaste)</t>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Verificación de mesa de trabajo y alineación</t>
         </is>
       </c>
       <c r="D13" s="22" t="n"/>
@@ -11238,7 +12384,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M13" s="24" t="n"/>
+      <c r="M13" s="21" t="n"/>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="22" t="n"/>
       <c r="P13" s="22" t="n"/>
@@ -11251,7 +12397,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Verificación de tornillería y fijaciones estructurales</t>
         </is>
@@ -11273,7 +12419,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M14" s="24" t="n"/>
+      <c r="M14" s="21" t="n"/>
       <c r="N14" s="22" t="n"/>
       <c r="O14" s="22" t="n"/>
       <c r="P14" s="22" t="n"/>
@@ -11286,9 +12432,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>Afilado o cambio de cuchillas (según desgaste)</t>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>Afilado o cambio de cuchilla (según desgaste)</t>
         </is>
       </c>
       <c r="D15" s="22" t="n"/>
@@ -11308,7 +12454,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M15" s="24" t="n"/>
+      <c r="M15" s="21" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
       <c r="P15" s="22" t="n"/>
@@ -11316,7 +12462,7 @@
     </row>
     <row r="16" ht="25.05" customHeight="1">
       <c r="A16" s="11" t="n"/>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
@@ -11334,12 +12480,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L16" s="36" t="inlineStr">
+      <c r="L16" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M16" s="36" t="inlineStr">
+      <c r="M16" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -11356,7 +12502,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Verificación visual del tablero (alarmas e indicadores)</t>
         </is>
@@ -11378,7 +12524,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M17" s="24" t="n"/>
+      <c r="M17" s="21" t="n"/>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="22" t="n"/>
@@ -11391,7 +12537,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>Reapriete de terminales en tablero eléctrico</t>
         </is>
@@ -11413,7 +12559,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n"/>
+      <c r="M18" s="21" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
       <c r="P18" s="22" t="n"/>
@@ -11426,7 +12572,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>Revisión de motores (temperatura, ruido y vibración)</t>
         </is>
@@ -11448,7 +12594,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n"/>
+      <c r="M19" s="21" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
       <c r="P19" s="22" t="n"/>
@@ -11461,9 +12607,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Revisión de sensores y fotoceldas</t>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Revisión de dispositivos de seguridad y paro de emergencia</t>
         </is>
       </c>
       <c r="D20" s="22" t="n"/>
@@ -11483,7 +12629,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n"/>
+      <c r="M20" s="21" t="n"/>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
@@ -11496,7 +12642,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C21" s="25" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>Prueba funcional de paros de emergencia</t>
         </is>
@@ -11518,7 +12664,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M21" s="24" t="n"/>
+      <c r="M21" s="21" t="n"/>
       <c r="N21" s="22" t="n"/>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="22" t="n"/>
@@ -11531,7 +12677,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Verificación de tierras físicas y continuidad</t>
         </is>
@@ -11553,7 +12699,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M22" s="24" t="n"/>
+      <c r="M22" s="21" t="n"/>
       <c r="N22" s="22" t="n"/>
       <c r="O22" s="22" t="n"/>
       <c r="P22" s="22" t="n"/>
@@ -11561,7 +12707,7 @@
     </row>
     <row r="23" ht="25.05" customHeight="1">
       <c r="A23" s="11" t="n"/>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  NEUMÁTICO</t>
         </is>
@@ -11579,12 +12725,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L23" s="36" t="inlineStr">
+      <c r="L23" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M23" s="36" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -11601,7 +12747,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Verificación de presión de trabajo y purga de condensados</t>
         </is>
@@ -11623,7 +12769,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
+      <c r="M24" s="21" t="n"/>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
       <c r="P24" s="22" t="n"/>
@@ -11636,9 +12782,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Inspección de mangueras, racores y conexiones neumáticas</t>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>Inspección de mangueras, racores y cilindros neumáticos</t>
         </is>
       </c>
       <c r="D25" s="22" t="n"/>
@@ -11658,7 +12804,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M25" s="24" t="n"/>
+      <c r="M25" s="21" t="n"/>
       <c r="N25" s="22" t="n"/>
       <c r="O25" s="22" t="n"/>
       <c r="P25" s="22" t="n"/>
@@ -11671,7 +12817,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Limpieza/cambio de filtros FRL</t>
         </is>
@@ -11693,7 +12839,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M26" s="24" t="n"/>
+      <c r="M26" s="21" t="n"/>
       <c r="N26" s="22" t="n"/>
       <c r="O26" s="22" t="n"/>
       <c r="P26" s="22" t="n"/>
@@ -11706,7 +12852,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>Revisión y ajuste de válvulas solenoides</t>
         </is>
@@ -11728,7 +12874,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M27" s="24" t="n"/>
+      <c r="M27" s="21" t="n"/>
       <c r="N27" s="22" t="n"/>
       <c r="O27" s="22" t="n"/>
       <c r="P27" s="22" t="n"/>
@@ -11736,7 +12882,7 @@
     </row>
     <row r="28" ht="25.05" customHeight="1">
       <c r="A28" s="11" t="n"/>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
@@ -11752,7 +12898,7 @@
       <c r="K28" s="22" t="n"/>
       <c r="L28" s="22" t="n"/>
       <c r="M28" s="23" t="n"/>
-      <c r="N28" s="33" t="inlineStr">
+      <c r="N28" s="43" t="inlineStr">
         <is>
           <t>VOLTAJE ALIMENTACIÓN</t>
         </is>
@@ -11913,38 +13059,38 @@
     </row>
     <row r="31" ht="25.05" customHeight="1">
       <c r="A31" s="11" t="n"/>
-      <c r="B31" s="70" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="45" t="n"/>
-      <c r="F31" s="45" t="n"/>
-      <c r="G31" s="46" t="n"/>
-      <c r="H31" s="71" t="inlineStr">
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+      <c r="E31" s="50" t="n"/>
+      <c r="F31" s="50" t="n"/>
+      <c r="G31" s="51" t="n"/>
+      <c r="H31" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
       <c r="I31" s="75" t="n"/>
       <c r="J31" s="75" t="n"/>
-      <c r="K31" s="72" t="inlineStr">
+      <c r="K31" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L31" s="45" t="n"/>
-      <c r="M31" s="45" t="n"/>
-      <c r="N31" s="45" t="n"/>
-      <c r="O31" s="45" t="n"/>
-      <c r="P31" s="45" t="n"/>
-      <c r="Q31" s="46" t="n"/>
+      <c r="L31" s="50" t="n"/>
+      <c r="M31" s="50" t="n"/>
+      <c r="N31" s="50" t="n"/>
+      <c r="O31" s="50" t="n"/>
+      <c r="P31" s="50" t="n"/>
+      <c r="Q31" s="51" t="n"/>
     </row>
     <row r="32" ht="25.05" customHeight="1">
-      <c r="B32" s="70" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -11954,7 +13100,7 @@
       <c r="E32" s="76" t="n"/>
       <c r="F32" s="76" t="n"/>
       <c r="G32" s="77" t="n"/>
-      <c r="K32" s="70" t="inlineStr">
+      <c r="K32" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12055,7 +13201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Q32"/>
+  <dimension ref="A2:Q33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
@@ -12065,7 +13211,7 @@
     <row r="1" ht="7.8" customHeight="1"/>
     <row r="2" ht="56.55" customHeight="1">
       <c r="A2" s="11" t="n"/>
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
@@ -12082,24 +13228,24 @@
       <c r="L2" s="22" t="n"/>
       <c r="M2" s="22" t="n"/>
       <c r="N2" s="23" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>No. de Documento             A9.I1.F2
-Revision:                                    00
-Fecha:                        08/06/2026</t>
-        </is>
-      </c>
-      <c r="P2" s="22" t="n"/>
-      <c r="Q2" s="23" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
       <c r="A3" s="11" t="n"/>
-      <c r="B3" s="38" t="n"/>
+      <c r="B3" s="36" t="n"/>
       <c r="C3" s="22" t="n"/>
       <c r="D3" s="23" t="n"/>
-      <c r="E3" s="34" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO PREVENTIVO   —   GAPCUTTER</t>
+      <c r="E3" s="38" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO PREVENTIVO   —   HOJEADORA ROBUST</t>
         </is>
       </c>
       <c r="F3" s="22" t="n"/>
@@ -12117,7 +13263,7 @@
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
@@ -12129,7 +13275,7 @@
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
       <c r="I4" s="23" t="n"/>
-      <c r="J4" s="32" t="inlineStr">
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
@@ -12144,7 +13290,7 @@
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
@@ -12156,7 +13302,7 @@
       <c r="G5" s="22" t="n"/>
       <c r="H5" s="22" t="n"/>
       <c r="I5" s="23" t="n"/>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
@@ -12171,9 +13317,9 @@
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>Nombre de máquina:  Gap cutter</t>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>Nombre de máquina:  Hojeadora Robust.</t>
         </is>
       </c>
       <c r="C6" s="22" t="n"/>
@@ -12183,9 +13329,9 @@
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="23" t="n"/>
-      <c r="J6" s="32" t="inlineStr">
-        <is>
-          <t>Número de máquina:  GC01</t>
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t>Número de máquina:  HR01</t>
         </is>
       </c>
       <c r="K6" s="22" t="n"/>
@@ -12198,7 +13344,7 @@
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO</t>
         </is>
@@ -12216,12 +13362,12 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M7" s="36" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">COMENTARIOS </t>
         </is>
@@ -12238,7 +13384,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Inspección visual: ruidos, vibraciones y fugas</t>
         </is>
@@ -12260,7 +13406,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M8" s="24" t="n"/>
+      <c r="M8" s="21" t="n"/>
       <c r="N8" s="22" t="n"/>
       <c r="O8" s="22" t="n"/>
       <c r="P8" s="22" t="n"/>
@@ -12273,9 +13419,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Revisión de cuchillas de corte (filo, desgaste y sujeción)</t>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Lubricación de rodillos de alimentación y guías</t>
         </is>
       </c>
       <c r="D9" s="22" t="n"/>
@@ -12295,7 +13441,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M9" s="24" t="n"/>
+      <c r="M9" s="21" t="n"/>
       <c r="N9" s="22" t="n"/>
       <c r="O9" s="22" t="n"/>
       <c r="P9" s="22" t="n"/>
@@ -12308,9 +13454,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>Lubricación de guías, ejes y mecanismos de corte</t>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de cuchillas circulares (filo y estado)</t>
         </is>
       </c>
       <c r="D10" s="22" t="n"/>
@@ -12330,7 +13476,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M10" s="24" t="n"/>
+      <c r="M10" s="21" t="n"/>
       <c r="N10" s="22" t="n"/>
       <c r="O10" s="22" t="n"/>
       <c r="P10" s="22" t="n"/>
@@ -12343,9 +13489,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>Verificación de alineación del sistema de corte</t>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>Revisión del sistema de separación de hojas</t>
         </is>
       </c>
       <c r="D11" s="22" t="n"/>
@@ -12365,7 +13511,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M11" s="24" t="n"/>
+      <c r="M11" s="21" t="n"/>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="22" t="n"/>
       <c r="P11" s="22" t="n"/>
@@ -12378,9 +13524,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de rodillos de alimentación y presión</t>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de alineación de rodillos transportadores</t>
         </is>
       </c>
       <c r="D12" s="22" t="n"/>
@@ -12400,7 +13546,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M12" s="24" t="n"/>
+      <c r="M12" s="21" t="n"/>
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
       <c r="P12" s="22" t="n"/>
@@ -12413,9 +13559,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>Verificación de tornillería y fijaciones estructurales</t>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Revisión de correas de transporte (tensión y desgaste)</t>
         </is>
       </c>
       <c r="D13" s="22" t="n"/>
@@ -12435,7 +13581,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M13" s="24" t="n"/>
+      <c r="M13" s="21" t="n"/>
       <c r="N13" s="22" t="n"/>
       <c r="O13" s="22" t="n"/>
       <c r="P13" s="22" t="n"/>
@@ -12448,9 +13594,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>Afilado o cambio de cuchillas (según desgaste)</t>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de tornillería y fijaciones estructurales</t>
         </is>
       </c>
       <c r="D14" s="22" t="n"/>
@@ -12470,7 +13616,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M14" s="24" t="n"/>
+      <c r="M14" s="21" t="n"/>
       <c r="N14" s="22" t="n"/>
       <c r="O14" s="22" t="n"/>
       <c r="P14" s="22" t="n"/>
@@ -12478,12 +13624,16 @@
     </row>
     <row r="15" ht="25.05" customHeight="1">
       <c r="A15" s="11" t="n"/>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ELÉCTRICO</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>Afilado o cambio de cuchillas (según desgaste)</t>
+        </is>
+      </c>
       <c r="D15" s="22" t="n"/>
       <c r="E15" s="22" t="n"/>
       <c r="F15" s="22" t="n"/>
@@ -12491,21 +13641,17 @@
       <c r="H15" s="22" t="n"/>
       <c r="I15" s="22" t="n"/>
       <c r="J15" s="23" t="n"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="L15" s="36" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="M15" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMENTARIOS </t>
-        </is>
-      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
       <c r="P15" s="22" t="n"/>
@@ -12513,16 +13659,12 @@
     </row>
     <row r="16" ht="25.05" customHeight="1">
       <c r="A16" s="11" t="n"/>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>Verificación visual del tablero (alarmas e indicadores)</t>
-        </is>
-      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ELÉCTRICO</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n"/>
       <c r="D16" s="22" t="n"/>
       <c r="E16" s="22" t="n"/>
       <c r="F16" s="22" t="n"/>
@@ -12530,17 +13672,21 @@
       <c r="H16" s="22" t="n"/>
       <c r="I16" s="22" t="n"/>
       <c r="J16" s="23" t="n"/>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M16" s="24" t="n"/>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L16" s="27" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M16" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMENTARIOS </t>
+        </is>
+      </c>
       <c r="N16" s="22" t="n"/>
       <c r="O16" s="22" t="n"/>
       <c r="P16" s="22" t="n"/>
@@ -12548,14 +13694,14 @@
     </row>
     <row r="17" ht="25.05" customHeight="1">
       <c r="A17" s="11" t="n"/>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>Reapriete de terminales en tablero eléctrico</t>
+          <t>Verificación visual del tablero (alarmas e indicadores)</t>
         </is>
       </c>
       <c r="D17" s="22" t="n"/>
@@ -12575,7 +13721,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M17" s="24" t="n"/>
+      <c r="M17" s="21" t="n"/>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="22" t="n"/>
@@ -12583,14 +13729,14 @@
     </row>
     <row r="18" ht="25.05" customHeight="1">
       <c r="A18" s="11" t="n"/>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>Revisión de motores (temperatura, ruido y vibración)</t>
+          <t>Reapriete de terminales en tablero eléctrico</t>
         </is>
       </c>
       <c r="D18" s="22" t="n"/>
@@ -12610,7 +13756,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M18" s="24" t="n"/>
+      <c r="M18" s="21" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
       <c r="P18" s="22" t="n"/>
@@ -12618,14 +13764,14 @@
     </row>
     <row r="19" ht="25.05" customHeight="1">
       <c r="A19" s="11" t="n"/>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Revisión de sensores y fotoceldas de posición</t>
+          <t>Revisión de motores (temperatura, ruido y vibración)</t>
         </is>
       </c>
       <c r="D19" s="22" t="n"/>
@@ -12645,7 +13791,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M19" s="24" t="n"/>
+      <c r="M19" s="21" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
       <c r="P19" s="22" t="n"/>
@@ -12653,14 +13799,14 @@
     </row>
     <row r="20" ht="25.05" customHeight="1">
       <c r="A20" s="11" t="n"/>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>Prueba funcional de paros de emergencia</t>
+          <t>Revisión de sensores y fotoceldas</t>
         </is>
       </c>
       <c r="D20" s="22" t="n"/>
@@ -12680,7 +13826,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M20" s="24" t="n"/>
+      <c r="M20" s="21" t="n"/>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
@@ -12688,14 +13834,14 @@
     </row>
     <row r="21" ht="25.05" customHeight="1">
       <c r="A21" s="11" t="n"/>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Verificación de tierras físicas y continuidad</t>
+          <t>Prueba funcional de paros de emergencia</t>
         </is>
       </c>
       <c r="D21" s="22" t="n"/>
@@ -12715,7 +13861,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M21" s="24" t="n"/>
+      <c r="M21" s="21" t="n"/>
       <c r="N21" s="22" t="n"/>
       <c r="O21" s="22" t="n"/>
       <c r="P21" s="22" t="n"/>
@@ -12723,12 +13869,16 @@
     </row>
     <row r="22" ht="25.05" customHeight="1">
       <c r="A22" s="11" t="n"/>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEUMÁTICO</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Verificación de tierras físicas y continuidad</t>
+        </is>
+      </c>
       <c r="D22" s="22" t="n"/>
       <c r="E22" s="22" t="n"/>
       <c r="F22" s="22" t="n"/>
@@ -12736,21 +13886,17 @@
       <c r="H22" s="22" t="n"/>
       <c r="I22" s="22" t="n"/>
       <c r="J22" s="23" t="n"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="L22" s="36" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="M22" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMENTARIOS </t>
-        </is>
-      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="n"/>
       <c r="N22" s="22" t="n"/>
       <c r="O22" s="22" t="n"/>
       <c r="P22" s="22" t="n"/>
@@ -12758,16 +13904,12 @@
     </row>
     <row r="23" ht="25.05" customHeight="1">
       <c r="A23" s="11" t="n"/>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de presión de trabajo y purga de condensados</t>
-        </is>
-      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEUMÁTICO</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n"/>
       <c r="D23" s="22" t="n"/>
       <c r="E23" s="22" t="n"/>
       <c r="F23" s="22" t="n"/>
@@ -12775,17 +13917,21 @@
       <c r="H23" s="22" t="n"/>
       <c r="I23" s="22" t="n"/>
       <c r="J23" s="23" t="n"/>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M23" s="24" t="n"/>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L23" s="27" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M23" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMENTARIOS </t>
+        </is>
+      </c>
       <c r="N23" s="22" t="n"/>
       <c r="O23" s="22" t="n"/>
       <c r="P23" s="22" t="n"/>
@@ -12793,14 +13939,14 @@
     </row>
     <row r="24" ht="25.05" customHeight="1">
       <c r="A24" s="11" t="n"/>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Inspección de mangueras, racores y cilindros neumáticos</t>
+          <t>Verificación de presión de trabajo y purga de condensados</t>
         </is>
       </c>
       <c r="D24" s="22" t="n"/>
@@ -12820,7 +13966,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M24" s="24" t="n"/>
+      <c r="M24" s="21" t="n"/>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
       <c r="P24" s="22" t="n"/>
@@ -12828,14 +13974,14 @@
     </row>
     <row r="25" ht="25.05" customHeight="1">
       <c r="A25" s="11" t="n"/>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Limpieza/cambio de filtros FRL</t>
+          <t>Inspección de mangueras, racores y conexiones neumáticas</t>
         </is>
       </c>
       <c r="D25" s="22" t="n"/>
@@ -12855,7 +14001,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M25" s="24" t="n"/>
+      <c r="M25" s="21" t="n"/>
       <c r="N25" s="22" t="n"/>
       <c r="O25" s="22" t="n"/>
       <c r="P25" s="22" t="n"/>
@@ -12863,14 +14009,14 @@
     </row>
     <row r="26" ht="25.05" customHeight="1">
       <c r="A26" s="11" t="n"/>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Revisión y ajuste de válvulas solenoides</t>
+          <t>Limpieza/cambio de filtros FRL</t>
         </is>
       </c>
       <c r="D26" s="22" t="n"/>
@@ -12890,7 +14036,7 @@
           <t>(   )</t>
         </is>
       </c>
-      <c r="M26" s="24" t="n"/>
+      <c r="M26" s="21" t="n"/>
       <c r="N26" s="22" t="n"/>
       <c r="O26" s="22" t="n"/>
       <c r="P26" s="22" t="n"/>
@@ -12898,309 +14044,342 @@
     </row>
     <row r="27" ht="25.05" customHeight="1">
       <c r="A27" s="11" t="n"/>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>CALENDARIO  DE  MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="n"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>Revisión y ajuste de válvulas solenoides</t>
+        </is>
+      </c>
       <c r="D27" s="22" t="n"/>
       <c r="E27" s="22" t="n"/>
       <c r="F27" s="22" t="n"/>
       <c r="G27" s="22" t="n"/>
       <c r="H27" s="22" t="n"/>
       <c r="I27" s="22" t="n"/>
-      <c r="J27" s="22" t="n"/>
-      <c r="K27" s="22" t="n"/>
-      <c r="L27" s="22" t="n"/>
-      <c r="M27" s="23" t="n"/>
-      <c r="N27" s="33" t="inlineStr">
-        <is>
-          <t>VOLTAJE ALIMENTACIÓN</t>
-        </is>
-      </c>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="n"/>
+      <c r="N27" s="22" t="n"/>
       <c r="O27" s="22" t="n"/>
       <c r="P27" s="22" t="n"/>
       <c r="Q27" s="23" t="n"/>
     </row>
     <row r="28" ht="25.05" customHeight="1">
       <c r="A28" s="11" t="n"/>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>ENE</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>FEB</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>ABR</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>DIC</t>
-        </is>
-      </c>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O28" s="6" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>VAC</t>
-        </is>
-      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>CALENDARIO  DE  MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="23" t="n"/>
+      <c r="N28" s="43" t="inlineStr">
+        <is>
+          <t>VOLTAJE ALIMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="O28" s="22" t="n"/>
+      <c r="P28" s="22" t="n"/>
+      <c r="Q28" s="23" t="n"/>
     </row>
     <row r="29" ht="25.05" customHeight="1">
       <c r="A29" s="11" t="n"/>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="n"/>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="6" t="n"/>
-      <c r="Q29" s="6" t="n"/>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>ABR</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>VAC</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="25.05" customHeight="1">
       <c r="A30" s="11" t="n"/>
-      <c r="B30" s="70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Realizo: </t>
-        </is>
-      </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
-      <c r="G30" s="46" t="n"/>
-      <c r="H30" s="71" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="6" t="n"/>
+      <c r="Q30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="25.05" customHeight="1">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="39" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+      <c r="E31" s="50" t="n"/>
+      <c r="F31" s="50" t="n"/>
+      <c r="G31" s="51" t="n"/>
+      <c r="H31" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
-      <c r="I30" s="75" t="n"/>
-      <c r="J30" s="75" t="n"/>
-      <c r="K30" s="72" t="inlineStr">
+      <c r="I31" s="75" t="n"/>
+      <c r="J31" s="75" t="n"/>
+      <c r="K31" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L30" s="45" t="n"/>
-      <c r="M30" s="45" t="n"/>
-      <c r="N30" s="45" t="n"/>
-      <c r="O30" s="45" t="n"/>
-      <c r="P30" s="45" t="n"/>
-      <c r="Q30" s="46" t="n"/>
-    </row>
-    <row r="31" ht="25.05" customHeight="1">
-      <c r="B31" s="70" t="inlineStr">
+      <c r="L31" s="50" t="n"/>
+      <c r="M31" s="50" t="n"/>
+      <c r="N31" s="50" t="n"/>
+      <c r="O31" s="50" t="n"/>
+      <c r="P31" s="50" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+    </row>
+    <row r="32" ht="25.05" customHeight="1">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="C31" s="76" t="n"/>
-      <c r="D31" s="76" t="n"/>
-      <c r="E31" s="76" t="n"/>
-      <c r="F31" s="76" t="n"/>
-      <c r="G31" s="77" t="n"/>
-      <c r="K31" s="70" t="inlineStr">
+      <c r="C32" s="76" t="n"/>
+      <c r="D32" s="76" t="n"/>
+      <c r="E32" s="76" t="n"/>
+      <c r="F32" s="76" t="n"/>
+      <c r="G32" s="77" t="n"/>
+      <c r="K32" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="L31" s="76" t="n"/>
-      <c r="M31" s="76" t="n"/>
-      <c r="N31" s="76" t="n"/>
-      <c r="O31" s="76" t="n"/>
-      <c r="P31" s="76" t="n"/>
-      <c r="Q31" s="77" t="n"/>
-    </row>
-    <row r="32" ht="25.05" customHeight="1">
-      <c r="B32" s="78" t="n"/>
-      <c r="C32" s="79" t="n"/>
-      <c r="D32" s="79" t="n"/>
-      <c r="E32" s="79" t="n"/>
-      <c r="F32" s="79" t="n"/>
-      <c r="G32" s="80" t="n"/>
-      <c r="K32" s="78" t="n"/>
-      <c r="L32" s="79" t="n"/>
-      <c r="M32" s="79" t="n"/>
-      <c r="N32" s="79" t="n"/>
-      <c r="O32" s="79" t="n"/>
-      <c r="P32" s="79" t="n"/>
-      <c r="Q32" s="80" t="n"/>
+      <c r="L32" s="76" t="n"/>
+      <c r="M32" s="76" t="n"/>
+      <c r="N32" s="76" t="n"/>
+      <c r="O32" s="76" t="n"/>
+      <c r="P32" s="76" t="n"/>
+      <c r="Q32" s="77" t="n"/>
+    </row>
+    <row r="33" ht="25.05" customHeight="1">
+      <c r="B33" s="78" t="n"/>
+      <c r="C33" s="79" t="n"/>
+      <c r="D33" s="79" t="n"/>
+      <c r="E33" s="79" t="n"/>
+      <c r="F33" s="79" t="n"/>
+      <c r="G33" s="80" t="n"/>
+      <c r="K33" s="78" t="n"/>
+      <c r="L33" s="79" t="n"/>
+      <c r="M33" s="79" t="n"/>
+      <c r="N33" s="79" t="n"/>
+      <c r="O33" s="79" t="n"/>
+      <c r="P33" s="79" t="n"/>
+      <c r="Q33" s="80" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="60">
+    <mergeCell ref="N28:Q28"/>
+    <mergeCell ref="H31:J33"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="K32:Q33"/>
     <mergeCell ref="C24:J24"/>
     <mergeCell ref="J5:Q5"/>
+    <mergeCell ref="B23:J23"/>
     <mergeCell ref="C14:J14"/>
+    <mergeCell ref="B32:G33"/>
     <mergeCell ref="M9:Q9"/>
-    <mergeCell ref="N27:Q27"/>
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="B28:M28"/>
     <mergeCell ref="C20:J20"/>
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="M11:Q11"/>
     <mergeCell ref="C25:J25"/>
-    <mergeCell ref="B31:G32"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="K31:Q32"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="M22:Q22"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="M13:Q13"/>
-    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="C9:J9"/>
     <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="C9:J9"/>
     <mergeCell ref="C12:J12"/>
+    <mergeCell ref="J4:Q4"/>
+    <mergeCell ref="M12:Q12"/>
     <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="J4:Q4"/>
+    <mergeCell ref="M25:Q25"/>
     <mergeCell ref="C21:J21"/>
-    <mergeCell ref="M25:Q25"/>
     <mergeCell ref="M15:Q15"/>
     <mergeCell ref="M21:Q21"/>
     <mergeCell ref="C11:J11"/>
-    <mergeCell ref="H30:J32"/>
+    <mergeCell ref="C27:J27"/>
     <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="M27:Q27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="C23:J23"/>
     <mergeCell ref="C8:J8"/>
+    <mergeCell ref="B16:J16"/>
     <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="C17:J17"/>
     <mergeCell ref="B7:J7"/>
-    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="M24:Q24"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="M24:Q24"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:G31"/>
     <mergeCell ref="M23:Q23"/>
     <mergeCell ref="M14:Q14"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="C13:J13"/>
-    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="C19:J19"/>
     <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="C19:J19"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -153,8 +153,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -234,8 +239,18 @@
         <fgColor rgb="00D6EAD8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001b5e20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002d8a45"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -512,11 +527,69 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -756,6 +829,17 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10980,7 +11064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:N42"/>
+  <dimension ref="B1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -11055,6 +11139,14 @@
           <t xml:space="preserve">  MECÁNICO</t>
         </is>
       </c>
+      <c r="C6" s="100" t="n"/>
+      <c r="D6" s="100" t="n"/>
+      <c r="E6" s="100" t="n"/>
+      <c r="F6" s="100" t="n"/>
+      <c r="G6" s="100" t="n"/>
+      <c r="H6" s="100" t="n"/>
+      <c r="I6" s="100" t="n"/>
+      <c r="J6" s="101" t="n"/>
       <c r="K6" s="87" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11070,6 +11162,7 @@
           <t>COMENTARIOS</t>
         </is>
       </c>
+      <c r="N6" s="101" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="88" t="inlineStr">
@@ -11082,6 +11175,13 @@
           <t>Inspección visual: ruidos, vibraciones y fugas en rodillos</t>
         </is>
       </c>
+      <c r="D7" s="100" t="n"/>
+      <c r="E7" s="100" t="n"/>
+      <c r="F7" s="100" t="n"/>
+      <c r="G7" s="100" t="n"/>
+      <c r="H7" s="100" t="n"/>
+      <c r="I7" s="100" t="n"/>
+      <c r="J7" s="101" t="n"/>
       <c r="K7" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11093,6 +11193,7 @@
         </is>
       </c>
       <c r="M7" s="91" t="n"/>
+      <c r="N7" s="101" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="92" t="inlineStr">
@@ -11105,6 +11206,13 @@
           <t>Lubricación de rodillos de calandria (baleros y chumaceras)</t>
         </is>
       </c>
+      <c r="D8" s="100" t="n"/>
+      <c r="E8" s="100" t="n"/>
+      <c r="F8" s="100" t="n"/>
+      <c r="G8" s="100" t="n"/>
+      <c r="H8" s="100" t="n"/>
+      <c r="I8" s="100" t="n"/>
+      <c r="J8" s="101" t="n"/>
       <c r="K8" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11116,6 +11224,7 @@
         </is>
       </c>
       <c r="M8" s="95" t="n"/>
+      <c r="N8" s="101" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="88" t="inlineStr">
@@ -11128,6 +11237,13 @@
           <t>Revisión y lubricación de cadena de transmisión y sprockets</t>
         </is>
       </c>
+      <c r="D9" s="100" t="n"/>
+      <c r="E9" s="100" t="n"/>
+      <c r="F9" s="100" t="n"/>
+      <c r="G9" s="100" t="n"/>
+      <c r="H9" s="100" t="n"/>
+      <c r="I9" s="100" t="n"/>
+      <c r="J9" s="101" t="n"/>
       <c r="K9" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11139,6 +11255,7 @@
         </is>
       </c>
       <c r="M9" s="91" t="n"/>
+      <c r="N9" s="101" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="92" t="inlineStr">
@@ -11151,6 +11268,13 @@
           <t>Verificación de tensión de cadena (deflexión máx. 1% de longitud)</t>
         </is>
       </c>
+      <c r="D10" s="100" t="n"/>
+      <c r="E10" s="100" t="n"/>
+      <c r="F10" s="100" t="n"/>
+      <c r="G10" s="100" t="n"/>
+      <c r="H10" s="100" t="n"/>
+      <c r="I10" s="100" t="n"/>
+      <c r="J10" s="101" t="n"/>
       <c r="K10" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11162,6 +11286,7 @@
         </is>
       </c>
       <c r="M10" s="95" t="n"/>
+      <c r="N10" s="101" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="88" t="inlineStr">
@@ -11174,6 +11299,13 @@
           <t>Revisión de caja reductora: nivel y calidad de aceite</t>
         </is>
       </c>
+      <c r="D11" s="100" t="n"/>
+      <c r="E11" s="100" t="n"/>
+      <c r="F11" s="100" t="n"/>
+      <c r="G11" s="100" t="n"/>
+      <c r="H11" s="100" t="n"/>
+      <c r="I11" s="100" t="n"/>
+      <c r="J11" s="101" t="n"/>
       <c r="K11" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11185,6 +11317,7 @@
         </is>
       </c>
       <c r="M11" s="91" t="n"/>
+      <c r="N11" s="101" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="92" t="inlineStr">
@@ -11197,6 +11330,13 @@
           <t>Verificación de alineación y paralelismo de rodillos</t>
         </is>
       </c>
+      <c r="D12" s="100" t="n"/>
+      <c r="E12" s="100" t="n"/>
+      <c r="F12" s="100" t="n"/>
+      <c r="G12" s="100" t="n"/>
+      <c r="H12" s="100" t="n"/>
+      <c r="I12" s="100" t="n"/>
+      <c r="J12" s="101" t="n"/>
       <c r="K12" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11208,6 +11348,7 @@
         </is>
       </c>
       <c r="M12" s="95" t="n"/>
+      <c r="N12" s="101" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="88" t="inlineStr">
@@ -11220,6 +11361,13 @@
           <t>Limpieza de rodillos y superficie de contacto (residuos de material)</t>
         </is>
       </c>
+      <c r="D13" s="100" t="n"/>
+      <c r="E13" s="100" t="n"/>
+      <c r="F13" s="100" t="n"/>
+      <c r="G13" s="100" t="n"/>
+      <c r="H13" s="100" t="n"/>
+      <c r="I13" s="100" t="n"/>
+      <c r="J13" s="101" t="n"/>
       <c r="K13" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11231,6 +11379,7 @@
         </is>
       </c>
       <c r="M13" s="91" t="n"/>
+      <c r="N13" s="101" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="92" t="inlineStr">
@@ -11243,6 +11392,13 @@
           <t>Revisión de tornillería y fijaciones estructurales</t>
         </is>
       </c>
+      <c r="D14" s="100" t="n"/>
+      <c r="E14" s="100" t="n"/>
+      <c r="F14" s="100" t="n"/>
+      <c r="G14" s="100" t="n"/>
+      <c r="H14" s="100" t="n"/>
+      <c r="I14" s="100" t="n"/>
+      <c r="J14" s="101" t="n"/>
       <c r="K14" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11254,6 +11410,7 @@
         </is>
       </c>
       <c r="M14" s="95" t="n"/>
+      <c r="N14" s="101" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="88" t="inlineStr">
@@ -11266,6 +11423,13 @@
           <t>Verificación del servo motor TECO JSMA-PSC44BK (temperatura y vibración)</t>
         </is>
       </c>
+      <c r="D15" s="100" t="n"/>
+      <c r="E15" s="100" t="n"/>
+      <c r="F15" s="100" t="n"/>
+      <c r="G15" s="100" t="n"/>
+      <c r="H15" s="100" t="n"/>
+      <c r="I15" s="100" t="n"/>
+      <c r="J15" s="101" t="n"/>
       <c r="K15" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11277,6 +11441,7 @@
         </is>
       </c>
       <c r="M15" s="91" t="n"/>
+      <c r="N15" s="101" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="86" t="inlineStr">
@@ -11284,6 +11449,14 @@
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
       </c>
+      <c r="C16" s="100" t="n"/>
+      <c r="D16" s="100" t="n"/>
+      <c r="E16" s="100" t="n"/>
+      <c r="F16" s="100" t="n"/>
+      <c r="G16" s="100" t="n"/>
+      <c r="H16" s="100" t="n"/>
+      <c r="I16" s="100" t="n"/>
+      <c r="J16" s="101" t="n"/>
       <c r="K16" s="87" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11299,6 +11472,7 @@
           <t>COMENTARIOS</t>
         </is>
       </c>
+      <c r="N16" s="101" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="88" t="inlineStr">
@@ -11311,6 +11485,13 @@
           <t>Verificación del HMI MCU 01 TS: alarmas, indicadores y pantalla táctil</t>
         </is>
       </c>
+      <c r="D17" s="100" t="n"/>
+      <c r="E17" s="100" t="n"/>
+      <c r="F17" s="100" t="n"/>
+      <c r="G17" s="100" t="n"/>
+      <c r="H17" s="100" t="n"/>
+      <c r="I17" s="100" t="n"/>
+      <c r="J17" s="101" t="n"/>
       <c r="K17" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11322,6 +11503,7 @@
         </is>
       </c>
       <c r="M17" s="91" t="n"/>
+      <c r="N17" s="101" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="92" t="inlineStr">
@@ -11334,6 +11516,13 @@
           <t>Limpieza de tablero eléctrico y revisión de cableado y ducterías</t>
         </is>
       </c>
+      <c r="D18" s="100" t="n"/>
+      <c r="E18" s="100" t="n"/>
+      <c r="F18" s="100" t="n"/>
+      <c r="G18" s="100" t="n"/>
+      <c r="H18" s="100" t="n"/>
+      <c r="I18" s="100" t="n"/>
+      <c r="J18" s="101" t="n"/>
       <c r="K18" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11345,6 +11534,7 @@
         </is>
       </c>
       <c r="M18" s="95" t="n"/>
+      <c r="N18" s="101" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="88" t="inlineStr">
@@ -11357,6 +11547,13 @@
           <t>Reapriete de terminales y conexiones eléctricas</t>
         </is>
       </c>
+      <c r="D19" s="100" t="n"/>
+      <c r="E19" s="100" t="n"/>
+      <c r="F19" s="100" t="n"/>
+      <c r="G19" s="100" t="n"/>
+      <c r="H19" s="100" t="n"/>
+      <c r="I19" s="100" t="n"/>
+      <c r="J19" s="101" t="n"/>
       <c r="K19" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11368,6 +11565,7 @@
         </is>
       </c>
       <c r="M19" s="91" t="n"/>
+      <c r="N19" s="101" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="92" t="inlineStr">
@@ -11380,6 +11578,13 @@
           <t>Revisión de portafusibles Lovato FB01 B 2P: 2FU1, 6FU1, 7FU1</t>
         </is>
       </c>
+      <c r="D20" s="100" t="n"/>
+      <c r="E20" s="100" t="n"/>
+      <c r="F20" s="100" t="n"/>
+      <c r="G20" s="100" t="n"/>
+      <c r="H20" s="100" t="n"/>
+      <c r="I20" s="100" t="n"/>
+      <c r="J20" s="101" t="n"/>
       <c r="K20" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11391,6 +11596,7 @@
         </is>
       </c>
       <c r="M20" s="95" t="n"/>
+      <c r="N20" s="101" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="88" t="inlineStr">
@@ -11403,6 +11609,13 @@
           <t>Verificación del relé de seguridad Allen-Bradley MSR126.1T (7K1)</t>
         </is>
       </c>
+      <c r="D21" s="100" t="n"/>
+      <c r="E21" s="100" t="n"/>
+      <c r="F21" s="100" t="n"/>
+      <c r="G21" s="100" t="n"/>
+      <c r="H21" s="100" t="n"/>
+      <c r="I21" s="100" t="n"/>
+      <c r="J21" s="101" t="n"/>
       <c r="K21" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11414,6 +11627,7 @@
         </is>
       </c>
       <c r="M21" s="91" t="n"/>
+      <c r="N21" s="101" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="92" t="inlineStr">
@@ -11426,6 +11640,13 @@
           <t>Revisión del servo drive TECO: parámetros, fallas y conexiones</t>
         </is>
       </c>
+      <c r="D22" s="100" t="n"/>
+      <c r="E22" s="100" t="n"/>
+      <c r="F22" s="100" t="n"/>
+      <c r="G22" s="100" t="n"/>
+      <c r="H22" s="100" t="n"/>
+      <c r="I22" s="100" t="n"/>
+      <c r="J22" s="101" t="n"/>
       <c r="K22" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11437,6 +11658,7 @@
         </is>
       </c>
       <c r="M22" s="95" t="n"/>
+      <c r="N22" s="101" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="88" t="inlineStr">
@@ -11449,6 +11671,13 @@
           <t>Verificación de fuente de poder Omron S8VK-C12024 (salida 24 VDC)</t>
         </is>
       </c>
+      <c r="D23" s="100" t="n"/>
+      <c r="E23" s="100" t="n"/>
+      <c r="F23" s="100" t="n"/>
+      <c r="G23" s="100" t="n"/>
+      <c r="H23" s="100" t="n"/>
+      <c r="I23" s="100" t="n"/>
+      <c r="J23" s="101" t="n"/>
       <c r="K23" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11460,6 +11689,7 @@
         </is>
       </c>
       <c r="M23" s="91" t="n"/>
+      <c r="N23" s="101" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="92" t="inlineStr">
@@ -11472,6 +11702,13 @@
           <t>Revisión del relevador SSR RM1A48D50 (7KPR1): temperatura y sujeción</t>
         </is>
       </c>
+      <c r="D24" s="100" t="n"/>
+      <c r="E24" s="100" t="n"/>
+      <c r="F24" s="100" t="n"/>
+      <c r="G24" s="100" t="n"/>
+      <c r="H24" s="100" t="n"/>
+      <c r="I24" s="100" t="n"/>
+      <c r="J24" s="101" t="n"/>
       <c r="K24" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11483,6 +11720,7 @@
         </is>
       </c>
       <c r="M24" s="95" t="n"/>
+      <c r="N24" s="101" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="88" t="inlineStr">
@@ -11495,6 +11733,13 @@
           <t>Prueba funcional: paro de emergencia y botón REAJUSTE EMERGENCIA</t>
         </is>
       </c>
+      <c r="D25" s="100" t="n"/>
+      <c r="E25" s="100" t="n"/>
+      <c r="F25" s="100" t="n"/>
+      <c r="G25" s="100" t="n"/>
+      <c r="H25" s="100" t="n"/>
+      <c r="I25" s="100" t="n"/>
+      <c r="J25" s="101" t="n"/>
       <c r="K25" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11506,6 +11751,7 @@
         </is>
       </c>
       <c r="M25" s="91" t="n"/>
+      <c r="N25" s="101" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="92" t="inlineStr">
@@ -11518,6 +11764,13 @@
           <t>Verificación de interruptor de seguridad Pizzato (funcionamiento y ajuste)</t>
         </is>
       </c>
+      <c r="D26" s="100" t="n"/>
+      <c r="E26" s="100" t="n"/>
+      <c r="F26" s="100" t="n"/>
+      <c r="G26" s="100" t="n"/>
+      <c r="H26" s="100" t="n"/>
+      <c r="I26" s="100" t="n"/>
+      <c r="J26" s="101" t="n"/>
       <c r="K26" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11529,6 +11782,7 @@
         </is>
       </c>
       <c r="M26" s="95" t="n"/>
+      <c r="N26" s="101" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="88" t="inlineStr">
@@ -11541,6 +11795,13 @@
           <t>Revisión del módulo I/O SHS DIN (señales de entrada/salida)</t>
         </is>
       </c>
+      <c r="D27" s="100" t="n"/>
+      <c r="E27" s="100" t="n"/>
+      <c r="F27" s="100" t="n"/>
+      <c r="G27" s="100" t="n"/>
+      <c r="H27" s="100" t="n"/>
+      <c r="I27" s="100" t="n"/>
+      <c r="J27" s="101" t="n"/>
       <c r="K27" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11552,6 +11813,7 @@
         </is>
       </c>
       <c r="M27" s="91" t="n"/>
+      <c r="N27" s="101" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="92" t="inlineStr">
@@ -11564,6 +11826,13 @@
           <t>Verificación del interruptor principal ABB OT25F4N2 (2QS1)</t>
         </is>
       </c>
+      <c r="D28" s="100" t="n"/>
+      <c r="E28" s="100" t="n"/>
+      <c r="F28" s="100" t="n"/>
+      <c r="G28" s="100" t="n"/>
+      <c r="H28" s="100" t="n"/>
+      <c r="I28" s="100" t="n"/>
+      <c r="J28" s="101" t="n"/>
       <c r="K28" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11575,6 +11844,7 @@
         </is>
       </c>
       <c r="M28" s="95" t="n"/>
+      <c r="N28" s="101" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="B29" s="88" t="inlineStr">
@@ -11587,6 +11857,13 @@
           <t>Verificación de tierras físicas y continuidad de tierra</t>
         </is>
       </c>
+      <c r="D29" s="100" t="n"/>
+      <c r="E29" s="100" t="n"/>
+      <c r="F29" s="100" t="n"/>
+      <c r="G29" s="100" t="n"/>
+      <c r="H29" s="100" t="n"/>
+      <c r="I29" s="100" t="n"/>
+      <c r="J29" s="101" t="n"/>
       <c r="K29" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11598,6 +11875,7 @@
         </is>
       </c>
       <c r="M29" s="91" t="n"/>
+      <c r="N29" s="101" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="86" t="inlineStr">
@@ -11605,6 +11883,14 @@
           <t xml:space="preserve">  CALENTAMIENTO</t>
         </is>
       </c>
+      <c r="C30" s="100" t="n"/>
+      <c r="D30" s="100" t="n"/>
+      <c r="E30" s="100" t="n"/>
+      <c r="F30" s="100" t="n"/>
+      <c r="G30" s="100" t="n"/>
+      <c r="H30" s="100" t="n"/>
+      <c r="I30" s="100" t="n"/>
+      <c r="J30" s="101" t="n"/>
       <c r="K30" s="87" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11620,6 +11906,7 @@
           <t>COMENTARIOS</t>
         </is>
       </c>
+      <c r="N30" s="101" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="88" t="inlineStr">
@@ -11632,6 +11919,13 @@
           <t>Verificación de temperatura de trabajo de rodillos calefactores</t>
         </is>
       </c>
+      <c r="D31" s="100" t="n"/>
+      <c r="E31" s="100" t="n"/>
+      <c r="F31" s="100" t="n"/>
+      <c r="G31" s="100" t="n"/>
+      <c r="H31" s="100" t="n"/>
+      <c r="I31" s="100" t="n"/>
+      <c r="J31" s="101" t="n"/>
       <c r="K31" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11643,6 +11937,7 @@
         </is>
       </c>
       <c r="M31" s="91" t="n"/>
+      <c r="N31" s="101" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="92" t="inlineStr">
@@ -11655,6 +11950,13 @@
           <t>Limpieza de resistencias calefactoras (polvo y residuos de material)</t>
         </is>
       </c>
+      <c r="D32" s="100" t="n"/>
+      <c r="E32" s="100" t="n"/>
+      <c r="F32" s="100" t="n"/>
+      <c r="G32" s="100" t="n"/>
+      <c r="H32" s="100" t="n"/>
+      <c r="I32" s="100" t="n"/>
+      <c r="J32" s="101" t="n"/>
       <c r="K32" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11666,6 +11968,7 @@
         </is>
       </c>
       <c r="M32" s="95" t="n"/>
+      <c r="N32" s="101" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="88" t="inlineStr">
@@ -11678,6 +11981,13 @@
           <t>Calibración de termocuplas y verificación de control de temperatura</t>
         </is>
       </c>
+      <c r="D33" s="100" t="n"/>
+      <c r="E33" s="100" t="n"/>
+      <c r="F33" s="100" t="n"/>
+      <c r="G33" s="100" t="n"/>
+      <c r="H33" s="100" t="n"/>
+      <c r="I33" s="100" t="n"/>
+      <c r="J33" s="101" t="n"/>
       <c r="K33" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11689,6 +11999,7 @@
         </is>
       </c>
       <c r="M33" s="91" t="n"/>
+      <c r="N33" s="101" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="92" t="inlineStr">
@@ -11701,6 +12012,13 @@
           <t>Medición eléctrica de resistencias calefactoras: continuidad y ohms</t>
         </is>
       </c>
+      <c r="D34" s="100" t="n"/>
+      <c r="E34" s="100" t="n"/>
+      <c r="F34" s="100" t="n"/>
+      <c r="G34" s="100" t="n"/>
+      <c r="H34" s="100" t="n"/>
+      <c r="I34" s="100" t="n"/>
+      <c r="J34" s="101" t="n"/>
       <c r="K34" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11712,6 +12030,7 @@
         </is>
       </c>
       <c r="M34" s="95" t="n"/>
+      <c r="N34" s="101" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="88" t="inlineStr">
@@ -11724,6 +12043,13 @@
           <t>Verificación del SSR RM1A48D50 como control de calefacción (7KPR1)</t>
         </is>
       </c>
+      <c r="D35" s="100" t="n"/>
+      <c r="E35" s="100" t="n"/>
+      <c r="F35" s="100" t="n"/>
+      <c r="G35" s="100" t="n"/>
+      <c r="H35" s="100" t="n"/>
+      <c r="I35" s="100" t="n"/>
+      <c r="J35" s="101" t="n"/>
       <c r="K35" s="90" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11735,6 +12061,7 @@
         </is>
       </c>
       <c r="M35" s="91" t="n"/>
+      <c r="N35" s="101" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="B36" s="92" t="inlineStr">
@@ -11747,6 +12074,13 @@
           <t>Verificación de uniformidad de calor en todos los rodillos</t>
         </is>
       </c>
+      <c r="D36" s="100" t="n"/>
+      <c r="E36" s="100" t="n"/>
+      <c r="F36" s="100" t="n"/>
+      <c r="G36" s="100" t="n"/>
+      <c r="H36" s="100" t="n"/>
+      <c r="I36" s="100" t="n"/>
+      <c r="J36" s="101" t="n"/>
       <c r="K36" s="94" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -11758,6 +12092,7 @@
         </is>
       </c>
       <c r="M36" s="95" t="n"/>
+      <c r="N36" s="101" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="96" t="inlineStr">
@@ -11765,6 +12100,11 @@
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
       </c>
+      <c r="N37" s="102" t="inlineStr">
+        <is>
+          <t>VOLTAJE ALIMENTACIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="97" t="inlineStr">
@@ -11827,6 +12167,27 @@
           <t>DIC</t>
         </is>
       </c>
+      <c r="N38" s="103" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O38" s="103" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="P38" s="103" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="Q38" s="103" t="inlineStr">
+        <is>
+          <t>Fuente 24VDC
+(20-25 V)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="94" t="inlineStr">
@@ -11889,6 +12250,10 @@
           <t>(   )</t>
         </is>
       </c>
+      <c r="N39" s="104" t="n"/>
+      <c r="O39" s="104" t="n"/>
+      <c r="P39" s="104" t="n"/>
+      <c r="Q39" s="104" t="n"/>
     </row>
     <row r="41" ht="50" customHeight="1">
       <c r="B41" s="85" t="inlineStr">
@@ -11916,81 +12281,82 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="75">
-    <mergeCell ref="C34:J34"/>
-    <mergeCell ref="B37:N37"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="M34:N34"/>
+  <mergeCells count="76">
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="C35:J35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="B37:M37"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="C32:J32"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="C13:J13"/>
     <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C33:J33"/>
     <mergeCell ref="C24:J24"/>
     <mergeCell ref="H41:I41"/>
+    <mergeCell ref="C26:J26"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="M34:N34"/>
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="C14:J14"/>
-    <mergeCell ref="I3:N3"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="C35:J35"/>
-    <mergeCell ref="C26:J26"/>
-    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="J41:N41"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="B42:G42"/>
     <mergeCell ref="C29:J29"/>
-    <mergeCell ref="M11:N11"/>
     <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="M31:N31"/>
     <mergeCell ref="C22:J22"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="I4:N4"/>
     <mergeCell ref="C31:J31"/>
-    <mergeCell ref="B6:J6"/>
     <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M30:N30"/>
     <mergeCell ref="C12:J12"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="N37:Q37"/>
     <mergeCell ref="C21:J21"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="C11:J11"/>
     <mergeCell ref="M28:N28"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="J41:N41"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="M8:N8"/>
     <mergeCell ref="C23:J23"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="M24:N24"/>
     <mergeCell ref="C7:J7"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="M23:N23"/>
     <mergeCell ref="M32:N32"/>
-    <mergeCell ref="C32:J32"/>
     <mergeCell ref="M14:N14"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C19:J19"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -9872,6 +9872,22 @@
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
     <col width="12.77734375" customWidth="1" min="2" max="17"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="7.8" customHeight="1"/>
@@ -11062,42 +11078,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="9.5546875" customWidth="1" min="1" max="1"/>
+    <col width="12.77734375" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="7.8" customHeight="1">
       <c r="B1" s="83" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="56.55" customHeight="1">
       <c r="B2" s="84" t="inlineStr">
         <is>
           <t>MANTENIMIENTO PREVENTIVO   —   CALENDER K1 EASY</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="97.8" customHeight="1">
       <c r="B3" s="85" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
@@ -11109,7 +11129,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="25.05" customHeight="1">
       <c r="B4" s="85" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
@@ -11121,7 +11141,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="46.2" customHeight="1">
       <c r="B5" s="85" t="inlineStr">
         <is>
           <t>Nombre de máquina:  Calender K1 Easy</t>
@@ -11133,7 +11153,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="25.05" customHeight="1">
       <c r="B6" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO</t>
@@ -11164,7 +11184,7 @@
       </c>
       <c r="N6" s="101" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="25.05" customHeight="1">
       <c r="B7" s="88" t="inlineStr">
         <is>
           <t>1</t>
@@ -11195,7 +11215,7 @@
       <c r="M7" s="91" t="n"/>
       <c r="N7" s="101" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="25.05" customHeight="1">
       <c r="B8" s="92" t="inlineStr">
         <is>
           <t>2</t>
@@ -11226,7 +11246,7 @@
       <c r="M8" s="95" t="n"/>
       <c r="N8" s="101" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="25.05" customHeight="1">
       <c r="B9" s="88" t="inlineStr">
         <is>
           <t>3</t>
@@ -11257,7 +11277,7 @@
       <c r="M9" s="91" t="n"/>
       <c r="N9" s="101" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="25.05" customHeight="1">
       <c r="B10" s="92" t="inlineStr">
         <is>
           <t>4</t>
@@ -11288,7 +11308,7 @@
       <c r="M10" s="95" t="n"/>
       <c r="N10" s="101" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="25.05" customHeight="1">
       <c r="B11" s="88" t="inlineStr">
         <is>
           <t>5</t>
@@ -11319,7 +11339,7 @@
       <c r="M11" s="91" t="n"/>
       <c r="N11" s="101" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="25.05" customHeight="1">
       <c r="B12" s="92" t="inlineStr">
         <is>
           <t>6</t>
@@ -11350,7 +11370,7 @@
       <c r="M12" s="95" t="n"/>
       <c r="N12" s="101" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="25.05" customHeight="1">
       <c r="B13" s="88" t="inlineStr">
         <is>
           <t>7</t>
@@ -11381,7 +11401,7 @@
       <c r="M13" s="91" t="n"/>
       <c r="N13" s="101" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="25.05" customHeight="1">
       <c r="B14" s="92" t="inlineStr">
         <is>
           <t>8</t>
@@ -11412,7 +11432,7 @@
       <c r="M14" s="95" t="n"/>
       <c r="N14" s="101" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="25.05" customHeight="1">
       <c r="B15" s="88" t="inlineStr">
         <is>
           <t>9</t>
@@ -11443,7 +11463,7 @@
       <c r="M15" s="91" t="n"/>
       <c r="N15" s="101" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="25.05" customHeight="1">
       <c r="B16" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
@@ -11474,7 +11494,7 @@
       </c>
       <c r="N16" s="101" t="n"/>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="25.05" customHeight="1">
       <c r="B17" s="88" t="inlineStr">
         <is>
           <t>10</t>
@@ -11505,7 +11525,7 @@
       <c r="M17" s="91" t="n"/>
       <c r="N17" s="101" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="25.05" customHeight="1">
       <c r="B18" s="92" t="inlineStr">
         <is>
           <t>11</t>
@@ -11536,7 +11556,7 @@
       <c r="M18" s="95" t="n"/>
       <c r="N18" s="101" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="25.05" customHeight="1">
       <c r="B19" s="88" t="inlineStr">
         <is>
           <t>12</t>
@@ -11567,7 +11587,7 @@
       <c r="M19" s="91" t="n"/>
       <c r="N19" s="101" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="25.05" customHeight="1">
       <c r="B20" s="92" t="inlineStr">
         <is>
           <t>13</t>
@@ -11598,7 +11618,7 @@
       <c r="M20" s="95" t="n"/>
       <c r="N20" s="101" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="25.05" customHeight="1">
       <c r="B21" s="88" t="inlineStr">
         <is>
           <t>14</t>
@@ -11629,7 +11649,7 @@
       <c r="M21" s="91" t="n"/>
       <c r="N21" s="101" t="n"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="25.05" customHeight="1">
       <c r="B22" s="92" t="inlineStr">
         <is>
           <t>15</t>
@@ -11660,7 +11680,7 @@
       <c r="M22" s="95" t="n"/>
       <c r="N22" s="101" t="n"/>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="25.05" customHeight="1">
       <c r="B23" s="88" t="inlineStr">
         <is>
           <t>16</t>
@@ -11691,7 +11711,7 @@
       <c r="M23" s="91" t="n"/>
       <c r="N23" s="101" t="n"/>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="25.05" customHeight="1">
       <c r="B24" s="92" t="inlineStr">
         <is>
           <t>17</t>
@@ -11722,7 +11742,7 @@
       <c r="M24" s="95" t="n"/>
       <c r="N24" s="101" t="n"/>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="25.05" customHeight="1">
       <c r="B25" s="88" t="inlineStr">
         <is>
           <t>18</t>
@@ -11753,7 +11773,7 @@
       <c r="M25" s="91" t="n"/>
       <c r="N25" s="101" t="n"/>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="25.05" customHeight="1">
       <c r="B26" s="92" t="inlineStr">
         <is>
           <t>19</t>
@@ -11784,7 +11804,7 @@
       <c r="M26" s="95" t="n"/>
       <c r="N26" s="101" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="25.05" customHeight="1">
       <c r="B27" s="88" t="inlineStr">
         <is>
           <t>20</t>
@@ -11815,7 +11835,7 @@
       <c r="M27" s="91" t="n"/>
       <c r="N27" s="101" t="n"/>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" ht="25.05" customHeight="1">
       <c r="B28" s="92" t="inlineStr">
         <is>
           <t>21</t>
@@ -11846,7 +11866,7 @@
       <c r="M28" s="95" t="n"/>
       <c r="N28" s="101" t="n"/>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="25.05" customHeight="1">
       <c r="B29" s="88" t="inlineStr">
         <is>
           <t>22</t>
@@ -11877,7 +11897,7 @@
       <c r="M29" s="91" t="n"/>
       <c r="N29" s="101" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="25.05" customHeight="1">
       <c r="B30" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">  CALENTAMIENTO</t>
@@ -11908,7 +11928,7 @@
       </c>
       <c r="N30" s="101" t="n"/>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="25.05" customHeight="1">
       <c r="B31" s="88" t="inlineStr">
         <is>
           <t>23</t>
@@ -11939,7 +11959,7 @@
       <c r="M31" s="91" t="n"/>
       <c r="N31" s="101" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="25.05" customHeight="1">
       <c r="B32" s="92" t="inlineStr">
         <is>
           <t>24</t>
@@ -11970,7 +11990,7 @@
       <c r="M32" s="95" t="n"/>
       <c r="N32" s="101" t="n"/>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="25.05" customHeight="1">
       <c r="B33" s="88" t="inlineStr">
         <is>
           <t>25</t>
@@ -12282,84 +12302,85 @@
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="C15:J15"/>
     <mergeCell ref="C33:J33"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="C14:J14"/>
     <mergeCell ref="I3:N3"/>
+    <mergeCell ref="B5:H5"/>
     <mergeCell ref="C35:J35"/>
+    <mergeCell ref="C26:J26"/>
     <mergeCell ref="M35:N35"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M20:N20"/>
     <mergeCell ref="I5:N5"/>
     <mergeCell ref="C20:J20"/>
     <mergeCell ref="B37:M37"/>
     <mergeCell ref="C25:J25"/>
     <mergeCell ref="M10:N10"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="C22:J22"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="I4:N4"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="C31:J31"/>
     <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="C32:J32"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="C26:J26"/>
-    <mergeCell ref="C10:J10"/>
-    <mergeCell ref="B6:J6"/>
     <mergeCell ref="C9:J9"/>
     <mergeCell ref="M13:N13"/>
     <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="M22:N22"/>
     <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="N37:Q37"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="M6:N6"/>
     <mergeCell ref="B41:G41"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M36:N36"/>
     <mergeCell ref="C36:J36"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M33:N33"/>
     <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M12:N12"/>
     <mergeCell ref="C27:J27"/>
     <mergeCell ref="J41:N41"/>
     <mergeCell ref="B2:N2"/>
+    <mergeCell ref="M8:N8"/>
     <mergeCell ref="M26:N26"/>
+    <mergeCell ref="B16:J16"/>
     <mergeCell ref="C8:J8"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="M24:N24"/>
     <mergeCell ref="C17:J17"/>
+    <mergeCell ref="C7:J7"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="B1:N1"/>
     <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="C32:J32"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="C13:J13"/>
     <mergeCell ref="C19:J19"/>
-    <mergeCell ref="C34:J34"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="C29:J29"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C22:J22"/>
-    <mergeCell ref="C31:J31"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="N37:Q37"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="C23:J23"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M14:N14"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -7217,7 +7217,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -11078,1305 +11078,1535 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Q42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:Q42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
-    <col width="12.77734375" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="12.77734375" customWidth="1" min="2" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="7.8" customHeight="1">
-      <c r="B1" s="83" t="inlineStr">
+    <row r="1" ht="7.8" customHeight="1"/>
+    <row r="2" ht="56.55" customHeight="1">
+      <c r="A2" s="11" t="n"/>
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="56.55" customHeight="1">
-      <c r="B2" s="84" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO PREVENTIVO   —   CALENDER K1 EASY</t>
-        </is>
-      </c>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+      <c r="L2" s="22" t="n"/>
+      <c r="M2" s="22" t="n"/>
+      <c r="N2" s="23" t="n"/>
+      <c r="O2" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> No. de Documento             A9.I1.F2
+ Revision:                                    00
+ Fecha:                        08/06/2026</t>
+        </is>
+      </c>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
-      <c r="B3" s="85" t="inlineStr">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="38" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO PREVENTIVO   — Calender K1 Easy</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
+      <c r="K3" s="22" t="n"/>
+      <c r="L3" s="22" t="n"/>
+      <c r="M3" s="22" t="n"/>
+      <c r="N3" s="23" t="n"/>
+      <c r="O3" s="35" t="n"/>
+      <c r="P3" s="22" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+    </row>
+    <row r="4" ht="25.05" customHeight="1">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
       </c>
-      <c r="I3" s="85" t="inlineStr">
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="22" t="n"/>
+      <c r="F4" s="22" t="n"/>
+      <c r="G4" s="22" t="n"/>
+      <c r="H4" s="22" t="n"/>
+      <c r="I4" s="23" t="n"/>
+      <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="25.05" customHeight="1">
-      <c r="B4" s="85" t="inlineStr">
+      <c r="K4" s="22" t="n"/>
+      <c r="L4" s="22" t="n"/>
+      <c r="M4" s="22" t="n"/>
+      <c r="N4" s="22" t="n"/>
+      <c r="O4" s="22" t="n"/>
+      <c r="P4" s="22" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+    </row>
+    <row r="5" ht="46.2" customHeight="1">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
       </c>
-      <c r="I4" s="85" t="inlineStr">
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="23" t="n"/>
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar EPP. Para revisiones eléctricas: PARO TOTAL.</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="46.2" customHeight="1">
-      <c r="B5" s="85" t="inlineStr">
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="22" t="n"/>
+      <c r="M5" s="22" t="n"/>
+      <c r="N5" s="22" t="n"/>
+      <c r="O5" s="22" t="n"/>
+      <c r="P5" s="22" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+    </row>
+    <row r="6" ht="25.05" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>Nombre de máquina:  Calender K1 Easy</t>
         </is>
       </c>
-      <c r="I5" s="85" t="inlineStr">
-        <is>
-          <t>Número de máquina:  K1-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25.05" customHeight="1">
-      <c r="B6" s="86" t="inlineStr">
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t>Número de máquina:  CK01</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="22" t="n"/>
+      <c r="P6" s="22" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="25.05" customHeight="1">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  MECÁNICO</t>
         </is>
       </c>
-      <c r="C6" s="100" t="n"/>
-      <c r="D6" s="100" t="n"/>
-      <c r="E6" s="100" t="n"/>
-      <c r="F6" s="100" t="n"/>
-      <c r="G6" s="100" t="n"/>
-      <c r="H6" s="100" t="n"/>
-      <c r="I6" s="100" t="n"/>
-      <c r="J6" s="101" t="n"/>
-      <c r="K6" s="87" t="inlineStr">
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="1" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L6" s="87" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M6" s="87" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>COMENTARIOS</t>
         </is>
       </c>
-      <c r="N6" s="101" t="n"/>
-    </row>
-    <row r="7" ht="25.05" customHeight="1">
-      <c r="B7" s="88" t="inlineStr">
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+    </row>
+    <row r="8" ht="25.05" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C7" s="89" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Inspección visual: ruidos, vibraciones y fugas en rodillos</t>
         </is>
       </c>
-      <c r="D7" s="100" t="n"/>
-      <c r="E7" s="100" t="n"/>
-      <c r="F7" s="100" t="n"/>
-      <c r="G7" s="100" t="n"/>
-      <c r="H7" s="100" t="n"/>
-      <c r="I7" s="100" t="n"/>
-      <c r="J7" s="101" t="n"/>
-      <c r="K7" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L7" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M7" s="91" t="n"/>
-      <c r="N7" s="101" t="n"/>
-    </row>
-    <row r="8" ht="25.05" customHeight="1">
-      <c r="B8" s="92" t="inlineStr">
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="23" t="n"/>
+    </row>
+    <row r="9" ht="25.05" customHeight="1">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C8" s="93" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Lubricación de rodillos de calandria (baleros y chumaceras)</t>
         </is>
       </c>
-      <c r="D8" s="100" t="n"/>
-      <c r="E8" s="100" t="n"/>
-      <c r="F8" s="100" t="n"/>
-      <c r="G8" s="100" t="n"/>
-      <c r="H8" s="100" t="n"/>
-      <c r="I8" s="100" t="n"/>
-      <c r="J8" s="101" t="n"/>
-      <c r="K8" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L8" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M8" s="95" t="n"/>
-      <c r="N8" s="101" t="n"/>
-    </row>
-    <row r="9" ht="25.05" customHeight="1">
-      <c r="B9" s="88" t="inlineStr">
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="n"/>
+      <c r="P9" s="22" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+    </row>
+    <row r="10" ht="25.05" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C9" s="89" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Revisión y lubricación de cadena de transmisión y sprockets</t>
         </is>
       </c>
-      <c r="D9" s="100" t="n"/>
-      <c r="E9" s="100" t="n"/>
-      <c r="F9" s="100" t="n"/>
-      <c r="G9" s="100" t="n"/>
-      <c r="H9" s="100" t="n"/>
-      <c r="I9" s="100" t="n"/>
-      <c r="J9" s="101" t="n"/>
-      <c r="K9" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L9" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M9" s="91" t="n"/>
-      <c r="N9" s="101" t="n"/>
-    </row>
-    <row r="10" ht="25.05" customHeight="1">
-      <c r="B10" s="92" t="inlineStr">
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="25.05" customHeight="1">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C10" s="93" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>Verificación de tensión de cadena (deflexión máx. 1% de longitud)</t>
         </is>
       </c>
-      <c r="D10" s="100" t="n"/>
-      <c r="E10" s="100" t="n"/>
-      <c r="F10" s="100" t="n"/>
-      <c r="G10" s="100" t="n"/>
-      <c r="H10" s="100" t="n"/>
-      <c r="I10" s="100" t="n"/>
-      <c r="J10" s="101" t="n"/>
-      <c r="K10" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L10" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M10" s="95" t="n"/>
-      <c r="N10" s="101" t="n"/>
-    </row>
-    <row r="11" ht="25.05" customHeight="1">
-      <c r="B11" s="88" t="inlineStr">
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="25.05" customHeight="1">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C11" s="89" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Revisión de caja reductora: nivel y calidad de aceite</t>
         </is>
       </c>
-      <c r="D11" s="100" t="n"/>
-      <c r="E11" s="100" t="n"/>
-      <c r="F11" s="100" t="n"/>
-      <c r="G11" s="100" t="n"/>
-      <c r="H11" s="100" t="n"/>
-      <c r="I11" s="100" t="n"/>
-      <c r="J11" s="101" t="n"/>
-      <c r="K11" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L11" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M11" s="91" t="n"/>
-      <c r="N11" s="101" t="n"/>
-    </row>
-    <row r="12" ht="25.05" customHeight="1">
-      <c r="B12" s="92" t="inlineStr">
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="23" t="n"/>
+    </row>
+    <row r="13" ht="25.05" customHeight="1">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C12" s="93" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>Verificación de alineación y paralelismo de rodillos</t>
         </is>
       </c>
-      <c r="D12" s="100" t="n"/>
-      <c r="E12" s="100" t="n"/>
-      <c r="F12" s="100" t="n"/>
-      <c r="G12" s="100" t="n"/>
-      <c r="H12" s="100" t="n"/>
-      <c r="I12" s="100" t="n"/>
-      <c r="J12" s="101" t="n"/>
-      <c r="K12" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L12" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M12" s="95" t="n"/>
-      <c r="N12" s="101" t="n"/>
-    </row>
-    <row r="13" ht="25.05" customHeight="1">
-      <c r="B13" s="88" t="inlineStr">
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="22" t="n"/>
+      <c r="P13" s="22" t="n"/>
+      <c r="Q13" s="23" t="n"/>
+    </row>
+    <row r="14" ht="25.05" customHeight="1">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C13" s="89" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Limpieza de rodillos y superficie de contacto (residuos de material)</t>
         </is>
       </c>
-      <c r="D13" s="100" t="n"/>
-      <c r="E13" s="100" t="n"/>
-      <c r="F13" s="100" t="n"/>
-      <c r="G13" s="100" t="n"/>
-      <c r="H13" s="100" t="n"/>
-      <c r="I13" s="100" t="n"/>
-      <c r="J13" s="101" t="n"/>
-      <c r="K13" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L13" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M13" s="91" t="n"/>
-      <c r="N13" s="101" t="n"/>
-    </row>
-    <row r="14" ht="25.05" customHeight="1">
-      <c r="B14" s="92" t="inlineStr">
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="23" t="n"/>
+    </row>
+    <row r="15" ht="25.05" customHeight="1">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C14" s="93" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>Revisión de tornillería y fijaciones estructurales</t>
         </is>
       </c>
-      <c r="D14" s="100" t="n"/>
-      <c r="E14" s="100" t="n"/>
-      <c r="F14" s="100" t="n"/>
-      <c r="G14" s="100" t="n"/>
-      <c r="H14" s="100" t="n"/>
-      <c r="I14" s="100" t="n"/>
-      <c r="J14" s="101" t="n"/>
-      <c r="K14" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L14" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M14" s="95" t="n"/>
-      <c r="N14" s="101" t="n"/>
-    </row>
-    <row r="15" ht="25.05" customHeight="1">
-      <c r="B15" s="88" t="inlineStr">
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+    </row>
+    <row r="16" ht="25.05" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C15" s="89" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Verificación del servo motor TECO JSMA-PSC44BK (temperatura y vibración)</t>
         </is>
       </c>
-      <c r="D15" s="100" t="n"/>
-      <c r="E15" s="100" t="n"/>
-      <c r="F15" s="100" t="n"/>
-      <c r="G15" s="100" t="n"/>
-      <c r="H15" s="100" t="n"/>
-      <c r="I15" s="100" t="n"/>
-      <c r="J15" s="101" t="n"/>
-      <c r="K15" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L15" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M15" s="91" t="n"/>
-      <c r="N15" s="101" t="n"/>
-    </row>
-    <row r="16" ht="25.05" customHeight="1">
-      <c r="B16" s="86" t="inlineStr">
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22" t="n"/>
+      <c r="P16" s="22" t="n"/>
+      <c r="Q16" s="23" t="n"/>
+    </row>
+    <row r="17" ht="25.05" customHeight="1">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ELÉCTRICO</t>
         </is>
       </c>
-      <c r="C16" s="100" t="n"/>
-      <c r="D16" s="100" t="n"/>
-      <c r="E16" s="100" t="n"/>
-      <c r="F16" s="100" t="n"/>
-      <c r="G16" s="100" t="n"/>
-      <c r="H16" s="100" t="n"/>
-      <c r="I16" s="100" t="n"/>
-      <c r="J16" s="101" t="n"/>
-      <c r="K16" s="87" t="inlineStr">
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="1" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L16" s="87" t="inlineStr">
+      <c r="L17" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M16" s="87" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>COMENTARIOS</t>
         </is>
       </c>
-      <c r="N16" s="101" t="n"/>
-    </row>
-    <row r="17" ht="25.05" customHeight="1">
-      <c r="B17" s="88" t="inlineStr">
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="23" t="n"/>
+    </row>
+    <row r="18" ht="25.05" customHeight="1">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C17" s="89" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Verificación del HMI MCU 01 TS: alarmas, indicadores y pantalla táctil</t>
         </is>
       </c>
-      <c r="D17" s="100" t="n"/>
-      <c r="E17" s="100" t="n"/>
-      <c r="F17" s="100" t="n"/>
-      <c r="G17" s="100" t="n"/>
-      <c r="H17" s="100" t="n"/>
-      <c r="I17" s="100" t="n"/>
-      <c r="J17" s="101" t="n"/>
-      <c r="K17" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L17" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M17" s="91" t="n"/>
-      <c r="N17" s="101" t="n"/>
-    </row>
-    <row r="18" ht="25.05" customHeight="1">
-      <c r="B18" s="92" t="inlineStr">
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="23" t="n"/>
+    </row>
+    <row r="19" ht="25.05" customHeight="1">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="93" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>Limpieza de tablero eléctrico y revisión de cableado y ducterías</t>
         </is>
       </c>
-      <c r="D18" s="100" t="n"/>
-      <c r="E18" s="100" t="n"/>
-      <c r="F18" s="100" t="n"/>
-      <c r="G18" s="100" t="n"/>
-      <c r="H18" s="100" t="n"/>
-      <c r="I18" s="100" t="n"/>
-      <c r="J18" s="101" t="n"/>
-      <c r="K18" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L18" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M18" s="95" t="n"/>
-      <c r="N18" s="101" t="n"/>
-    </row>
-    <row r="19" ht="25.05" customHeight="1">
-      <c r="B19" s="88" t="inlineStr">
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="25.05" customHeight="1">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="89" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Reapriete de terminales y conexiones eléctricas</t>
         </is>
       </c>
-      <c r="D19" s="100" t="n"/>
-      <c r="E19" s="100" t="n"/>
-      <c r="F19" s="100" t="n"/>
-      <c r="G19" s="100" t="n"/>
-      <c r="H19" s="100" t="n"/>
-      <c r="I19" s="100" t="n"/>
-      <c r="J19" s="101" t="n"/>
-      <c r="K19" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L19" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M19" s="91" t="n"/>
-      <c r="N19" s="101" t="n"/>
-    </row>
-    <row r="20" ht="25.05" customHeight="1">
-      <c r="B20" s="92" t="inlineStr">
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="25.05" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="93" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>Revisión de portafusibles Lovato FB01 B 2P: 2FU1, 6FU1, 7FU1</t>
         </is>
       </c>
-      <c r="D20" s="100" t="n"/>
-      <c r="E20" s="100" t="n"/>
-      <c r="F20" s="100" t="n"/>
-      <c r="G20" s="100" t="n"/>
-      <c r="H20" s="100" t="n"/>
-      <c r="I20" s="100" t="n"/>
-      <c r="J20" s="101" t="n"/>
-      <c r="K20" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L20" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M20" s="95" t="n"/>
-      <c r="N20" s="101" t="n"/>
-    </row>
-    <row r="21" ht="25.05" customHeight="1">
-      <c r="B21" s="88" t="inlineStr">
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M21" s="27" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="23" t="n"/>
+    </row>
+    <row r="22" ht="25.05" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="89" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Verificación del relé de seguridad Allen-Bradley MSR126.1T (7K1)</t>
         </is>
       </c>
-      <c r="D21" s="100" t="n"/>
-      <c r="E21" s="100" t="n"/>
-      <c r="F21" s="100" t="n"/>
-      <c r="G21" s="100" t="n"/>
-      <c r="H21" s="100" t="n"/>
-      <c r="I21" s="100" t="n"/>
-      <c r="J21" s="101" t="n"/>
-      <c r="K21" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L21" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M21" s="91" t="n"/>
-      <c r="N21" s="101" t="n"/>
-    </row>
-    <row r="22" ht="25.05" customHeight="1">
-      <c r="B22" s="92" t="inlineStr">
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="n"/>
+      <c r="N22" s="22" t="n"/>
+      <c r="O22" s="22" t="n"/>
+      <c r="P22" s="22" t="n"/>
+      <c r="Q22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="25.05" customHeight="1">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="93" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>Revisión del servo drive TECO: parámetros, fallas y conexiones</t>
         </is>
       </c>
-      <c r="D22" s="100" t="n"/>
-      <c r="E22" s="100" t="n"/>
-      <c r="F22" s="100" t="n"/>
-      <c r="G22" s="100" t="n"/>
-      <c r="H22" s="100" t="n"/>
-      <c r="I22" s="100" t="n"/>
-      <c r="J22" s="101" t="n"/>
-      <c r="K22" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L22" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M22" s="95" t="n"/>
-      <c r="N22" s="101" t="n"/>
-    </row>
-    <row r="23" ht="25.05" customHeight="1">
-      <c r="B23" s="88" t="inlineStr">
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="22" t="n"/>
+      <c r="Q23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="25.05" customHeight="1">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C23" s="89" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Verificación de fuente de poder Omron S8VK-C12024 (salida 24 VDC)</t>
         </is>
       </c>
-      <c r="D23" s="100" t="n"/>
-      <c r="E23" s="100" t="n"/>
-      <c r="F23" s="100" t="n"/>
-      <c r="G23" s="100" t="n"/>
-      <c r="H23" s="100" t="n"/>
-      <c r="I23" s="100" t="n"/>
-      <c r="J23" s="101" t="n"/>
-      <c r="K23" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L23" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M23" s="91" t="n"/>
-      <c r="N23" s="101" t="n"/>
-    </row>
-    <row r="24" ht="25.05" customHeight="1">
-      <c r="B24" s="92" t="inlineStr">
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="25.05" customHeight="1">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C24" s="93" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>Revisión del relevador SSR RM1A48D50 (7KPR1): temperatura y sujeción</t>
         </is>
       </c>
-      <c r="D24" s="100" t="n"/>
-      <c r="E24" s="100" t="n"/>
-      <c r="F24" s="100" t="n"/>
-      <c r="G24" s="100" t="n"/>
-      <c r="H24" s="100" t="n"/>
-      <c r="I24" s="100" t="n"/>
-      <c r="J24" s="101" t="n"/>
-      <c r="K24" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L24" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M24" s="95" t="n"/>
-      <c r="N24" s="101" t="n"/>
-    </row>
-    <row r="25" ht="25.05" customHeight="1">
-      <c r="B25" s="88" t="inlineStr">
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="22" t="n"/>
+      <c r="P25" s="22" t="n"/>
+      <c r="Q25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="25.05" customHeight="1">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C25" s="89" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Prueba funcional: paro de emergencia y botón REAJUSTE EMERGENCIA</t>
         </is>
       </c>
-      <c r="D25" s="100" t="n"/>
-      <c r="E25" s="100" t="n"/>
-      <c r="F25" s="100" t="n"/>
-      <c r="G25" s="100" t="n"/>
-      <c r="H25" s="100" t="n"/>
-      <c r="I25" s="100" t="n"/>
-      <c r="J25" s="101" t="n"/>
-      <c r="K25" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L25" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M25" s="91" t="n"/>
-      <c r="N25" s="101" t="n"/>
-    </row>
-    <row r="26" ht="25.05" customHeight="1">
-      <c r="B26" s="92" t="inlineStr">
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22" t="n"/>
+      <c r="P26" s="22" t="n"/>
+      <c r="Q26" s="23" t="n"/>
+    </row>
+    <row r="27" ht="25.05" customHeight="1">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C26" s="93" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>Verificación de interruptor de seguridad Pizzato (funcionamiento y ajuste)</t>
         </is>
       </c>
-      <c r="D26" s="100" t="n"/>
-      <c r="E26" s="100" t="n"/>
-      <c r="F26" s="100" t="n"/>
-      <c r="G26" s="100" t="n"/>
-      <c r="H26" s="100" t="n"/>
-      <c r="I26" s="100" t="n"/>
-      <c r="J26" s="101" t="n"/>
-      <c r="K26" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L26" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M26" s="95" t="n"/>
-      <c r="N26" s="101" t="n"/>
-    </row>
-    <row r="27" ht="25.05" customHeight="1">
-      <c r="B27" s="88" t="inlineStr">
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M27" s="63" t="n"/>
+      <c r="N27" s="81" t="n"/>
+      <c r="O27" s="81" t="n"/>
+      <c r="P27" s="81" t="n"/>
+      <c r="Q27" s="82" t="n"/>
+    </row>
+    <row r="28" ht="25.05" customHeight="1">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C27" s="89" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>Revisión del módulo I/O SHS DIN (señales de entrada/salida)</t>
         </is>
       </c>
-      <c r="D27" s="100" t="n"/>
-      <c r="E27" s="100" t="n"/>
-      <c r="F27" s="100" t="n"/>
-      <c r="G27" s="100" t="n"/>
-      <c r="H27" s="100" t="n"/>
-      <c r="I27" s="100" t="n"/>
-      <c r="J27" s="101" t="n"/>
-      <c r="K27" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L27" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M27" s="91" t="n"/>
-      <c r="N27" s="101" t="n"/>
-    </row>
-    <row r="28" ht="25.05" customHeight="1">
-      <c r="B28" s="92" t="inlineStr">
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M28" s="66" t="n"/>
+      <c r="N28" s="50" t="n"/>
+      <c r="O28" s="50" t="n"/>
+      <c r="P28" s="50" t="n"/>
+      <c r="Q28" s="51" t="n"/>
+    </row>
+    <row r="29" ht="25.05" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C28" s="93" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Verificación del interruptor principal ABB OT25F4N2 (2QS1)</t>
         </is>
       </c>
-      <c r="D28" s="100" t="n"/>
-      <c r="E28" s="100" t="n"/>
-      <c r="F28" s="100" t="n"/>
-      <c r="G28" s="100" t="n"/>
-      <c r="H28" s="100" t="n"/>
-      <c r="I28" s="100" t="n"/>
-      <c r="J28" s="101" t="n"/>
-      <c r="K28" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L28" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M28" s="95" t="n"/>
-      <c r="N28" s="101" t="n"/>
-    </row>
-    <row r="29" ht="25.05" customHeight="1">
-      <c r="B29" s="88" t="inlineStr">
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M29" s="66" t="n"/>
+      <c r="N29" s="50" t="n"/>
+      <c r="O29" s="50" t="n"/>
+      <c r="P29" s="50" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="25.05" customHeight="1">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C29" s="89" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>Verificación de tierras físicas y continuidad de tierra</t>
         </is>
       </c>
-      <c r="D29" s="100" t="n"/>
-      <c r="E29" s="100" t="n"/>
-      <c r="F29" s="100" t="n"/>
-      <c r="G29" s="100" t="n"/>
-      <c r="H29" s="100" t="n"/>
-      <c r="I29" s="100" t="n"/>
-      <c r="J29" s="101" t="n"/>
-      <c r="K29" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L29" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M29" s="91" t="n"/>
-      <c r="N29" s="101" t="n"/>
-    </row>
-    <row r="30" ht="25.05" customHeight="1">
-      <c r="B30" s="86" t="inlineStr">
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M30" s="66" t="n"/>
+      <c r="N30" s="50" t="n"/>
+      <c r="O30" s="50" t="n"/>
+      <c r="P30" s="50" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+    </row>
+    <row r="31" ht="25.05" customHeight="1">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  CALENTAMIENTO</t>
         </is>
       </c>
-      <c r="C30" s="100" t="n"/>
-      <c r="D30" s="100" t="n"/>
-      <c r="E30" s="100" t="n"/>
-      <c r="F30" s="100" t="n"/>
-      <c r="G30" s="100" t="n"/>
-      <c r="H30" s="100" t="n"/>
-      <c r="I30" s="100" t="n"/>
-      <c r="J30" s="101" t="n"/>
-      <c r="K30" s="87" t="inlineStr">
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="1" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="L30" s="87" t="inlineStr">
+      <c r="L31" s="27" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="M30" s="87" t="inlineStr">
+      <c r="M31" s="27" t="inlineStr">
         <is>
           <t>COMENTARIOS</t>
         </is>
       </c>
-      <c r="N30" s="101" t="n"/>
-    </row>
-    <row r="31" ht="25.05" customHeight="1">
-      <c r="B31" s="88" t="inlineStr">
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="23" t="n"/>
+    </row>
+    <row r="32" ht="25.05" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C31" s="89" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>Verificación de temperatura de trabajo de rodillos calefactores</t>
         </is>
       </c>
-      <c r="D31" s="100" t="n"/>
-      <c r="E31" s="100" t="n"/>
-      <c r="F31" s="100" t="n"/>
-      <c r="G31" s="100" t="n"/>
-      <c r="H31" s="100" t="n"/>
-      <c r="I31" s="100" t="n"/>
-      <c r="J31" s="101" t="n"/>
-      <c r="K31" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L31" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M31" s="91" t="n"/>
-      <c r="N31" s="101" t="n"/>
-    </row>
-    <row r="32" ht="25.05" customHeight="1">
-      <c r="B32" s="92" t="inlineStr">
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M32" s="66" t="n"/>
+      <c r="N32" s="50" t="n"/>
+      <c r="O32" s="50" t="n"/>
+      <c r="P32" s="50" t="n"/>
+      <c r="Q32" s="51" t="n"/>
+    </row>
+    <row r="33" ht="25.05" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="C32" s="93" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Limpieza de resistencias calefactoras (polvo y residuos de material)</t>
         </is>
       </c>
-      <c r="D32" s="100" t="n"/>
-      <c r="E32" s="100" t="n"/>
-      <c r="F32" s="100" t="n"/>
-      <c r="G32" s="100" t="n"/>
-      <c r="H32" s="100" t="n"/>
-      <c r="I32" s="100" t="n"/>
-      <c r="J32" s="101" t="n"/>
-      <c r="K32" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L32" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M32" s="95" t="n"/>
-      <c r="N32" s="101" t="n"/>
-    </row>
-    <row r="33" ht="25.05" customHeight="1">
-      <c r="B33" s="88" t="inlineStr">
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M33" s="66" t="n"/>
+      <c r="N33" s="50" t="n"/>
+      <c r="O33" s="50" t="n"/>
+      <c r="P33" s="50" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+    </row>
+    <row r="34" ht="17.4" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C33" s="89" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Calibración de termocuplas y verificación de control de temperatura</t>
         </is>
       </c>
-      <c r="D33" s="100" t="n"/>
-      <c r="E33" s="100" t="n"/>
-      <c r="F33" s="100" t="n"/>
-      <c r="G33" s="100" t="n"/>
-      <c r="H33" s="100" t="n"/>
-      <c r="I33" s="100" t="n"/>
-      <c r="J33" s="101" t="n"/>
-      <c r="K33" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L33" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M33" s="91" t="n"/>
-      <c r="N33" s="101" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="92" t="inlineStr">
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="23" t="n"/>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M34" s="23" t="n"/>
+      <c r="N34" s="22" t="n"/>
+      <c r="O34" s="22" t="n"/>
+      <c r="P34" s="22" t="n"/>
+      <c r="Q34" s="23" t="n"/>
+    </row>
+    <row r="35" ht="17.4" customHeight="1">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="C34" s="93" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>Medición eléctrica de resistencias calefactoras: continuidad y ohms</t>
         </is>
       </c>
-      <c r="D34" s="100" t="n"/>
-      <c r="E34" s="100" t="n"/>
-      <c r="F34" s="100" t="n"/>
-      <c r="G34" s="100" t="n"/>
-      <c r="H34" s="100" t="n"/>
-      <c r="I34" s="100" t="n"/>
-      <c r="J34" s="101" t="n"/>
-      <c r="K34" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L34" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M34" s="95" t="n"/>
-      <c r="N34" s="101" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="88" t="inlineStr">
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="22" t="n"/>
+      <c r="O35" s="22" t="n"/>
+      <c r="P35" s="22" t="n"/>
+      <c r="Q35" s="23" t="n"/>
+    </row>
+    <row r="36" ht="17.4" customHeight="1">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="C35" s="89" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Verificación del SSR RM1A48D50 como control de calefacción (7KPR1)</t>
         </is>
       </c>
-      <c r="D35" s="100" t="n"/>
-      <c r="E35" s="100" t="n"/>
-      <c r="F35" s="100" t="n"/>
-      <c r="G35" s="100" t="n"/>
-      <c r="H35" s="100" t="n"/>
-      <c r="I35" s="100" t="n"/>
-      <c r="J35" s="101" t="n"/>
-      <c r="K35" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L35" s="90" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M35" s="91" t="n"/>
-      <c r="N35" s="101" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="92" t="inlineStr">
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="22" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="22" t="n"/>
+      <c r="O36" s="22" t="n"/>
+      <c r="P36" s="22" t="n"/>
+      <c r="Q36" s="23" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="C36" s="93" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>Verificación de uniformidad de calor en todos los rodillos</t>
         </is>
       </c>
-      <c r="D36" s="100" t="n"/>
-      <c r="E36" s="100" t="n"/>
-      <c r="F36" s="100" t="n"/>
-      <c r="G36" s="100" t="n"/>
-      <c r="H36" s="100" t="n"/>
-      <c r="I36" s="100" t="n"/>
-      <c r="J36" s="101" t="n"/>
-      <c r="K36" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L36" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M36" s="95" t="n"/>
-      <c r="N36" s="101" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="96" t="inlineStr">
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="22" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M37" s="51" t="n"/>
+      <c r="N37" s="50" t="n"/>
+      <c r="O37" s="50" t="n"/>
+      <c r="P37" s="50" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+    </row>
+    <row r="38" ht="14.4" customHeight="1">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>CALENDARIO  DE  MANTENIMIENTO</t>
         </is>
       </c>
-      <c r="N37" s="102" t="inlineStr">
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="22" t="n"/>
+      <c r="K38" s="22" t="n"/>
+      <c r="L38" s="22" t="n"/>
+      <c r="M38" s="23" t="n"/>
+      <c r="N38" s="43" t="inlineStr">
         <is>
           <t>VOLTAJE ALIMENTACIÓN</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="97" t="inlineStr">
+      <c r="O38" s="22" t="n"/>
+      <c r="P38" s="22" t="n"/>
+      <c r="Q38" s="23" t="n"/>
+    </row>
+    <row r="39" ht="14.4" customHeight="1">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>ENE</t>
         </is>
       </c>
-      <c r="C38" s="97" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="D38" s="97" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="E38" s="97" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>ABR</t>
         </is>
       </c>
-      <c r="F38" s="97" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G38" s="97" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="H38" s="97" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="I38" s="97" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>AGO</t>
         </is>
       </c>
-      <c r="J38" s="97" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="K38" s="97" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L38" s="97" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="M38" s="97" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>DIC</t>
         </is>
       </c>
-      <c r="N38" s="103" t="inlineStr">
+      <c r="N39" s="6" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="O38" s="103" t="inlineStr">
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="P38" s="103" t="inlineStr">
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="Q38" s="103" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>Fuente 24VDC
 (20-25 V)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="C39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="D39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="E39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="F39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="G39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="H39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="I39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="J39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="K39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M39" s="94" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="N39" s="104" t="n"/>
-      <c r="O39" s="104" t="n"/>
-      <c r="P39" s="104" t="n"/>
-      <c r="Q39" s="104" t="n"/>
-    </row>
-    <row r="41" ht="50" customHeight="1">
-      <c r="B41" s="85" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="H41" s="98" t="inlineStr">
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+      <c r="E41" s="50" t="n"/>
+      <c r="F41" s="50" t="n"/>
+      <c r="G41" s="51" t="n"/>
+      <c r="H41" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
-      <c r="J41" s="99" t="inlineStr">
+      <c r="I41" s="75" t="n"/>
+      <c r="J41" s="75" t="n"/>
+      <c r="K41" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Mantenimiento:
 Firma: _____________________________</t>
         </is>
       </c>
+      <c r="L41" s="50" t="n"/>
+      <c r="M41" s="50" t="n"/>
+      <c r="N41" s="50" t="n"/>
+      <c r="O41" s="50" t="n"/>
+      <c r="P41" s="50" t="n"/>
+      <c r="Q41" s="51" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="98" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+      <c r="E42" s="50" t="n"/>
+      <c r="F42" s="50" t="n"/>
+      <c r="G42" s="51" t="n"/>
+      <c r="K42" s="39" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="L42" s="50" t="n"/>
+      <c r="M42" s="50" t="n"/>
+      <c r="N42" s="50" t="n"/>
+      <c r="O42" s="50" t="n"/>
+      <c r="P42" s="50" t="n"/>
+      <c r="Q42" s="51" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
+  <mergeCells count="80">
+    <mergeCell ref="M34:Q34"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="C35:J35"/>
+    <mergeCell ref="M35:Q35"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="J6:Q6"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="M30:Q30"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="M33:Q33"/>
+    <mergeCell ref="M28:Q28"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="M27:Q27"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="K41:Q41"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="C32:J32"/>
+    <mergeCell ref="M32:Q32"/>
+    <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="N38:Q38"/>
     <mergeCell ref="C34:J34"/>
     <mergeCell ref="B42:G42"/>
-    <mergeCell ref="M34:N34"/>
     <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C33:J33"/>
     <mergeCell ref="C24:J24"/>
+    <mergeCell ref="J5:Q5"/>
     <mergeCell ref="H41:I41"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="C35:J35"/>
+    <mergeCell ref="M9:Q9"/>
+    <mergeCell ref="B38:M38"/>
     <mergeCell ref="C26:J26"/>
-    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M20:Q20"/>
     <mergeCell ref="C29:J29"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="B37:M37"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:Q11"/>
     <mergeCell ref="C10:J10"/>
-    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="M10:Q10"/>
     <mergeCell ref="C22:J22"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="C31:J31"/>
-    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="M31:Q31"/>
     <mergeCell ref="C9:J9"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="J4:Q4"/>
     <mergeCell ref="C12:J12"/>
-    <mergeCell ref="N37:Q37"/>
     <mergeCell ref="C21:J21"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="M15:Q15"/>
     <mergeCell ref="B41:G41"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="M37:Q37"/>
     <mergeCell ref="C36:J36"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="J41:N41"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M36:Q36"/>
+    <mergeCell ref="M18:Q18"/>
     <mergeCell ref="C23:J23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="C32:J32"/>
-    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="M29:Q29"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="B31:J31"/>
     <mergeCell ref="C28:J28"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="K42:Q42"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -157,6 +157,18 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001b5e20"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001b5e20"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="17">
@@ -589,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -840,6 +852,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11117,9 +11135,13 @@
       <c r="P2" s="50" t="n"/>
       <c r="Q2" s="51" t="n"/>
     </row>
-    <row r="3" ht="97.8" customHeight="1">
+    <row r="3" ht="50" customHeight="1">
       <c r="A3" s="11" t="n"/>
-      <c r="B3" s="36" t="n"/>
+      <c r="B3" s="105" t="inlineStr">
+        <is>
+          <t>AD-PACK</t>
+        </is>
+      </c>
       <c r="C3" s="22" t="n"/>
       <c r="D3" s="23" t="n"/>
       <c r="E3" s="38" t="inlineStr">
@@ -11136,7 +11158,12 @@
       <c r="L3" s="22" t="n"/>
       <c r="M3" s="22" t="n"/>
       <c r="N3" s="23" t="n"/>
-      <c r="O3" s="35" t="n"/>
+      <c r="O3" s="106" t="inlineStr">
+        <is>
+          <t>CONVERSIÓN
+by AD-PACK</t>
+        </is>
+      </c>
       <c r="P3" s="22" t="n"/>
       <c r="Q3" s="23" t="n"/>
     </row>
@@ -12529,81 +12556,81 @@
   </sheetData>
   <mergeCells count="80">
     <mergeCell ref="M34:Q34"/>
-    <mergeCell ref="C30:J30"/>
     <mergeCell ref="C33:J33"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="C14:J14"/>
     <mergeCell ref="C35:J35"/>
-    <mergeCell ref="M35:Q35"/>
     <mergeCell ref="C20:J20"/>
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="C25:J25"/>
     <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="M30:Q30"/>
     <mergeCell ref="M21:Q21"/>
     <mergeCell ref="C11:J11"/>
-    <mergeCell ref="M33:Q33"/>
-    <mergeCell ref="M28:Q28"/>
-    <mergeCell ref="C27:J27"/>
     <mergeCell ref="M27:Q27"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="C8:J8"/>
     <mergeCell ref="K41:Q41"/>
     <mergeCell ref="M24:Q24"/>
     <mergeCell ref="C32:J32"/>
-    <mergeCell ref="M32:Q32"/>
-    <mergeCell ref="M14:Q14"/>
     <mergeCell ref="B5:I5"/>
-    <mergeCell ref="C19:J19"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="C34:J34"/>
-    <mergeCell ref="B42:G42"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C24:J24"/>
     <mergeCell ref="J5:Q5"/>
     <mergeCell ref="H41:I41"/>
     <mergeCell ref="M9:Q9"/>
-    <mergeCell ref="B38:M38"/>
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="C29:J29"/>
     <mergeCell ref="M11:Q11"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="C16:J16"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="C22:J22"/>
     <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="M13:Q13"/>
     <mergeCell ref="M31:Q31"/>
     <mergeCell ref="C9:J9"/>
-    <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="M16:Q16"/>
     <mergeCell ref="J4:Q4"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="C21:J21"/>
-    <mergeCell ref="M25:Q25"/>
     <mergeCell ref="M15:Q15"/>
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="M37:Q37"/>
     <mergeCell ref="C36:J36"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="M26:Q26"/>
+    <mergeCell ref="M29:Q29"/>
+    <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="M35:Q35"/>
+    <mergeCell ref="M30:Q30"/>
+    <mergeCell ref="M33:Q33"/>
+    <mergeCell ref="M28:Q28"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="M32:Q32"/>
+    <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B38:M38"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="C22:J22"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="C21:J21"/>
+    <mergeCell ref="M25:Q25"/>
     <mergeCell ref="M36:Q36"/>
     <mergeCell ref="M18:Q18"/>
     <mergeCell ref="C23:J23"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="M26:Q26"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="M17:Q17"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="M29:Q29"/>
-    <mergeCell ref="M23:Q23"/>
     <mergeCell ref="B31:J31"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C37:J37"/>
     <mergeCell ref="M19:Q19"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="K42:Q42"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -17,7 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hojeadora Robust" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gapcutter" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Calender K1 Easy'!$B$1:$Q$42</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -7242,6 +7244,22 @@
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
     <col width="12.77734375" customWidth="1" min="2" max="17"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="7.8" customHeight="1"/>
@@ -11096,13 +11114,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
     <col width="12.77734375" customWidth="1" min="2" max="17"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="7.8" customHeight="1"/>
@@ -12636,7 +12670,7 @@
     <mergeCell ref="K42:Q42"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gapcutter" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Komatsu OBS45'!$B$1:$Q$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Calender K1 Easy'!$B$1:$Q$42</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -6002,7 +6003,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -6019,18 +6020,6 @@
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
       </c>
-      <c r="C2" s="22" t="n"/>
-      <c r="D2" s="22" t="n"/>
-      <c r="E2" s="22" t="n"/>
-      <c r="F2" s="22" t="n"/>
-      <c r="G2" s="22" t="n"/>
-      <c r="H2" s="22" t="n"/>
-      <c r="I2" s="22" t="n"/>
-      <c r="J2" s="22" t="n"/>
-      <c r="K2" s="22" t="n"/>
-      <c r="L2" s="22" t="n"/>
-      <c r="M2" s="22" t="n"/>
-      <c r="N2" s="23" t="n"/>
       <c r="O2" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve"> No. de Documento             A9.I1.F2
@@ -6038,31 +6027,16 @@
  Fecha:                        08/06/2026</t>
         </is>
       </c>
-      <c r="P2" s="50" t="n"/>
-      <c r="Q2" s="51" t="n"/>
     </row>
     <row r="3" ht="97.8" customHeight="1">
       <c r="A3" s="11" t="n"/>
       <c r="B3" s="36" t="n"/>
-      <c r="C3" s="22" t="n"/>
-      <c r="D3" s="23" t="n"/>
       <c r="E3" s="38" t="inlineStr">
         <is>
           <t>MANTENIMIENTO PREVENTIVO   —   KOMATSU OBS45 – PRENSA OBDS</t>
         </is>
       </c>
-      <c r="F3" s="22" t="n"/>
-      <c r="G3" s="22" t="n"/>
-      <c r="H3" s="22" t="n"/>
-      <c r="I3" s="22" t="n"/>
-      <c r="J3" s="22" t="n"/>
-      <c r="K3" s="22" t="n"/>
-      <c r="L3" s="22" t="n"/>
-      <c r="M3" s="22" t="n"/>
-      <c r="N3" s="23" t="n"/>
       <c r="O3" s="35" t="n"/>
-      <c r="P3" s="22" t="n"/>
-      <c r="Q3" s="23" t="n"/>
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
@@ -6071,25 +6045,11 @@
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
       </c>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n"/>
-      <c r="E4" s="22" t="n"/>
-      <c r="F4" s="22" t="n"/>
-      <c r="G4" s="22" t="n"/>
-      <c r="H4" s="22" t="n"/>
-      <c r="I4" s="23" t="n"/>
       <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
       </c>
-      <c r="K4" s="22" t="n"/>
-      <c r="L4" s="22" t="n"/>
-      <c r="M4" s="22" t="n"/>
-      <c r="N4" s="22" t="n"/>
-      <c r="O4" s="22" t="n"/>
-      <c r="P4" s="22" t="n"/>
-      <c r="Q4" s="23" t="n"/>
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
@@ -6098,25 +6058,11 @@
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="22" t="n"/>
-      <c r="G5" s="22" t="n"/>
-      <c r="H5" s="22" t="n"/>
-      <c r="I5" s="23" t="n"/>
       <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
       </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="22" t="n"/>
-      <c r="M5" s="22" t="n"/>
-      <c r="N5" s="22" t="n"/>
-      <c r="O5" s="22" t="n"/>
-      <c r="P5" s="22" t="n"/>
-      <c r="Q5" s="23" t="n"/>
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
@@ -6125,31 +6071,17 @@
           <t>Nombre de máquina:  Komatsu OBS45</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="n"/>
-      <c r="H6" s="22" t="n"/>
-      <c r="I6" s="23" t="n"/>
       <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Número de máquina:  KO01</t>
         </is>
       </c>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="22" t="n"/>
-      <c r="M6" s="22" t="n"/>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="22" t="n"/>
-      <c r="P6" s="22" t="n"/>
-      <c r="Q6" s="23" t="n"/>
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MECÁNICO / HIDRÁULICO</t>
+          <t xml:space="preserve">  MECÁNICO / LUBRICACIÓN</t>
         </is>
       </c>
       <c r="C7" s="22" t="n"/>
@@ -6172,7 +6104,7 @@
       </c>
       <c r="M7" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMENTARIOS </t>
+          <t>COMENTARIOS</t>
         </is>
       </c>
       <c r="N7" s="22" t="n"/>
@@ -6189,7 +6121,7 @@
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>Inspección visual de estructura, cilindros y mangueras</t>
+          <t>Inspección visual de estructura: guías, columnas y tornillería</t>
         </is>
       </c>
       <c r="D8" s="22" t="n"/>
@@ -6217,14 +6149,14 @@
     </row>
     <row r="9" ht="25.05" customHeight="1">
       <c r="A9" s="11" t="n"/>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de nivel y calidad del aceite hidráulico</t>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Verificación del nivel de aceite Clutch &amp; Brake (visor - zona verde)</t>
         </is>
       </c>
       <c r="D9" s="22" t="n"/>
@@ -6259,7 +6191,7 @@
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>Revisión de cilindros hidráulicos (vástagos, sellos y fugas)</t>
+          <t>Verificación del nivel de aceite Gear Box (visor - zona verde)</t>
         </is>
       </c>
       <c r="D10" s="22" t="n"/>
@@ -6287,14 +6219,14 @@
     </row>
     <row r="11" ht="25.05" customHeight="1">
       <c r="A11" s="11" t="n"/>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
-        <is>
-          <t>Limpieza de filtro de aceite hidráulico</t>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de bomba de lubricación automática HOWA SMD: nivel de depósito</t>
         </is>
       </c>
       <c r="D11" s="22" t="n"/>
@@ -6329,7 +6261,7 @@
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>Revisión de bomba hidráulica (ruido, presión y temperatura)</t>
+          <t>Verificar caudal y ciclos del lubricador HOWA (ajuste de descarga SMD3/SMD6)</t>
         </is>
       </c>
       <c r="D12" s="22" t="n"/>
@@ -6357,14 +6289,14 @@
     </row>
     <row r="13" ht="25.05" customHeight="1">
       <c r="A13" s="11" t="n"/>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
-        <is>
-          <t>Verificación de válvulas de control y alivio de presión</t>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Lubricación manual de guías y columnas (puntos de engrase)</t>
         </is>
       </c>
       <c r="D13" s="22" t="n"/>
@@ -6427,14 +6359,14 @@
     </row>
     <row r="15" ht="25.05" customHeight="1">
       <c r="A15" s="11" t="n"/>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>Lubricación de guías, columnas y mecanismos de cierre</t>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de tornillería y fijaciones estructurales</t>
         </is>
       </c>
       <c r="D15" s="22" t="n"/>
@@ -6469,7 +6401,7 @@
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>Verificación de tornillería y fijaciones estructurales</t>
+          <t>Revisión del contador D.MAINT en panel Komatsu (reseteo si aplica)</t>
         </is>
       </c>
       <c r="D16" s="22" t="n"/>
@@ -6497,16 +6429,12 @@
     </row>
     <row r="17" ht="25.05" customHeight="1">
       <c r="A17" s="11" t="n"/>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C17" s="59" t="inlineStr">
-        <is>
-          <t>Cambio de aceite hidráulico (programado)</t>
-        </is>
-      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ELÉCTRICO</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n"/>
       <c r="D17" s="22" t="n"/>
       <c r="E17" s="22" t="n"/>
       <c r="F17" s="22" t="n"/>
@@ -6514,17 +6442,21 @@
       <c r="H17" s="22" t="n"/>
       <c r="I17" s="22" t="n"/>
       <c r="J17" s="23" t="n"/>
-      <c r="K17" s="62" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L17" s="62" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M17" s="62" t="n"/>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L17" s="27" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M17" s="27" t="inlineStr">
+        <is>
+          <t>COMENTARIOS</t>
+        </is>
+      </c>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="22" t="n"/>
@@ -6532,12 +6464,16 @@
     </row>
     <row r="18" ht="25.05" customHeight="1">
       <c r="A18" s="11" t="n"/>
-      <c r="B18" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ELÉCTRICO</t>
-        </is>
-      </c>
-      <c r="C18" s="58" t="n"/>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Verificación del panel Komatsu: HMI, alarmas e indicadores (T.COUNT, L.COUNT, D.MAINT)</t>
+        </is>
+      </c>
       <c r="D18" s="22" t="n"/>
       <c r="E18" s="22" t="n"/>
       <c r="F18" s="22" t="n"/>
@@ -6545,21 +6481,17 @@
       <c r="H18" s="22" t="n"/>
       <c r="I18" s="22" t="n"/>
       <c r="J18" s="23" t="n"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="L18" s="27" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="M18" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COMENTARIOS </t>
-        </is>
-      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M18" s="27" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
       <c r="P18" s="22" t="n"/>
@@ -6567,14 +6499,14 @@
     </row>
     <row r="19" ht="25.05" customHeight="1">
       <c r="A19" s="11" t="n"/>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>Verificación visual del tablero (alarmas e indicadores)</t>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Verificación del VFD Komatsu G7 (CIMR-G7A2371, 3.7kW): parámetros, fallas y temperatura</t>
         </is>
       </c>
       <c r="D19" s="22" t="n"/>
@@ -6609,7 +6541,7 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Limpieza de tableros eléctricos y revisión de cableado</t>
+          <t>Verificación del transformador HDS HTIB-Y7.5KEULB (7.5kVA, 460→220V): temperatura</t>
         </is>
       </c>
       <c r="D20" s="22" t="n"/>
@@ -6637,14 +6569,14 @@
     </row>
     <row r="21" ht="25.05" customHeight="1">
       <c r="A21" s="11" t="n"/>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C21" s="25" t="inlineStr">
-        <is>
-          <t>Reapriete de terminales en tablero eléctrico</t>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Revisión del interruptor principal Fuji BW50RAGU-3P020 (20A, 3P): estado y operación</t>
         </is>
       </c>
       <c r="D21" s="22" t="n"/>
@@ -6679,7 +6611,7 @@
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Verificación de fusibles, contactores y relés térmicos</t>
+          <t>Limpieza de tablero eléctrico y revisión de borneras (U1, X1, X2, U2, V1, Y1Y2, V2, W1, Z1Z2, W2)</t>
         </is>
       </c>
       <c r="D22" s="22" t="n"/>
@@ -6707,14 +6639,14 @@
     </row>
     <row r="23" ht="25.05" customHeight="1">
       <c r="A23" s="11" t="n"/>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de motores (temperatura, ruido y vibración)</t>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Reapriete de terminales y conexiones eléctricas</t>
         </is>
       </c>
       <c r="D23" s="22" t="n"/>
@@ -6749,7 +6681,7 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Revisión de sensores de posición y finales de carrera</t>
+          <t>Verificación de sensores de posición y finales de carrera</t>
         </is>
       </c>
       <c r="D24" s="22" t="n"/>
@@ -6777,14 +6709,14 @@
     </row>
     <row r="25" ht="25.05" customHeight="1">
       <c r="A25" s="11" t="n"/>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
-        <is>
-          <t>Revisión de dispositivos de seguridad y cortina óptica</t>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Revisión de dispositivos de seguridad: doble mando (TWO HAND) y cortina óptica (LIGHT GUARD)</t>
         </is>
       </c>
       <c r="D25" s="22" t="n"/>
@@ -6819,7 +6751,7 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Prueba funcional de paros de emergencia</t>
+          <t>Prueba funcional de paros de emergencia (EMG. STOP/FAULT)</t>
         </is>
       </c>
       <c r="D26" s="22" t="n"/>
@@ -6847,12 +6779,12 @@
     </row>
     <row r="27" ht="25.05" customHeight="1">
       <c r="A27" s="11" t="n"/>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>Verificación de tierras físicas y continuidad</t>
         </is>
@@ -6882,14 +6814,12 @@
     </row>
     <row r="28" ht="25.05" customHeight="1">
       <c r="A28" s="11" t="n"/>
-      <c r="B28" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>Termografía de tableros y conexiones</t>
-        </is>
-      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEUMÁTICO</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n"/>
       <c r="D28" s="22" t="n"/>
       <c r="E28" s="22" t="n"/>
       <c r="F28" s="22" t="n"/>
@@ -6897,17 +6827,21 @@
       <c r="H28" s="22" t="n"/>
       <c r="I28" s="22" t="n"/>
       <c r="J28" s="23" t="n"/>
-      <c r="K28" s="52" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L28" s="52" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M28" s="52" t="n"/>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L28" s="27" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M28" s="27" t="inlineStr">
+        <is>
+          <t>COMENTARIOS</t>
+        </is>
+      </c>
       <c r="N28" s="22" t="n"/>
       <c r="O28" s="22" t="n"/>
       <c r="P28" s="22" t="n"/>
@@ -6915,320 +6849,395 @@
     </row>
     <row r="29" ht="25.05" customHeight="1">
       <c r="A29" s="11" t="n"/>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>CALENDARIO  DE  MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n"/>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Verificación de presión de trabajo y purga de condensados</t>
+        </is>
+      </c>
       <c r="D29" s="22" t="n"/>
       <c r="E29" s="22" t="n"/>
       <c r="F29" s="22" t="n"/>
       <c r="G29" s="22" t="n"/>
       <c r="H29" s="22" t="n"/>
       <c r="I29" s="22" t="n"/>
-      <c r="J29" s="22" t="n"/>
-      <c r="K29" s="22" t="n"/>
-      <c r="L29" s="22" t="n"/>
-      <c r="M29" s="23" t="n"/>
-      <c r="N29" s="43" t="inlineStr">
-        <is>
-          <t>VOLTAJE ALIMENTACIÓN</t>
-        </is>
-      </c>
-      <c r="O29" s="22" t="n"/>
-      <c r="P29" s="22" t="n"/>
-      <c r="Q29" s="23" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="25.05" customHeight="1">
       <c r="A30" s="11" t="n"/>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>ENE</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>FEB</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>ABR</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>JUN</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>SEP</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>OCT</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>NOV</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>DIC</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>VAC</t>
-        </is>
-      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Revisión del regulador de presión KONAN D4-15A-NR (ajuste y funcionamiento)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="22" t="n"/>
+      <c r="O30" s="22" t="n"/>
+      <c r="P30" s="22" t="n"/>
+      <c r="Q30" s="23" t="n"/>
     </row>
     <row r="31" ht="25.05" customHeight="1">
       <c r="A31" s="11" t="n"/>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>(   )</t>
-        </is>
-      </c>
-      <c r="N31" s="6" t="n"/>
-      <c r="O31" s="6" t="n"/>
-      <c r="P31" s="6" t="n"/>
-      <c r="Q31" s="6" t="n"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Inspección de mangueras, racores y conexiones neumáticas</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="23" t="n"/>
     </row>
     <row r="32" ht="25.05" customHeight="1">
       <c r="A32" s="11" t="n"/>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>CALENDARIO  DE  MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="22" t="n"/>
+      <c r="K32" s="22" t="n"/>
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="23" t="n"/>
+      <c r="N32" s="43" t="inlineStr">
+        <is>
+          <t>VOLTAJE ALIMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="O32" s="22" t="n"/>
+      <c r="P32" s="22" t="n"/>
+      <c r="Q32" s="23" t="n"/>
+    </row>
+    <row r="33" ht="25.05" customHeight="1">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>FEB</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>ABR</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>JUN</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>JUL</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>SEP</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>NOV</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>VAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24.6" customHeight="1">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>(   )</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Realizo: </t>
         </is>
       </c>
-      <c r="C32" s="50" t="n"/>
-      <c r="D32" s="50" t="n"/>
-      <c r="E32" s="50" t="n"/>
-      <c r="F32" s="50" t="n"/>
-      <c r="G32" s="51" t="n"/>
-      <c r="H32" s="41" t="inlineStr">
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+      <c r="E35" s="50" t="n"/>
+      <c r="F35" s="50" t="n"/>
+      <c r="G35" s="51" t="n"/>
+      <c r="H35" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
       </c>
-      <c r="I32" s="75" t="n"/>
-      <c r="J32" s="75" t="n"/>
-      <c r="K32" s="40" t="inlineStr">
+      <c r="I35" s="75" t="n"/>
+      <c r="J35" s="75" t="n"/>
+      <c r="K35" s="40" t="inlineStr">
         <is>
           <t>Supervisor de Producción: 
 Firma: _____________________________</t>
         </is>
       </c>
-      <c r="L32" s="50" t="n"/>
-      <c r="M32" s="50" t="n"/>
-      <c r="N32" s="50" t="n"/>
-      <c r="O32" s="50" t="n"/>
-      <c r="P32" s="50" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-    </row>
-    <row r="33" ht="25.05" customHeight="1">
-      <c r="B33" s="39" t="inlineStr">
+      <c r="L35" s="50" t="n"/>
+      <c r="M35" s="50" t="n"/>
+      <c r="N35" s="50" t="n"/>
+      <c r="O35" s="50" t="n"/>
+      <c r="P35" s="50" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="C33" s="76" t="n"/>
-      <c r="D33" s="76" t="n"/>
-      <c r="E33" s="76" t="n"/>
-      <c r="F33" s="76" t="n"/>
-      <c r="G33" s="77" t="n"/>
-      <c r="K33" s="39" t="inlineStr">
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+      <c r="E36" s="50" t="n"/>
+      <c r="F36" s="50" t="n"/>
+      <c r="G36" s="51" t="n"/>
+      <c r="K36" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="L33" s="76" t="n"/>
-      <c r="M33" s="76" t="n"/>
-      <c r="N33" s="76" t="n"/>
-      <c r="O33" s="76" t="n"/>
-      <c r="P33" s="76" t="n"/>
-      <c r="Q33" s="77" t="n"/>
-    </row>
-    <row r="34" ht="24.6" customHeight="1">
-      <c r="B34" s="78" t="n"/>
-      <c r="C34" s="79" t="n"/>
-      <c r="D34" s="79" t="n"/>
-      <c r="E34" s="79" t="n"/>
-      <c r="F34" s="79" t="n"/>
-      <c r="G34" s="80" t="n"/>
-      <c r="K34" s="78" t="n"/>
-      <c r="L34" s="79" t="n"/>
-      <c r="M34" s="79" t="n"/>
-      <c r="N34" s="79" t="n"/>
-      <c r="O34" s="79" t="n"/>
-      <c r="P34" s="79" t="n"/>
-      <c r="Q34" s="80" t="n"/>
+      <c r="L36" s="50" t="n"/>
+      <c r="M36" s="50" t="n"/>
+      <c r="N36" s="50" t="n"/>
+      <c r="O36" s="50" t="n"/>
+      <c r="P36" s="50" t="n"/>
+      <c r="Q36" s="51" t="n"/>
     </row>
     <row r="45">
       <c r="J45" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="B33:G34"/>
+  <mergeCells count="57">
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="M30:Q30"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="K36:Q36"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="M28:Q28"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="M27:Q27"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="C13:J13"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C24:J24"/>
-    <mergeCell ref="J5:Q5"/>
-    <mergeCell ref="K33:Q34"/>
-    <mergeCell ref="C14:J14"/>
     <mergeCell ref="M9:Q9"/>
-    <mergeCell ref="B29:M29"/>
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="H32:J34"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="J6:Q6"/>
+    <mergeCell ref="C29:J29"/>
     <mergeCell ref="M11:Q11"/>
-    <mergeCell ref="C25:J25"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="C16:J16"/>
-    <mergeCell ref="E3:N3"/>
     <mergeCell ref="M10:Q10"/>
     <mergeCell ref="C22:J22"/>
     <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="C31:J31"/>
     <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="M31:Q31"/>
     <mergeCell ref="C9:J9"/>
     <mergeCell ref="M7:Q7"/>
     <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="J4:Q4"/>
-    <mergeCell ref="M12:Q12"/>
     <mergeCell ref="C12:J12"/>
+    <mergeCell ref="C21:J21"/>
     <mergeCell ref="M25:Q25"/>
-    <mergeCell ref="C21:J21"/>
     <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="M28:Q28"/>
-    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B32:M32"/>
+    <mergeCell ref="K35:Q35"/>
     <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="M27:Q27"/>
     <mergeCell ref="C23:J23"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="B2:N2"/>
     <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="M26:Q26"/>
     <mergeCell ref="B7:J7"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="B3:D3"/>
     <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="M26:Q26"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="M29:Q29"/>
     <mergeCell ref="M23:Q23"/>
-    <mergeCell ref="M14:Q14"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C19:J19"/>
     <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="N29:Q29"/>
-    <mergeCell ref="B4:I4"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -6010,6 +6010,22 @@
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
     <col width="12.77734375" customWidth="1" min="2" max="17"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="7.8" customHeight="1"/>
@@ -6028,7 +6044,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="97.8" customHeight="1">
+    <row r="3" ht="50" customHeight="1">
       <c r="A3" s="11" t="n"/>
       <c r="B3" s="36" t="n"/>
       <c r="E3" s="38" t="inlineStr">
@@ -6947,7 +6963,7 @@
       <c r="P31" s="22" t="n"/>
       <c r="Q31" s="23" t="n"/>
     </row>
-    <row r="32" ht="25.05" customHeight="1">
+    <row r="32" ht="17.4" customHeight="1">
       <c r="A32" s="11" t="n"/>
       <c r="B32" s="24" t="inlineStr">
         <is>
@@ -6974,7 +6990,7 @@
       <c r="P32" s="22" t="n"/>
       <c r="Q32" s="23" t="n"/>
     </row>
-    <row r="33" ht="25.05" customHeight="1">
+    <row r="33" ht="17.4" customHeight="1">
       <c r="B33" s="10" t="inlineStr">
         <is>
           <t>ENE</t>
@@ -7056,7 +7072,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="24.6" customHeight="1">
+    <row r="34" ht="17.4" customHeight="1">
       <c r="B34" s="9" t="inlineStr">
         <is>
           <t>(   )</t>
@@ -7118,7 +7134,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="24" customHeight="1">
       <c r="A35" s="11" t="n"/>
       <c r="B35" s="39" t="inlineStr">
         <is>
@@ -7150,7 +7166,7 @@
       <c r="P35" s="50" t="n"/>
       <c r="Q35" s="51" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="14.4" customHeight="1">
       <c r="B36" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -7180,38 +7196,24 @@
   <mergeCells count="57">
     <mergeCell ref="H35:I35"/>
     <mergeCell ref="C30:J30"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="C24:J24"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="C14:J14"/>
-    <mergeCell ref="C20:J20"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="C25:J25"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="M30:Q30"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="K36:Q36"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="M28:Q28"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="M27:Q27"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="M14:Q14"/>
-    <mergeCell ref="C19:J19"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="C24:J24"/>
     <mergeCell ref="M9:Q9"/>
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="M20:Q20"/>
     <mergeCell ref="C29:J29"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="B28:J28"/>
     <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="C25:J25"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="C16:J16"/>
     <mergeCell ref="M10:Q10"/>
     <mergeCell ref="C22:J22"/>
     <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="N32:Q32"/>
     <mergeCell ref="C31:J31"/>
     <mergeCell ref="M13:Q13"/>
     <mergeCell ref="M31:Q31"/>
@@ -7219,20 +7221,34 @@
     <mergeCell ref="M7:Q7"/>
     <mergeCell ref="M16:Q16"/>
     <mergeCell ref="C12:J12"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="M30:Q30"/>
     <mergeCell ref="C21:J21"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="K36:Q36"/>
     <mergeCell ref="M25:Q25"/>
+    <mergeCell ref="C11:J11"/>
     <mergeCell ref="M15:Q15"/>
     <mergeCell ref="B35:G35"/>
+    <mergeCell ref="M28:Q28"/>
     <mergeCell ref="B32:M32"/>
     <mergeCell ref="K35:Q35"/>
+    <mergeCell ref="C27:J27"/>
     <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="M27:Q27"/>
     <mergeCell ref="C23:J23"/>
+    <mergeCell ref="C8:J8"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="M26:Q26"/>
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="M24:Q24"/>
     <mergeCell ref="M29:Q29"/>
     <mergeCell ref="M23:Q23"/>
+    <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="C13:J13"/>
     <mergeCell ref="M19:Q19"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -6005,7 +6005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Q45"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
@@ -6036,6 +6036,18 @@
           <t>AD-PACK  —  ÁREA DE CONVERSIÓN</t>
         </is>
       </c>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="22" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="22" t="n"/>
+      <c r="K2" s="22" t="n"/>
+      <c r="L2" s="22" t="n"/>
+      <c r="M2" s="22" t="n"/>
+      <c r="N2" s="23" t="n"/>
       <c r="O2" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve"> No. de Documento             A9.I1.F2
@@ -6043,16 +6055,31 @@
  Fecha:                        08/06/2026</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="50" customHeight="1">
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="51" t="n"/>
+    </row>
+    <row r="3" ht="97.8" customHeight="1">
       <c r="A3" s="11" t="n"/>
       <c r="B3" s="36" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="23" t="n"/>
       <c r="E3" s="38" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO PREVENTIVO   —   KOMATSU OBS45 – PRENSA OBDS</t>
-        </is>
-      </c>
+          <t>MANTENIMIENTO PREVENTIVO   —   KOMATSU OBS45</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
+      <c r="K3" s="22" t="n"/>
+      <c r="L3" s="22" t="n"/>
+      <c r="M3" s="22" t="n"/>
+      <c r="N3" s="23" t="n"/>
       <c r="O3" s="35" t="n"/>
+      <c r="P3" s="22" t="n"/>
+      <c r="Q3" s="23" t="n"/>
     </row>
     <row r="4" ht="25.05" customHeight="1">
       <c r="A4" s="11" t="n"/>
@@ -6061,11 +6088,25 @@
           <t>Alcance: Equipos de Conversión – AD-PACK</t>
         </is>
       </c>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="22" t="n"/>
+      <c r="F4" s="22" t="n"/>
+      <c r="G4" s="22" t="n"/>
+      <c r="H4" s="22" t="n"/>
+      <c r="I4" s="23" t="n"/>
       <c r="J4" s="33" t="inlineStr">
         <is>
           <t>Autor: Mariano Leyva</t>
         </is>
       </c>
+      <c r="K4" s="22" t="n"/>
+      <c r="L4" s="22" t="n"/>
+      <c r="M4" s="22" t="n"/>
+      <c r="N4" s="22" t="n"/>
+      <c r="O4" s="22" t="n"/>
+      <c r="P4" s="22" t="n"/>
+      <c r="Q4" s="23" t="n"/>
     </row>
     <row r="5" ht="46.2" customHeight="1">
       <c r="A5" s="11" t="n"/>
@@ -6074,24 +6115,52 @@
           <t>Tipo de mantenimiento:  Preventivo</t>
         </is>
       </c>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="23" t="n"/>
       <c r="J5" s="33" t="inlineStr">
         <is>
           <t>Indicaciones: Usar equipo de seguridad.</t>
         </is>
       </c>
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="22" t="n"/>
+      <c r="M5" s="22" t="n"/>
+      <c r="N5" s="22" t="n"/>
+      <c r="O5" s="22" t="n"/>
+      <c r="P5" s="22" t="n"/>
+      <c r="Q5" s="23" t="n"/>
     </row>
     <row r="6" ht="25.05" customHeight="1">
       <c r="A6" s="11" t="n"/>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>Nombre de máquina:  Komatsu OBS45</t>
-        </is>
-      </c>
+          <t>Nombre de máquina:  Komatsu OBS45 – Prensa de Punzonado</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+      <c r="I6" s="23" t="n"/>
       <c r="J6" s="33" t="inlineStr">
         <is>
           <t>Número de máquina:  KO01</t>
         </is>
       </c>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="22" t="n"/>
+      <c r="P6" s="22" t="n"/>
+      <c r="Q6" s="23" t="n"/>
     </row>
     <row r="7" ht="25.05" customHeight="1">
       <c r="A7" s="11" t="n"/>
@@ -7193,11 +7262,12 @@
       <c r="J45" s="18" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="68">
     <mergeCell ref="H35:I35"/>
     <mergeCell ref="C30:J30"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C24:J24"/>
+    <mergeCell ref="J5:Q5"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="M9:Q9"/>
@@ -7208,8 +7278,10 @@
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="M11:Q11"/>
     <mergeCell ref="C25:J25"/>
+    <mergeCell ref="J6:Q6"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="C16:J16"/>
+    <mergeCell ref="E3:N3"/>
     <mergeCell ref="M10:Q10"/>
     <mergeCell ref="C22:J22"/>
     <mergeCell ref="M22:Q22"/>
@@ -7217,8 +7289,10 @@
     <mergeCell ref="C31:J31"/>
     <mergeCell ref="M13:Q13"/>
     <mergeCell ref="M31:Q31"/>
+    <mergeCell ref="O2:Q2"/>
     <mergeCell ref="C9:J9"/>
     <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="J4:Q4"/>
     <mergeCell ref="M16:Q16"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="M12:Q12"/>
@@ -7238,18 +7312,24 @@
     <mergeCell ref="M18:Q18"/>
     <mergeCell ref="M27:Q27"/>
     <mergeCell ref="C23:J23"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="O3:Q3"/>
     <mergeCell ref="C8:J8"/>
     <mergeCell ref="M8:Q8"/>
     <mergeCell ref="M26:Q26"/>
     <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="M17:Q17"/>
     <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="B6:I6"/>
     <mergeCell ref="M29:Q29"/>
     <mergeCell ref="M23:Q23"/>
     <mergeCell ref="M14:Q14"/>
+    <mergeCell ref="B5:I5"/>
     <mergeCell ref="C19:J19"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="B4:I4"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7264,7 +7344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Q39"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -174,7 +174,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -262,6 +262,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002d8a45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001a5c2a"/>
       </patternFill>
     </fill>
   </fills>
@@ -604,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -860,6 +865,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6005,7 +6013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A2:Q45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
@@ -7215,7 +7223,7 @@
       <c r="E35" s="50" t="n"/>
       <c r="F35" s="50" t="n"/>
       <c r="G35" s="51" t="n"/>
-      <c r="H35" s="41" t="inlineStr">
+      <c r="H35" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
@@ -7263,7 +7271,6 @@
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="H35:I35"/>
     <mergeCell ref="C30:J30"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C24:J24"/>
@@ -7283,6 +7290,7 @@
     <mergeCell ref="C16:J16"/>
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="H35:J36"/>
     <mergeCell ref="C22:J22"/>
     <mergeCell ref="M22:Q22"/>
     <mergeCell ref="N32:Q32"/>
@@ -7292,8 +7300,8 @@
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="C9:J9"/>
     <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="M16:Q16"/>
     <mergeCell ref="J4:Q4"/>
-    <mergeCell ref="M16:Q16"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="M12:Q12"/>
     <mergeCell ref="M30:Q30"/>
@@ -7344,7 +7352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A2:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="9.5546875" customWidth="1" min="1" max="1"/>
@@ -12649,7 +12657,7 @@
       <c r="E41" s="50" t="n"/>
       <c r="F41" s="50" t="n"/>
       <c r="G41" s="51" t="n"/>
-      <c r="H41" s="41" t="inlineStr">
+      <c r="H41" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
@@ -12713,7 +12721,6 @@
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C24:J24"/>
     <mergeCell ref="J5:Q5"/>
-    <mergeCell ref="H41:I41"/>
     <mergeCell ref="M9:Q9"/>
     <mergeCell ref="C26:J26"/>
     <mergeCell ref="M20:Q20"/>
@@ -12723,6 +12730,7 @@
     <mergeCell ref="M22:Q22"/>
     <mergeCell ref="M31:Q31"/>
     <mergeCell ref="C9:J9"/>
+    <mergeCell ref="H41:J42"/>
     <mergeCell ref="J4:Q4"/>
     <mergeCell ref="M15:Q15"/>
     <mergeCell ref="B41:G41"/>

--- a/MTTO_Preventivo_Conversion_2026.xlsx
+++ b/MTTO_Preventivo_Conversion_2026.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -173,8 +173,13 @@
       <color rgb="001b5e20"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -267,6 +272,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001a5c2a"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A5C2A"/>
       </patternFill>
     </fill>
   </fills>
@@ -609,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -868,6 +878,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7223,7 +7236,7 @@
       <c r="E35" s="50" t="n"/>
       <c r="F35" s="50" t="n"/>
       <c r="G35" s="51" t="n"/>
-      <c r="H35" s="107" t="inlineStr">
+      <c r="H35" s="108" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
@@ -12657,7 +12670,7 @@
       <c r="E41" s="50" t="n"/>
       <c r="F41" s="50" t="n"/>
       <c r="G41" s="51" t="n"/>
-      <c r="H41" s="107" t="inlineStr">
+      <c r="H41" s="108" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha: </t>
         </is>
